--- a/data/warn-scraper/cache/ia/source.xlsx
+++ b/data/warn-scraper/cache/ia/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowamac.sharepoint.com/sites/IWDWorkforceServices/Shared Documents/Rapid Response/WARN/WARN Log/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C06E98D-9850-405D-91BA-89C3839E5CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1868EF7-8924-45B7-9CE7-1577EC9ABDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6365" uniqueCount="1157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6374" uniqueCount="1160">
   <si>
     <t>Iowa WARN Log</t>
   </si>
@@ -3488,6 +3488,15 @@
   </si>
   <si>
     <t>1000 4th St NW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cedar Valley Corp, LLC </t>
+  </si>
+  <si>
+    <t>2637 Wagner Road</t>
+  </si>
+  <si>
+    <t>02/6/2026</t>
   </si>
   <si>
     <t>Lynn</t>
@@ -3523,7 +3532,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yy"/>
     <numFmt numFmtId="166" formatCode="m/d/yyyy;@"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3605,6 +3614,18 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Calibri"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -3672,7 +3693,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3770,20 +3791,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3795,6 +3804,48 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3804,27 +3855,29 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -30555,40 +30608,40 @@
       <c r="Z505" s="2"/>
     </row>
     <row r="506" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A506" s="7" t="s">
+      <c r="A506" s="48" t="s">
         <v>991</v>
       </c>
-      <c r="B506" s="2" t="s">
+      <c r="B506" s="49" t="s">
         <v>992</v>
       </c>
-      <c r="C506" s="2" t="s">
+      <c r="C506" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="D506" s="2" t="s">
+      <c r="D506" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="E506" s="2" t="s">
+      <c r="E506" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F506" s="5">
+      <c r="F506" s="50">
         <v>52498</v>
       </c>
-      <c r="G506" s="2" t="s">
+      <c r="G506" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="H506" s="5">
+      <c r="H506" s="50">
         <v>2</v>
       </c>
-      <c r="I506" s="26" t="s">
+      <c r="I506" s="51" t="s">
         <v>1095</v>
       </c>
-      <c r="J506" s="26">
+      <c r="J506" s="51">
         <v>45961</v>
       </c>
-      <c r="K506" s="2" t="s">
+      <c r="K506" s="49" t="s">
         <v>366</v>
       </c>
-      <c r="L506" s="2" t="s">
+      <c r="L506" s="49" t="s">
         <v>45</v>
       </c>
       <c r="M506" s="2"/>
@@ -30607,40 +30660,40 @@
       <c r="Z506" s="2"/>
     </row>
     <row r="507" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A507" s="7" t="s">
+      <c r="A507" s="48" t="s">
         <v>169</v>
       </c>
-      <c r="B507" s="2" t="s">
+      <c r="B507" s="49" t="s">
         <v>481</v>
       </c>
-      <c r="C507" s="2" t="s">
+      <c r="C507" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="D507" s="2" t="s">
+      <c r="D507" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="E507" s="2" t="s">
+      <c r="E507" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F507" s="5">
+      <c r="F507" s="50">
         <v>50266</v>
       </c>
-      <c r="G507" s="2" t="s">
+      <c r="G507" s="49" t="s">
         <v>732</v>
       </c>
-      <c r="H507" s="5">
+      <c r="H507" s="50">
         <v>23</v>
       </c>
-      <c r="I507" s="26">
+      <c r="I507" s="51">
         <v>45930</v>
       </c>
-      <c r="J507" s="26">
+      <c r="J507" s="51">
         <v>45989</v>
       </c>
-      <c r="K507" s="2" t="s">
+      <c r="K507" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="L507" s="2" t="s">
+      <c r="L507" s="49" t="s">
         <v>107</v>
       </c>
       <c r="M507" s="2"/>
@@ -30659,40 +30712,40 @@
       <c r="Z507" s="2"/>
     </row>
     <row r="508" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A508" s="7" t="s">
+      <c r="A508" s="48" t="s">
         <v>1096</v>
       </c>
-      <c r="B508" s="2" t="s">
+      <c r="B508" s="49" t="s">
         <v>1097</v>
       </c>
-      <c r="C508" s="2" t="s">
+      <c r="C508" s="49" t="s">
         <v>538</v>
       </c>
-      <c r="D508" s="2" t="s">
+      <c r="D508" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="E508" s="2" t="s">
+      <c r="E508" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F508" s="5">
+      <c r="F508" s="50">
         <v>52001</v>
       </c>
-      <c r="G508" s="2" t="s">
+      <c r="G508" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="H508" s="5">
+      <c r="H508" s="50">
         <v>38</v>
       </c>
-      <c r="I508" s="26">
+      <c r="I508" s="51">
         <v>45931</v>
       </c>
-      <c r="J508" s="26">
+      <c r="J508" s="51">
         <v>45962</v>
       </c>
-      <c r="K508" s="2" t="s">
+      <c r="K508" s="49" t="s">
         <v>391</v>
       </c>
-      <c r="L508" s="2" t="s">
+      <c r="L508" s="49" t="s">
         <v>107</v>
       </c>
       <c r="M508" s="2"/>
@@ -30711,40 +30764,40 @@
       <c r="Z508" s="2"/>
     </row>
     <row r="509" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A509" s="7" t="s">
+      <c r="A509" s="48" t="s">
         <v>1096</v>
       </c>
-      <c r="B509" s="2" t="s">
+      <c r="B509" s="49" t="s">
         <v>1097</v>
       </c>
-      <c r="C509" s="2" t="s">
+      <c r="C509" s="49" t="s">
         <v>538</v>
       </c>
-      <c r="D509" s="2" t="s">
+      <c r="D509" s="49" t="s">
         <v>140</v>
       </c>
-      <c r="E509" s="2" t="s">
+      <c r="E509" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F509" s="5">
+      <c r="F509" s="50">
         <v>52001</v>
       </c>
-      <c r="G509" s="2" t="s">
+      <c r="G509" s="49" t="s">
         <v>732</v>
       </c>
-      <c r="H509" s="5">
+      <c r="H509" s="50">
         <v>2</v>
       </c>
-      <c r="I509" s="26">
+      <c r="I509" s="51">
         <v>45937</v>
       </c>
-      <c r="J509" s="26">
+      <c r="J509" s="51">
         <v>45962</v>
       </c>
-      <c r="K509" s="2" t="s">
+      <c r="K509" s="49" t="s">
         <v>391</v>
       </c>
-      <c r="L509" s="2" t="s">
+      <c r="L509" s="49" t="s">
         <v>107</v>
       </c>
       <c r="M509" s="2"/>
@@ -30763,40 +30816,40 @@
       <c r="Z509" s="2"/>
     </row>
     <row r="510" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A510" s="7" t="s">
+      <c r="A510" s="48" t="s">
         <v>169</v>
       </c>
-      <c r="B510" s="2" t="s">
+      <c r="B510" s="49" t="s">
         <v>481</v>
       </c>
-      <c r="C510" s="2" t="s">
+      <c r="C510" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="D510" s="2" t="s">
+      <c r="D510" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="E510" s="2" t="s">
+      <c r="E510" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F510" s="5">
+      <c r="F510" s="50">
         <v>50266</v>
       </c>
-      <c r="G510" s="2" t="s">
+      <c r="G510" s="49" t="s">
         <v>732</v>
       </c>
-      <c r="H510" s="5">
+      <c r="H510" s="50">
         <v>1</v>
       </c>
-      <c r="I510" s="26">
+      <c r="I510" s="51">
         <v>45944</v>
       </c>
-      <c r="J510" s="26">
+      <c r="J510" s="51">
         <v>46003</v>
       </c>
-      <c r="K510" s="2" t="s">
+      <c r="K510" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="L510" s="2" t="s">
+      <c r="L510" s="49" t="s">
         <v>107</v>
       </c>
       <c r="M510" s="2"/>
@@ -30815,40 +30868,40 @@
       <c r="Z510" s="2"/>
     </row>
     <row r="511" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A511" s="7" t="s">
+      <c r="A511" s="48" t="s">
         <v>1098</v>
       </c>
-      <c r="B511" s="2" t="s">
+      <c r="B511" s="49" t="s">
         <v>1099</v>
       </c>
-      <c r="C511" s="2" t="s">
+      <c r="C511" s="49" t="s">
         <v>65</v>
       </c>
-      <c r="D511" s="2" t="s">
+      <c r="D511" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="E511" s="2" t="s">
+      <c r="E511" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F511" s="5">
+      <c r="F511" s="50">
         <v>52722</v>
       </c>
-      <c r="G511" s="2" t="s">
+      <c r="G511" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="H511" s="5">
+      <c r="H511" s="50">
         <v>85</v>
       </c>
-      <c r="I511" s="26">
+      <c r="I511" s="51">
         <v>45953</v>
       </c>
-      <c r="J511" s="26">
+      <c r="J511" s="51">
         <v>45959</v>
       </c>
-      <c r="K511" s="2" t="s">
+      <c r="K511" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="L511" s="2" t="s">
+      <c r="L511" s="49" t="s">
         <v>37</v>
       </c>
       <c r="M511" s="2"/>
@@ -30867,40 +30920,40 @@
       <c r="Z511" s="2"/>
     </row>
     <row r="512" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A512" s="7" t="s">
+      <c r="A512" s="48" t="s">
         <v>1100</v>
       </c>
-      <c r="B512" s="2" t="s">
+      <c r="B512" s="49" t="s">
         <v>1101</v>
       </c>
-      <c r="C512" s="2" t="s">
+      <c r="C512" s="49" t="s">
         <v>886</v>
       </c>
-      <c r="D512" s="2" t="s">
+      <c r="D512" s="49" t="s">
         <v>779</v>
       </c>
-      <c r="E512" s="2" t="s">
+      <c r="E512" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F512" s="5">
+      <c r="F512" s="50">
         <v>52653</v>
       </c>
-      <c r="G512" s="2" t="s">
+      <c r="G512" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="H512" s="5">
+      <c r="H512" s="50">
         <v>21</v>
       </c>
-      <c r="I512" s="26">
+      <c r="I512" s="51">
         <v>45957</v>
       </c>
-      <c r="J512" s="26">
+      <c r="J512" s="51">
         <v>45957</v>
       </c>
-      <c r="K512" s="2" t="s">
+      <c r="K512" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="L512" s="2" t="s">
+      <c r="L512" s="49" t="s">
         <v>37</v>
       </c>
       <c r="M512" s="2"/>
@@ -30919,40 +30972,40 @@
       <c r="Z512" s="2"/>
     </row>
     <row r="513" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A513" s="7" t="s">
+      <c r="A513" s="48" t="s">
         <v>995</v>
       </c>
-      <c r="B513" s="2" t="s">
+      <c r="B513" s="49" t="s">
         <v>1102</v>
       </c>
-      <c r="C513" s="2" t="s">
+      <c r="C513" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="D513" s="2" t="s">
+      <c r="D513" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="E513" s="2" t="s">
+      <c r="E513" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F513" s="5">
+      <c r="F513" s="50">
         <v>52404</v>
       </c>
-      <c r="G513" s="2" t="s">
+      <c r="G513" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H513" s="5">
+      <c r="H513" s="50">
         <v>46</v>
       </c>
-      <c r="I513" s="26">
+      <c r="I513" s="51">
         <v>45958</v>
       </c>
-      <c r="J513" s="26">
+      <c r="J513" s="51">
         <v>45987</v>
       </c>
-      <c r="K513" s="2" t="s">
+      <c r="K513" s="49" t="s">
         <v>366</v>
       </c>
-      <c r="L513" s="2" t="s">
+      <c r="L513" s="49" t="s">
         <v>181</v>
       </c>
       <c r="M513" s="2"/>
@@ -30971,40 +31024,40 @@
       <c r="Z513" s="2"/>
     </row>
     <row r="514" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A514" s="7" t="s">
+      <c r="A514" s="48" t="s">
         <v>169</v>
       </c>
-      <c r="B514" s="2" t="s">
+      <c r="B514" s="49" t="s">
         <v>481</v>
       </c>
-      <c r="C514" s="2" t="s">
+      <c r="C514" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="D514" s="2" t="s">
+      <c r="D514" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="E514" s="2" t="s">
+      <c r="E514" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F514" s="5">
+      <c r="F514" s="50">
         <v>50266</v>
       </c>
-      <c r="G514" s="2" t="s">
+      <c r="G514" s="49" t="s">
         <v>732</v>
       </c>
-      <c r="H514" s="5">
+      <c r="H514" s="50">
         <v>63</v>
       </c>
-      <c r="I514" s="26">
+      <c r="I514" s="51">
         <v>45958</v>
       </c>
-      <c r="J514" s="26">
+      <c r="J514" s="51">
         <v>46017</v>
       </c>
-      <c r="K514" s="2" t="s">
+      <c r="K514" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="L514" s="2" t="s">
+      <c r="L514" s="49" t="s">
         <v>107</v>
       </c>
       <c r="M514" s="2"/>
@@ -31023,40 +31076,40 @@
       <c r="Z514" s="2"/>
     </row>
     <row r="515" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A515" s="7" t="s">
+      <c r="A515" s="48" t="s">
         <v>1103</v>
       </c>
-      <c r="B515" s="2" t="s">
+      <c r="B515" s="49" t="s">
         <v>1104</v>
       </c>
-      <c r="C515" s="2" t="s">
+      <c r="C515" s="49" t="s">
         <v>568</v>
       </c>
-      <c r="D515" s="2" t="s">
+      <c r="D515" s="49" t="s">
         <v>167</v>
       </c>
-      <c r="E515" s="2" t="s">
+      <c r="E515" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F515" s="5">
+      <c r="F515" s="50">
         <v>50401</v>
       </c>
-      <c r="G515" s="2" t="s">
+      <c r="G515" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="H515" s="5">
+      <c r="H515" s="50">
         <v>147</v>
       </c>
-      <c r="I515" s="26">
+      <c r="I515" s="51">
         <v>45959</v>
       </c>
-      <c r="J515" s="26">
+      <c r="J515" s="51">
         <v>46022</v>
       </c>
-      <c r="K515" s="2" t="s">
+      <c r="K515" s="49" t="s">
         <v>391</v>
       </c>
-      <c r="L515" s="2" t="s">
+      <c r="L515" s="49" t="s">
         <v>220</v>
       </c>
       <c r="M515" s="2"/>
@@ -31075,40 +31128,40 @@
       <c r="Z515" s="2"/>
     </row>
     <row r="516" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A516" s="7" t="s">
+      <c r="A516" s="48" t="s">
         <v>991</v>
       </c>
-      <c r="B516" s="2" t="s">
+      <c r="B516" s="49" t="s">
         <v>992</v>
       </c>
-      <c r="C516" s="2" t="s">
+      <c r="C516" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="D516" s="2" t="s">
+      <c r="D516" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="E516" s="2" t="s">
+      <c r="E516" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F516" s="5">
+      <c r="F516" s="50">
         <v>52498</v>
       </c>
-      <c r="G516" s="2" t="s">
+      <c r="G516" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="H516" s="5">
+      <c r="H516" s="50">
         <v>3</v>
       </c>
-      <c r="I516" s="26">
+      <c r="I516" s="51">
         <v>45965</v>
       </c>
-      <c r="J516" s="26">
+      <c r="J516" s="51">
         <v>46022</v>
       </c>
-      <c r="K516" s="2" t="s">
+      <c r="K516" s="49" t="s">
         <v>366</v>
       </c>
-      <c r="L516" s="2" t="s">
+      <c r="L516" s="49" t="s">
         <v>45</v>
       </c>
       <c r="M516" s="2"/>
@@ -31127,40 +31180,40 @@
       <c r="Z516" s="2"/>
     </row>
     <row r="517" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A517" s="7" t="s">
+      <c r="A517" s="48" t="s">
         <v>169</v>
       </c>
-      <c r="B517" s="2" t="s">
+      <c r="B517" s="49" t="s">
         <v>481</v>
       </c>
-      <c r="C517" s="2" t="s">
+      <c r="C517" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="D517" s="2" t="s">
+      <c r="D517" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="E517" s="2" t="s">
+      <c r="E517" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F517" s="5">
+      <c r="F517" s="50">
         <v>50266</v>
       </c>
-      <c r="G517" s="2" t="s">
+      <c r="G517" s="49" t="s">
         <v>732</v>
       </c>
-      <c r="H517" s="5">
+      <c r="H517" s="50">
         <v>26</v>
       </c>
-      <c r="I517" s="26">
+      <c r="I517" s="51">
         <v>45965</v>
       </c>
-      <c r="J517" s="26">
+      <c r="J517" s="51">
         <v>46024</v>
       </c>
-      <c r="K517" s="2" t="s">
+      <c r="K517" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="L517" s="2" t="s">
+      <c r="L517" s="49" t="s">
         <v>107</v>
       </c>
       <c r="M517" s="2"/>
@@ -31180,40 +31233,40 @@
       <c r="AB517"/>
     </row>
     <row r="518" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A518" s="7" t="s">
+      <c r="A518" s="48" t="s">
         <v>745</v>
       </c>
-      <c r="B518" s="2" t="s">
+      <c r="B518" s="49" t="s">
         <v>1030</v>
       </c>
-      <c r="C518" s="2" t="s">
+      <c r="C518" s="49" t="s">
         <v>1066</v>
       </c>
-      <c r="D518" s="2" t="s">
+      <c r="D518" s="49" t="s">
         <v>1031</v>
       </c>
-      <c r="E518" s="2" t="s">
+      <c r="E518" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F518" s="5">
+      <c r="F518" s="50">
         <v>50616</v>
       </c>
-      <c r="G518" s="2" t="s">
+      <c r="G518" s="49" t="s">
         <v>1105</v>
       </c>
-      <c r="H518" s="5">
+      <c r="H518" s="50">
         <v>0</v>
       </c>
-      <c r="I518" s="26">
+      <c r="I518" s="51">
         <v>45967</v>
       </c>
-      <c r="J518" s="26">
+      <c r="J518" s="51">
         <v>46073</v>
       </c>
-      <c r="K518" s="2" t="s">
+      <c r="K518" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="L518" s="2" t="s">
+      <c r="L518" s="49" t="s">
         <v>37</v>
       </c>
       <c r="M518" s="2"/>
@@ -31232,40 +31285,40 @@
       <c r="Z518" s="2"/>
     </row>
     <row r="519" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A519" s="7" t="s">
+      <c r="A519" s="48" t="s">
         <v>1106</v>
       </c>
-      <c r="B519" s="2" t="s">
+      <c r="B519" s="49" t="s">
         <v>1107</v>
       </c>
-      <c r="C519" s="2" t="s">
+      <c r="C519" s="49" t="s">
         <v>427</v>
       </c>
-      <c r="D519" s="2" t="s">
+      <c r="D519" s="49" t="s">
         <v>332</v>
       </c>
-      <c r="E519" s="2" t="s">
+      <c r="E519" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F519" s="5">
+      <c r="F519" s="50">
         <v>50703</v>
       </c>
-      <c r="G519" s="2" t="s">
+      <c r="G519" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H519" s="5">
+      <c r="H519" s="50">
         <v>12</v>
       </c>
-      <c r="I519" s="26">
+      <c r="I519" s="51">
         <v>45960</v>
       </c>
-      <c r="J519" s="26">
+      <c r="J519" s="51">
         <v>45988</v>
       </c>
-      <c r="K519" s="2" t="s">
+      <c r="K519" s="49" t="s">
         <v>391</v>
       </c>
-      <c r="L519" s="2" t="s">
+      <c r="L519" s="49" t="s">
         <v>37</v>
       </c>
       <c r="M519" s="2"/>
@@ -31285,40 +31338,40 @@
       <c r="AD519"/>
     </row>
     <row r="520" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A520" s="7" t="s">
+      <c r="A520" s="48" t="s">
         <v>1108</v>
       </c>
-      <c r="B520" s="2" t="s">
+      <c r="B520" s="49" t="s">
         <v>1109</v>
       </c>
-      <c r="C520" s="2" t="s">
+      <c r="C520" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="D520" s="2" t="s">
+      <c r="D520" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="E520" s="2" t="s">
+      <c r="E520" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F520" s="5">
+      <c r="F520" s="50">
         <v>52404</v>
       </c>
-      <c r="G520" s="2" t="s">
+      <c r="G520" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="H520" s="5">
+      <c r="H520" s="50">
         <v>34</v>
       </c>
-      <c r="I520" s="26">
+      <c r="I520" s="51">
         <v>45972</v>
       </c>
-      <c r="J520" s="26">
+      <c r="J520" s="51">
         <v>46022</v>
       </c>
-      <c r="K520" s="2" t="s">
+      <c r="K520" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="L520" s="2" t="s">
+      <c r="L520" s="49" t="s">
         <v>37</v>
       </c>
       <c r="M520" s="2"/>
@@ -31337,40 +31390,40 @@
       <c r="Z520" s="2"/>
     </row>
     <row r="521" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A521" s="7" t="s">
+      <c r="A521" s="48" t="s">
         <v>1110</v>
       </c>
-      <c r="B521" s="2" t="s">
+      <c r="B521" s="49" t="s">
         <v>1111</v>
       </c>
-      <c r="C521" s="2" t="s">
+      <c r="C521" s="49" t="s">
         <v>364</v>
       </c>
-      <c r="D521" s="2" t="s">
+      <c r="D521" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="E521" s="2" t="s">
+      <c r="E521" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F521" s="5">
+      <c r="F521" s="50">
         <v>52317</v>
       </c>
-      <c r="G521" s="2" t="s">
+      <c r="G521" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H521" s="5">
+      <c r="H521" s="50">
         <v>70</v>
       </c>
-      <c r="I521" s="26">
+      <c r="I521" s="51">
         <v>45975</v>
       </c>
-      <c r="J521" s="26">
+      <c r="J521" s="51">
         <v>46009</v>
       </c>
-      <c r="K521" s="2" t="s">
+      <c r="K521" s="49" t="s">
         <v>366</v>
       </c>
-      <c r="L521" s="2" t="s">
+      <c r="L521" s="49" t="s">
         <v>313</v>
       </c>
       <c r="M521" s="2"/>
@@ -31389,40 +31442,40 @@
       <c r="Z521" s="2"/>
     </row>
     <row r="522" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A522" s="7" t="s">
+      <c r="A522" s="48" t="s">
         <v>1112</v>
       </c>
-      <c r="B522" s="2" t="s">
+      <c r="B522" s="49" t="s">
         <v>1113</v>
       </c>
-      <c r="C522" s="2" t="s">
+      <c r="C522" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="D522" s="2" t="s">
+      <c r="D522" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="E522" s="2" t="s">
+      <c r="E522" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F522" s="5">
+      <c r="F522" s="50">
         <v>52816</v>
       </c>
-      <c r="G522" s="2" t="s">
+      <c r="G522" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H522" s="5">
+      <c r="H522" s="50">
         <v>28</v>
       </c>
-      <c r="I522" s="26">
+      <c r="I522" s="51">
         <v>45979</v>
       </c>
-      <c r="J522" s="26">
+      <c r="J522" s="51">
         <v>46010</v>
       </c>
-      <c r="K522" s="2" t="s">
+      <c r="K522" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="L522" s="2" t="s">
+      <c r="L522" s="49" t="s">
         <v>313</v>
       </c>
       <c r="M522" s="2"/>
@@ -31441,40 +31494,40 @@
       <c r="Z522" s="2"/>
     </row>
     <row r="523" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A523" s="7" t="s">
+      <c r="A523" s="48" t="s">
         <v>1114</v>
       </c>
-      <c r="B523" s="2" t="s">
+      <c r="B523" s="49" t="s">
         <v>1115</v>
       </c>
-      <c r="C523" s="2" t="s">
+      <c r="C523" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="D523" s="2" t="s">
+      <c r="D523" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="E523" s="2" t="s">
+      <c r="E523" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F523" s="5">
+      <c r="F523" s="50">
         <v>50321</v>
       </c>
-      <c r="G523" s="2" t="s">
+      <c r="G523" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="H523" s="5">
+      <c r="H523" s="50">
         <v>90</v>
       </c>
-      <c r="I523" s="26">
+      <c r="I523" s="51">
         <v>45971</v>
       </c>
-      <c r="J523" s="26">
+      <c r="J523" s="51">
         <v>46008</v>
       </c>
-      <c r="K523" s="2" t="s">
+      <c r="K523" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="L523" s="2" t="s">
+      <c r="L523" s="49" t="s">
         <v>45</v>
       </c>
       <c r="M523" s="2"/>
@@ -31493,40 +31546,40 @@
       <c r="Z523" s="2"/>
     </row>
     <row r="524" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A524" s="7" t="s">
+      <c r="A524" s="48" t="s">
         <v>1112</v>
       </c>
-      <c r="B524" s="2" t="s">
+      <c r="B524" s="49" t="s">
         <v>1113</v>
       </c>
-      <c r="C524" s="2" t="s">
+      <c r="C524" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="D524" s="2" t="s">
+      <c r="D524" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="E524" s="2" t="s">
+      <c r="E524" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F524" s="5">
+      <c r="F524" s="50">
         <v>52816</v>
       </c>
-      <c r="G524" s="2" t="s">
+      <c r="G524" s="49" t="s">
         <v>1105</v>
       </c>
-      <c r="H524" s="5">
+      <c r="H524" s="50">
         <v>2</v>
       </c>
-      <c r="I524" s="26">
+      <c r="I524" s="51">
         <v>45986</v>
       </c>
-      <c r="J524" s="26">
+      <c r="J524" s="51">
         <v>45987</v>
       </c>
-      <c r="K524" s="2" t="s">
+      <c r="K524" s="49" t="s">
         <v>28</v>
       </c>
-      <c r="L524" s="2" t="s">
+      <c r="L524" s="49" t="s">
         <v>313</v>
       </c>
       <c r="M524" s="2"/>
@@ -31545,40 +31598,40 @@
       <c r="Z524" s="2"/>
     </row>
     <row r="525" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A525" s="7" t="s">
+      <c r="A525" s="48" t="s">
         <v>169</v>
       </c>
-      <c r="B525" s="2" t="s">
+      <c r="B525" s="49" t="s">
         <v>481</v>
       </c>
-      <c r="C525" s="2" t="s">
+      <c r="C525" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="D525" s="2" t="s">
+      <c r="D525" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="E525" s="2" t="s">
+      <c r="E525" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F525" s="5">
+      <c r="F525" s="50">
         <v>50266</v>
       </c>
-      <c r="G525" s="2" t="s">
+      <c r="G525" s="49" t="s">
         <v>732</v>
       </c>
-      <c r="H525" s="5">
+      <c r="H525" s="50">
         <v>14</v>
       </c>
-      <c r="I525" s="26">
+      <c r="I525" s="51">
         <v>45986</v>
       </c>
-      <c r="J525" s="26">
+      <c r="J525" s="51">
         <v>46045</v>
       </c>
-      <c r="K525" s="2" t="s">
+      <c r="K525" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="L525" s="2" t="s">
+      <c r="L525" s="49" t="s">
         <v>107</v>
       </c>
       <c r="M525" s="2"/>
@@ -31597,40 +31650,40 @@
       <c r="Z525" s="2"/>
     </row>
     <row r="526" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A526" s="7" t="s">
+      <c r="A526" s="48" t="s">
         <v>1116</v>
       </c>
-      <c r="B526" s="2" t="s">
+      <c r="B526" s="49" t="s">
         <v>1117</v>
       </c>
-      <c r="C526" s="2" t="s">
+      <c r="C526" s="49" t="s">
         <v>1118</v>
       </c>
-      <c r="D526" s="2" t="s">
+      <c r="D526" s="49" t="s">
         <v>256</v>
       </c>
-      <c r="E526" s="2" t="s">
+      <c r="E526" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F526" s="5">
+      <c r="F526" s="50">
         <v>50217</v>
       </c>
-      <c r="G526" s="2" t="s">
+      <c r="G526" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H526" s="5">
+      <c r="H526" s="50">
         <v>62</v>
       </c>
-      <c r="I526" s="26">
+      <c r="I526" s="51">
         <v>45992</v>
       </c>
-      <c r="J526" s="26">
+      <c r="J526" s="51">
         <v>46022</v>
       </c>
-      <c r="K526" s="2" t="s">
+      <c r="K526" s="49" t="s">
         <v>533</v>
       </c>
-      <c r="L526" s="2" t="s">
+      <c r="L526" s="49" t="s">
         <v>313</v>
       </c>
       <c r="M526" s="2"/>
@@ -31649,40 +31702,40 @@
       <c r="Z526" s="2"/>
     </row>
     <row r="527" spans="1:34" ht="14.25" customHeight="1">
-      <c r="A527" s="7" t="s">
+      <c r="A527" s="48" t="s">
         <v>1119</v>
       </c>
-      <c r="B527" s="2" t="s">
+      <c r="B527" s="49" t="s">
         <v>1120</v>
       </c>
-      <c r="C527" s="2" t="s">
+      <c r="C527" s="49" t="s">
         <v>1121</v>
       </c>
-      <c r="D527" s="2" t="s">
+      <c r="D527" s="49" t="s">
         <v>232</v>
       </c>
-      <c r="E527" s="2" t="s">
+      <c r="E527" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F527" s="5">
+      <c r="F527" s="50">
         <v>51510</v>
       </c>
-      <c r="G527" s="2" t="s">
+      <c r="G527" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="H527" s="5">
+      <c r="H527" s="50">
         <v>26</v>
       </c>
-      <c r="I527" s="26">
+      <c r="I527" s="51">
         <v>45992</v>
       </c>
-      <c r="J527" s="26">
+      <c r="J527" s="51">
         <v>46052</v>
       </c>
-      <c r="K527" s="2" t="s">
+      <c r="K527" s="49" t="s">
         <v>533</v>
       </c>
-      <c r="L527" s="2" t="s">
+      <c r="L527" s="49" t="s">
         <v>503</v>
       </c>
       <c r="M527" s="18"/>
@@ -31708,101 +31761,101 @@
       <c r="AG527"/>
       <c r="AH527"/>
     </row>
-    <row r="528" spans="1:34" s="47" customFormat="1" ht="27.75" customHeight="1">
-      <c r="A528" s="43" t="s">
+    <row r="528" spans="1:34" s="43" customFormat="1" ht="27.75" customHeight="1">
+      <c r="A528" s="52" t="s">
         <v>1122</v>
       </c>
-      <c r="B528" s="41" t="s">
+      <c r="B528" s="53" t="s">
         <v>1120</v>
       </c>
-      <c r="C528" s="41" t="s">
+      <c r="C528" s="53" t="s">
         <v>1121</v>
       </c>
-      <c r="D528" s="41" t="s">
+      <c r="D528" s="53" t="s">
         <v>232</v>
       </c>
-      <c r="E528" s="41" t="s">
+      <c r="E528" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="F528" s="41">
+      <c r="F528" s="53">
         <v>51510</v>
       </c>
-      <c r="G528" s="41" t="s">
+      <c r="G528" s="53" t="s">
         <v>52</v>
       </c>
-      <c r="H528" s="45">
+      <c r="H528" s="54">
         <v>42</v>
       </c>
-      <c r="I528" s="42">
+      <c r="I528" s="55">
         <v>45992</v>
       </c>
-      <c r="J528" s="42">
+      <c r="J528" s="55">
         <v>46052</v>
       </c>
-      <c r="K528" s="41" t="s">
+      <c r="K528" s="53" t="s">
         <v>533</v>
       </c>
-      <c r="L528" s="41" t="s">
+      <c r="L528" s="53" t="s">
         <v>177</v>
       </c>
-      <c r="M528" s="44"/>
-      <c r="N528" s="44"/>
-      <c r="O528" s="44"/>
-      <c r="P528" s="44"/>
-      <c r="Q528" s="44"/>
-      <c r="R528" s="44"/>
-      <c r="S528" s="44"/>
-      <c r="T528" s="44"/>
-      <c r="U528" s="44"/>
-      <c r="V528" s="44"/>
-      <c r="W528" s="44"/>
-      <c r="X528" s="44"/>
-      <c r="Y528" s="44"/>
-      <c r="Z528" s="44"/>
-      <c r="AA528" s="46"/>
-      <c r="AB528" s="46"/>
-      <c r="AC528" s="46"/>
-      <c r="AD528" s="46"/>
-      <c r="AE528" s="46"/>
-      <c r="AF528" s="46"/>
-      <c r="AG528" s="46"/>
-      <c r="AH528" s="46"/>
+      <c r="M528" s="41"/>
+      <c r="N528" s="41"/>
+      <c r="O528" s="41"/>
+      <c r="P528" s="41"/>
+      <c r="Q528" s="41"/>
+      <c r="R528" s="41"/>
+      <c r="S528" s="41"/>
+      <c r="T528" s="41"/>
+      <c r="U528" s="41"/>
+      <c r="V528" s="41"/>
+      <c r="W528" s="41"/>
+      <c r="X528" s="41"/>
+      <c r="Y528" s="41"/>
+      <c r="Z528" s="41"/>
+      <c r="AA528" s="42"/>
+      <c r="AB528" s="42"/>
+      <c r="AC528" s="42"/>
+      <c r="AD528" s="42"/>
+      <c r="AE528" s="42"/>
+      <c r="AF528" s="42"/>
+      <c r="AG528" s="42"/>
+      <c r="AH528" s="42"/>
     </row>
     <row r="529" spans="1:37" ht="30" customHeight="1">
-      <c r="A529" s="7" t="s">
+      <c r="A529" s="48" t="s">
         <v>1123</v>
       </c>
-      <c r="B529" s="41" t="s">
+      <c r="B529" s="53" t="s">
         <v>1124</v>
       </c>
-      <c r="C529" s="41" t="s">
+      <c r="C529" s="53" t="s">
         <v>84</v>
       </c>
-      <c r="D529" s="41" t="s">
+      <c r="D529" s="53" t="s">
         <v>60</v>
       </c>
-      <c r="E529" s="41" t="s">
+      <c r="E529" s="53" t="s">
         <v>34</v>
       </c>
-      <c r="F529" s="41">
+      <c r="F529" s="53">
         <v>52404</v>
       </c>
-      <c r="G529" s="41" t="s">
+      <c r="G529" s="53" t="s">
         <v>42</v>
       </c>
-      <c r="H529" s="45">
+      <c r="H529" s="54">
         <v>30</v>
       </c>
-      <c r="I529" s="42">
+      <c r="I529" s="55">
         <v>45994</v>
       </c>
-      <c r="J529" s="42">
+      <c r="J529" s="55">
         <v>46054</v>
       </c>
-      <c r="K529" s="41" t="s">
+      <c r="K529" s="53" t="s">
         <v>366</v>
       </c>
-      <c r="L529" s="41" t="s">
+      <c r="L529" s="53" t="s">
         <v>177</v>
       </c>
       <c r="M529" s="2"/>
@@ -31821,40 +31874,40 @@
       <c r="Z529" s="2"/>
     </row>
     <row r="530" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A530" s="7" t="s">
+      <c r="A530" s="48" t="s">
         <v>169</v>
       </c>
-      <c r="B530" s="2" t="s">
+      <c r="B530" s="49" t="s">
         <v>481</v>
       </c>
-      <c r="C530" s="2" t="s">
+      <c r="C530" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="D530" s="2" t="s">
+      <c r="D530" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="E530" s="2" t="s">
+      <c r="E530" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F530" s="5">
+      <c r="F530" s="50">
         <v>50266</v>
       </c>
-      <c r="G530" s="2" t="s">
+      <c r="G530" s="49" t="s">
         <v>732</v>
       </c>
-      <c r="H530" s="5">
+      <c r="H530" s="50">
         <v>25</v>
       </c>
-      <c r="I530" s="26">
+      <c r="I530" s="51">
         <v>46000</v>
       </c>
-      <c r="J530" s="26">
+      <c r="J530" s="51">
         <v>46059</v>
       </c>
-      <c r="K530" s="2" t="s">
+      <c r="K530" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="L530" s="2" t="s">
+      <c r="L530" s="49" t="s">
         <v>107</v>
       </c>
       <c r="M530" s="2"/>
@@ -31873,40 +31926,40 @@
       <c r="Z530" s="2"/>
     </row>
     <row r="531" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A531" s="7" t="s">
+      <c r="A531" s="48" t="s">
         <v>1125</v>
       </c>
-      <c r="B531" s="2" t="s">
+      <c r="B531" s="49" t="s">
         <v>1126</v>
       </c>
-      <c r="C531" s="2" t="s">
+      <c r="C531" s="49" t="s">
         <v>1127</v>
       </c>
-      <c r="D531" s="2" t="s">
+      <c r="D531" s="49" t="s">
         <v>730</v>
       </c>
-      <c r="E531" s="2" t="s">
+      <c r="E531" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F531" s="5">
+      <c r="F531" s="50">
         <v>51041</v>
       </c>
-      <c r="G531" s="2" t="s">
+      <c r="G531" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H531" s="5">
+      <c r="H531" s="50">
         <v>33</v>
       </c>
-      <c r="I531" s="26">
+      <c r="I531" s="51">
         <v>46001</v>
       </c>
-      <c r="J531" s="26">
+      <c r="J531" s="51">
         <v>46059</v>
       </c>
-      <c r="K531" s="2" t="s">
+      <c r="K531" s="49" t="s">
         <v>533</v>
       </c>
-      <c r="L531" s="2" t="s">
+      <c r="L531" s="49" t="s">
         <v>313</v>
       </c>
       <c r="M531" s="18"/>
@@ -31935,40 +31988,40 @@
       <c r="AJ531"/>
     </row>
     <row r="532" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A532" s="7" t="s">
+      <c r="A532" s="48" t="s">
         <v>1128</v>
       </c>
-      <c r="B532" s="2" t="s">
+      <c r="B532" s="49" t="s">
         <v>1129</v>
       </c>
-      <c r="C532" s="2" t="s">
+      <c r="C532" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="D532" s="2" t="s">
+      <c r="D532" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="E532" s="2" t="s">
+      <c r="E532" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F532" s="5">
+      <c r="F532" s="50">
         <v>52241</v>
       </c>
-      <c r="G532" s="2" t="s">
+      <c r="G532" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="H532" s="5">
+      <c r="H532" s="50">
         <v>61</v>
       </c>
-      <c r="I532" s="26">
+      <c r="I532" s="51">
         <v>46003</v>
       </c>
-      <c r="J532" s="26">
+      <c r="J532" s="51">
         <v>46003</v>
       </c>
-      <c r="K532" s="2" t="s">
+      <c r="K532" s="49" t="s">
         <v>366</v>
       </c>
-      <c r="L532" s="2" t="s">
+      <c r="L532" s="49" t="s">
         <v>313</v>
       </c>
       <c r="M532" s="2"/>
@@ -31987,40 +32040,40 @@
       <c r="Z532" s="2"/>
     </row>
     <row r="533" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A533" s="7" t="s">
+      <c r="A533" s="48" t="s">
         <v>1130</v>
       </c>
-      <c r="B533" s="2" t="s">
+      <c r="B533" s="49" t="s">
         <v>1131</v>
       </c>
-      <c r="C533" s="2" t="s">
+      <c r="C533" s="49" t="s">
         <v>1132</v>
       </c>
-      <c r="D533" s="2" t="s">
+      <c r="D533" s="49" t="s">
         <v>212</v>
       </c>
-      <c r="E533" s="2" t="s">
+      <c r="E533" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F533" s="5">
+      <c r="F533" s="50">
         <v>50156</v>
       </c>
-      <c r="G533" s="2" t="s">
+      <c r="G533" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H533" s="5">
+      <c r="H533" s="50">
         <v>18</v>
       </c>
-      <c r="I533" s="26">
+      <c r="I533" s="51">
         <v>46003</v>
       </c>
-      <c r="J533" s="26">
+      <c r="J533" s="51">
         <v>46006</v>
       </c>
-      <c r="K533" s="2" t="s">
+      <c r="K533" s="49" t="s">
         <v>379</v>
       </c>
-      <c r="L533" s="2" t="s">
+      <c r="L533" s="49" t="s">
         <v>313</v>
       </c>
       <c r="M533" s="2"/>
@@ -32039,40 +32092,40 @@
       <c r="Z533" s="2"/>
     </row>
     <row r="534" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A534" s="7" t="s">
+      <c r="A534" s="48" t="s">
         <v>1133</v>
       </c>
-      <c r="B534" s="2" t="s">
+      <c r="B534" s="49" t="s">
         <v>1134</v>
       </c>
-      <c r="C534" s="2" t="s">
+      <c r="C534" s="49" t="s">
         <v>175</v>
       </c>
-      <c r="D534" s="2" t="s">
+      <c r="D534" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="E534" s="2" t="s">
+      <c r="E534" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F534" s="5">
+      <c r="F534" s="50">
         <v>50021</v>
       </c>
-      <c r="G534" s="2" t="s">
+      <c r="G534" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="H534" s="5">
+      <c r="H534" s="50">
         <v>29</v>
       </c>
-      <c r="I534" s="26">
+      <c r="I534" s="51">
         <v>46014</v>
       </c>
-      <c r="J534" s="26">
+      <c r="J534" s="51">
         <v>46014</v>
       </c>
-      <c r="K534" s="2" t="s">
+      <c r="K534" s="49" t="s">
         <v>379</v>
       </c>
-      <c r="L534" s="2" t="s">
+      <c r="L534" s="49" t="s">
         <v>613</v>
       </c>
       <c r="M534" s="1"/>
@@ -32089,53 +32142,53 @@
       <c r="X534" s="1"/>
       <c r="Y534" s="1"/>
       <c r="Z534" s="1"/>
-      <c r="AA534" s="48"/>
-      <c r="AB534" s="48"/>
-      <c r="AC534" s="48"/>
-      <c r="AD534" s="48"/>
-      <c r="AE534" s="48"/>
-      <c r="AF534" s="48"/>
-      <c r="AG534" s="48"/>
-      <c r="AH534" s="48"/>
-      <c r="AI534" s="48"/>
-      <c r="AJ534" s="48"/>
-      <c r="AK534" s="48"/>
+      <c r="AA534" s="44"/>
+      <c r="AB534" s="44"/>
+      <c r="AC534" s="44"/>
+      <c r="AD534" s="44"/>
+      <c r="AE534" s="44"/>
+      <c r="AF534" s="44"/>
+      <c r="AG534" s="44"/>
+      <c r="AH534" s="44"/>
+      <c r="AI534" s="44"/>
+      <c r="AJ534" s="44"/>
+      <c r="AK534" s="44"/>
     </row>
     <row r="535" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A535" s="7" t="s">
+      <c r="A535" s="48" t="s">
         <v>1135</v>
       </c>
-      <c r="B535" s="2" t="s">
+      <c r="B535" s="49" t="s">
         <v>1136</v>
       </c>
-      <c r="C535" s="2" t="s">
+      <c r="C535" s="49" t="s">
         <v>1090</v>
       </c>
-      <c r="D535" s="2" t="s">
+      <c r="D535" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="E535" s="2" t="s">
+      <c r="E535" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F535" s="5">
+      <c r="F535" s="50">
         <v>52601</v>
       </c>
-      <c r="G535" s="2" t="s">
+      <c r="G535" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H535" s="5">
+      <c r="H535" s="50">
         <v>7</v>
       </c>
-      <c r="I535" s="26">
+      <c r="I535" s="51">
         <v>46042</v>
       </c>
-      <c r="J535" s="26" t="s">
+      <c r="J535" s="51" t="s">
         <v>1137</v>
       </c>
-      <c r="K535" s="2" t="s">
+      <c r="K535" s="49" t="s">
         <v>417</v>
       </c>
-      <c r="L535" s="2" t="s">
+      <c r="L535" s="49" t="s">
         <v>313</v>
       </c>
       <c r="M535" s="2"/>
@@ -32154,40 +32207,40 @@
       <c r="Z535" s="2"/>
     </row>
     <row r="536" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A536" s="7" t="s">
+      <c r="A536" s="48" t="s">
         <v>1135</v>
       </c>
-      <c r="B536" s="2" t="s">
+      <c r="B536" s="49" t="s">
         <v>1136</v>
       </c>
-      <c r="C536" s="2" t="s">
+      <c r="C536" s="49" t="s">
         <v>1090</v>
       </c>
-      <c r="D536" s="2" t="s">
+      <c r="D536" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="E536" s="2" t="s">
+      <c r="E536" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F536" s="5">
+      <c r="F536" s="50">
         <v>52601</v>
       </c>
-      <c r="G536" s="2" t="s">
+      <c r="G536" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H536" s="5">
+      <c r="H536" s="50">
         <v>4</v>
       </c>
-      <c r="I536" s="26">
+      <c r="I536" s="51">
         <v>46042</v>
       </c>
-      <c r="J536" s="26">
+      <c r="J536" s="51">
         <v>46113</v>
       </c>
-      <c r="K536" s="2" t="s">
+      <c r="K536" s="49" t="s">
         <v>417</v>
       </c>
-      <c r="L536" s="2" t="s">
+      <c r="L536" s="49" t="s">
         <v>313</v>
       </c>
       <c r="M536" s="2"/>
@@ -32206,40 +32259,40 @@
       <c r="Z536" s="2"/>
     </row>
     <row r="537" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A537" s="7" t="s">
+      <c r="A537" s="48" t="s">
         <v>1135</v>
       </c>
-      <c r="B537" s="2" t="s">
+      <c r="B537" s="49" t="s">
         <v>1136</v>
       </c>
-      <c r="C537" s="2" t="s">
+      <c r="C537" s="49" t="s">
         <v>1090</v>
       </c>
-      <c r="D537" s="2" t="s">
+      <c r="D537" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="E537" s="2" t="s">
+      <c r="E537" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F537" s="5">
+      <c r="F537" s="50">
         <v>52601</v>
       </c>
-      <c r="G537" s="2" t="s">
+      <c r="G537" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H537" s="5">
+      <c r="H537" s="50">
         <v>52</v>
       </c>
-      <c r="I537" s="26">
+      <c r="I537" s="51">
         <v>46042</v>
       </c>
-      <c r="J537" s="26">
+      <c r="J537" s="51">
         <v>46114</v>
       </c>
-      <c r="K537" s="2" t="s">
+      <c r="K537" s="49" t="s">
         <v>417</v>
       </c>
-      <c r="L537" s="2" t="s">
+      <c r="L537" s="49" t="s">
         <v>313</v>
       </c>
       <c r="M537" s="2"/>
@@ -32258,40 +32311,40 @@
       <c r="Z537" s="2"/>
     </row>
     <row r="538" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A538" s="7" t="s">
+      <c r="A538" s="48" t="s">
         <v>1135</v>
       </c>
-      <c r="B538" s="2" t="s">
+      <c r="B538" s="49" t="s">
         <v>1136</v>
       </c>
-      <c r="C538" s="2" t="s">
+      <c r="C538" s="49" t="s">
         <v>1090</v>
       </c>
-      <c r="D538" s="2" t="s">
+      <c r="D538" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="E538" s="2" t="s">
+      <c r="E538" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F538" s="5">
+      <c r="F538" s="50">
         <v>52601</v>
       </c>
-      <c r="G538" s="2" t="s">
+      <c r="G538" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H538" s="5">
+      <c r="H538" s="50">
         <v>18</v>
       </c>
-      <c r="I538" s="26">
+      <c r="I538" s="51">
         <v>46042</v>
       </c>
-      <c r="J538" s="26">
+      <c r="J538" s="51">
         <v>46120</v>
       </c>
-      <c r="K538" s="2" t="s">
+      <c r="K538" s="49" t="s">
         <v>417</v>
       </c>
-      <c r="L538" s="2" t="s">
+      <c r="L538" s="49" t="s">
         <v>313</v>
       </c>
       <c r="M538" s="2"/>
@@ -32310,40 +32363,40 @@
       <c r="Z538" s="2"/>
     </row>
     <row r="539" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A539" s="7" t="s">
+      <c r="A539" s="48" t="s">
         <v>1135</v>
       </c>
-      <c r="B539" s="2" t="s">
+      <c r="B539" s="49" t="s">
         <v>1136</v>
       </c>
-      <c r="C539" s="2" t="s">
+      <c r="C539" s="49" t="s">
         <v>1090</v>
       </c>
-      <c r="D539" s="2" t="s">
+      <c r="D539" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="E539" s="2" t="s">
+      <c r="E539" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F539" s="5">
+      <c r="F539" s="50">
         <v>52601</v>
       </c>
-      <c r="G539" s="2" t="s">
+      <c r="G539" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H539" s="5">
+      <c r="H539" s="50">
         <v>9</v>
       </c>
-      <c r="I539" s="26">
+      <c r="I539" s="51">
         <v>46042</v>
       </c>
-      <c r="J539" s="26">
+      <c r="J539" s="51">
         <v>46121</v>
       </c>
-      <c r="K539" s="2" t="s">
+      <c r="K539" s="49" t="s">
         <v>417</v>
       </c>
-      <c r="L539" s="2" t="s">
+      <c r="L539" s="49" t="s">
         <v>313</v>
       </c>
       <c r="M539" s="2"/>
@@ -32362,40 +32415,40 @@
       <c r="Z539" s="2"/>
     </row>
     <row r="540" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A540" s="7" t="s">
+      <c r="A540" s="48" t="s">
         <v>1135</v>
       </c>
-      <c r="B540" s="2" t="s">
+      <c r="B540" s="49" t="s">
         <v>1136</v>
       </c>
-      <c r="C540" s="2" t="s">
+      <c r="C540" s="49" t="s">
         <v>1090</v>
       </c>
-      <c r="D540" s="2" t="s">
+      <c r="D540" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="E540" s="2" t="s">
+      <c r="E540" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F540" s="5">
+      <c r="F540" s="50">
         <v>52601</v>
       </c>
-      <c r="G540" s="2" t="s">
+      <c r="G540" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H540" s="5">
+      <c r="H540" s="50">
         <v>21</v>
       </c>
-      <c r="I540" s="26">
+      <c r="I540" s="51">
         <v>46042</v>
       </c>
-      <c r="J540" s="26">
+      <c r="J540" s="51">
         <v>46122</v>
       </c>
-      <c r="K540" s="2" t="s">
+      <c r="K540" s="49" t="s">
         <v>417</v>
       </c>
-      <c r="L540" s="2" t="s">
+      <c r="L540" s="49" t="s">
         <v>313</v>
       </c>
       <c r="M540" s="2"/>
@@ -32414,40 +32467,40 @@
       <c r="Z540" s="2"/>
     </row>
     <row r="541" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A541" s="7" t="s">
+      <c r="A541" s="48" t="s">
         <v>1135</v>
       </c>
-      <c r="B541" s="2" t="s">
+      <c r="B541" s="49" t="s">
         <v>1136</v>
       </c>
-      <c r="C541" s="2" t="s">
+      <c r="C541" s="49" t="s">
         <v>1090</v>
       </c>
-      <c r="D541" s="2" t="s">
+      <c r="D541" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="E541" s="2" t="s">
+      <c r="E541" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F541" s="5">
+      <c r="F541" s="50">
         <v>52601</v>
       </c>
-      <c r="G541" s="2" t="s">
+      <c r="G541" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H541" s="5">
+      <c r="H541" s="50">
         <v>16</v>
       </c>
-      <c r="I541" s="26">
+      <c r="I541" s="51">
         <v>46042</v>
       </c>
-      <c r="J541" s="26">
+      <c r="J541" s="51">
         <v>46125</v>
       </c>
-      <c r="K541" s="2" t="s">
+      <c r="K541" s="49" t="s">
         <v>417</v>
       </c>
-      <c r="L541" s="2" t="s">
+      <c r="L541" s="49" t="s">
         <v>313</v>
       </c>
       <c r="M541" s="2"/>
@@ -32466,40 +32519,40 @@
       <c r="Z541" s="2"/>
     </row>
     <row r="542" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A542" s="7" t="s">
+      <c r="A542" s="48" t="s">
         <v>1135</v>
       </c>
-      <c r="B542" s="2" t="s">
+      <c r="B542" s="49" t="s">
         <v>1136</v>
       </c>
-      <c r="C542" s="2" t="s">
+      <c r="C542" s="49" t="s">
         <v>1090</v>
       </c>
-      <c r="D542" s="2" t="s">
+      <c r="D542" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="E542" s="2" t="s">
+      <c r="E542" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F542" s="5">
+      <c r="F542" s="50">
         <v>52601</v>
       </c>
-      <c r="G542" s="2" t="s">
+      <c r="G542" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H542" s="5">
+      <c r="H542" s="50">
         <v>16</v>
       </c>
-      <c r="I542" s="26">
+      <c r="I542" s="51">
         <v>46042</v>
       </c>
-      <c r="J542" s="26">
+      <c r="J542" s="51">
         <v>46142</v>
       </c>
-      <c r="K542" s="2" t="s">
+      <c r="K542" s="49" t="s">
         <v>417</v>
       </c>
-      <c r="L542" s="2" t="s">
+      <c r="L542" s="49" t="s">
         <v>313</v>
       </c>
       <c r="M542" s="2"/>
@@ -32518,40 +32571,40 @@
       <c r="Z542" s="2"/>
     </row>
     <row r="543" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A543" s="7" t="s">
+      <c r="A543" s="48" t="s">
         <v>1135</v>
       </c>
-      <c r="B543" s="2" t="s">
+      <c r="B543" s="49" t="s">
         <v>1136</v>
       </c>
-      <c r="C543" s="2" t="s">
+      <c r="C543" s="49" t="s">
         <v>1090</v>
       </c>
-      <c r="D543" s="2" t="s">
+      <c r="D543" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="E543" s="2" t="s">
+      <c r="E543" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F543" s="5">
+      <c r="F543" s="50">
         <v>52601</v>
       </c>
-      <c r="G543" s="2" t="s">
+      <c r="G543" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H543" s="5">
+      <c r="H543" s="50">
         <v>42</v>
       </c>
-      <c r="I543" s="26">
+      <c r="I543" s="51">
         <v>46042</v>
       </c>
-      <c r="J543" s="26">
+      <c r="J543" s="51">
         <v>46143</v>
       </c>
-      <c r="K543" s="2" t="s">
+      <c r="K543" s="49" t="s">
         <v>417</v>
       </c>
-      <c r="L543" s="2" t="s">
+      <c r="L543" s="49" t="s">
         <v>313</v>
       </c>
       <c r="M543" s="2"/>
@@ -32570,40 +32623,40 @@
       <c r="Z543" s="2"/>
     </row>
     <row r="544" spans="1:37" ht="14.25" customHeight="1">
-      <c r="A544" s="52" t="s">
+      <c r="A544" s="56" t="s">
         <v>1135</v>
       </c>
-      <c r="B544" s="53" t="s">
+      <c r="B544" s="57" t="s">
         <v>1136</v>
       </c>
-      <c r="C544" s="53" t="s">
+      <c r="C544" s="57" t="s">
         <v>1090</v>
       </c>
-      <c r="D544" s="53" t="s">
+      <c r="D544" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="E544" s="53" t="s">
+      <c r="E544" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="F544" s="54">
+      <c r="F544" s="58">
         <v>52601</v>
       </c>
-      <c r="G544" s="53" t="s">
+      <c r="G544" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="H544" s="54">
+      <c r="H544" s="58">
         <v>24</v>
       </c>
-      <c r="I544" s="55">
+      <c r="I544" s="59">
         <v>46042</v>
       </c>
-      <c r="J544" s="55">
+      <c r="J544" s="59">
         <v>46171</v>
       </c>
-      <c r="K544" s="53" t="s">
+      <c r="K544" s="57" t="s">
         <v>417</v>
       </c>
-      <c r="L544" s="53" t="s">
+      <c r="L544" s="57" t="s">
         <v>313</v>
       </c>
       <c r="M544" s="2"/>
@@ -32658,32 +32711,32 @@
       <c r="L545" s="57" t="s">
         <v>107</v>
       </c>
-      <c r="M545" s="49"/>
-      <c r="N545" s="49"/>
-      <c r="O545" s="49"/>
-      <c r="P545" s="49"/>
-      <c r="Q545" s="49"/>
-      <c r="R545" s="49"/>
-      <c r="S545" s="49"/>
-      <c r="T545" s="49"/>
-      <c r="U545" s="49"/>
-      <c r="V545" s="49"/>
-      <c r="W545" s="49"/>
-      <c r="X545" s="49"/>
-      <c r="Y545" s="49"/>
-      <c r="Z545" s="49"/>
-      <c r="AA545" s="50"/>
-      <c r="AB545" s="50"/>
-      <c r="AC545" s="50"/>
-      <c r="AD545" s="50"/>
-      <c r="AE545" s="50"/>
-      <c r="AF545" s="50"/>
-      <c r="AG545" s="50"/>
-      <c r="AH545" s="50"/>
-      <c r="AI545" s="51"/>
-      <c r="AJ545" s="51"/>
-      <c r="AK545" s="51"/>
-      <c r="AL545" s="51"/>
+      <c r="M545" s="45"/>
+      <c r="N545" s="45"/>
+      <c r="O545" s="45"/>
+      <c r="P545" s="45"/>
+      <c r="Q545" s="45"/>
+      <c r="R545" s="45"/>
+      <c r="S545" s="45"/>
+      <c r="T545" s="45"/>
+      <c r="U545" s="45"/>
+      <c r="V545" s="45"/>
+      <c r="W545" s="45"/>
+      <c r="X545" s="45"/>
+      <c r="Y545" s="45"/>
+      <c r="Z545" s="45"/>
+      <c r="AA545" s="46"/>
+      <c r="AB545" s="46"/>
+      <c r="AC545" s="46"/>
+      <c r="AD545" s="46"/>
+      <c r="AE545" s="46"/>
+      <c r="AF545" s="46"/>
+      <c r="AG545" s="46"/>
+      <c r="AH545" s="46"/>
+      <c r="AI545" s="47"/>
+      <c r="AJ545" s="47"/>
+      <c r="AK545" s="47"/>
+      <c r="AL545" s="47"/>
       <c r="AM545"/>
       <c r="AN545"/>
       <c r="AO545"/>
@@ -32707,37 +32760,37 @@
       <c r="BG545"/>
     </row>
     <row r="546" spans="1:59" ht="14.25" customHeight="1">
-      <c r="A546" s="7" t="s">
+      <c r="A546" s="48" t="s">
         <v>1138</v>
       </c>
-      <c r="B546" s="2" t="s">
+      <c r="B546" s="49" t="s">
         <v>1139</v>
       </c>
-      <c r="C546" s="2" t="s">
+      <c r="C546" s="49" t="s">
         <v>544</v>
       </c>
-      <c r="D546" s="2" t="s">
+      <c r="D546" s="49" t="s">
         <v>544</v>
       </c>
-      <c r="E546" s="2" t="s">
+      <c r="E546" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F546" s="5">
+      <c r="F546" s="50">
         <v>52732</v>
       </c>
-      <c r="G546" s="2" t="s">
+      <c r="G546" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="H546" s="5">
+      <c r="H546" s="50">
         <v>51</v>
       </c>
-      <c r="I546" s="26" t="s">
+      <c r="I546" s="51" t="s">
         <v>1140</v>
       </c>
-      <c r="J546" s="26">
+      <c r="J546" s="51">
         <v>46104</v>
       </c>
-      <c r="K546" s="2" t="s">
+      <c r="K546" s="49" t="s">
         <v>28</v>
       </c>
       <c r="L546" s="60" t="s">
@@ -32759,40 +32812,40 @@
       <c r="Z546" s="2"/>
     </row>
     <row r="547" spans="1:59" ht="14.25" customHeight="1">
-      <c r="A547" s="7" t="s">
+      <c r="A547" s="48" t="s">
         <v>1141</v>
       </c>
-      <c r="B547" s="2" t="s">
+      <c r="B547" s="49" t="s">
         <v>1142</v>
       </c>
-      <c r="C547" s="2" t="s">
+      <c r="C547" s="49" t="s">
         <v>890</v>
       </c>
-      <c r="D547" s="2" t="s">
+      <c r="D547" s="49" t="s">
         <v>886</v>
       </c>
-      <c r="E547" s="2" t="s">
+      <c r="E547" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F547" s="5">
+      <c r="F547" s="50">
         <v>52501</v>
       </c>
-      <c r="G547" s="2" t="s">
+      <c r="G547" s="49" t="s">
         <v>52</v>
       </c>
-      <c r="H547" s="5">
+      <c r="H547" s="50">
         <v>40</v>
       </c>
-      <c r="I547" s="26">
+      <c r="I547" s="51">
         <v>46045</v>
       </c>
-      <c r="J547" s="26">
+      <c r="J547" s="51">
         <v>46080</v>
       </c>
-      <c r="K547" s="2" t="s">
+      <c r="K547" s="49" t="s">
         <v>372</v>
       </c>
-      <c r="L547" s="2" t="s">
+      <c r="L547" s="49" t="s">
         <v>220</v>
       </c>
       <c r="M547" s="2"/>
@@ -32811,40 +32864,40 @@
       <c r="Z547" s="2"/>
     </row>
     <row r="548" spans="1:59" ht="14.25" customHeight="1">
-      <c r="A548" s="7" t="s">
+      <c r="A548" s="48" t="s">
         <v>1143</v>
       </c>
-      <c r="B548" s="2" t="s">
+      <c r="B548" s="49" t="s">
         <v>1144</v>
       </c>
-      <c r="C548" s="2" t="s">
+      <c r="C548" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="D548" s="2" t="s">
+      <c r="D548" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="E548" s="2" t="s">
+      <c r="E548" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F548" s="5">
+      <c r="F548" s="50">
         <v>50314</v>
       </c>
-      <c r="G548" s="2" t="s">
+      <c r="G548" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="H548" s="5">
+      <c r="H548" s="50">
         <v>67</v>
       </c>
-      <c r="I548" s="26">
+      <c r="I548" s="51">
         <v>46048</v>
       </c>
-      <c r="J548" s="26">
+      <c r="J548" s="51">
         <v>46098</v>
       </c>
-      <c r="K548" s="2" t="s">
+      <c r="K548" s="49" t="s">
         <v>379</v>
       </c>
-      <c r="L548" s="2" t="s">
+      <c r="L548" s="49" t="s">
         <v>220</v>
       </c>
       <c r="M548" s="2"/>
@@ -32863,40 +32916,40 @@
       <c r="Z548" s="2"/>
     </row>
     <row r="549" spans="1:59" ht="14.25" customHeight="1">
-      <c r="A549" s="7" t="s">
+      <c r="A549" s="48" t="s">
         <v>1145</v>
       </c>
-      <c r="B549" s="2" t="s">
+      <c r="B549" s="49" t="s">
         <v>1146</v>
       </c>
-      <c r="C549" s="2" t="s">
+      <c r="C549" s="49" t="s">
         <v>1026</v>
       </c>
-      <c r="D549" s="2" t="s">
+      <c r="D549" s="49" t="s">
         <v>41</v>
       </c>
-      <c r="E549" s="2" t="s">
+      <c r="E549" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F549" s="5">
+      <c r="F549" s="50">
         <v>50111</v>
       </c>
-      <c r="G549" s="2" t="s">
+      <c r="G549" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H549" s="5">
+      <c r="H549" s="50">
         <v>47</v>
       </c>
-      <c r="I549" s="26">
+      <c r="I549" s="51">
         <v>46049</v>
       </c>
-      <c r="J549" s="26">
+      <c r="J549" s="51">
         <v>46112</v>
       </c>
-      <c r="K549" s="2" t="s">
+      <c r="K549" s="49" t="s">
         <v>379</v>
       </c>
-      <c r="L549" s="7" t="s">
+      <c r="L549" s="48" t="s">
         <v>503</v>
       </c>
       <c r="M549" s="2"/>
@@ -32915,40 +32968,40 @@
       <c r="Z549" s="2"/>
     </row>
     <row r="550" spans="1:59" ht="14.25" customHeight="1">
-      <c r="A550" s="7" t="s">
+      <c r="A550" s="48" t="s">
         <v>1147</v>
       </c>
-      <c r="B550" s="2" t="s">
+      <c r="B550" s="49" t="s">
         <v>1148</v>
       </c>
-      <c r="C550" s="2" t="s">
+      <c r="C550" s="49" t="s">
         <v>568</v>
       </c>
-      <c r="D550" s="2" t="s">
+      <c r="D550" s="49" t="s">
         <v>167</v>
       </c>
-      <c r="E550" s="2" t="s">
+      <c r="E550" s="49" t="s">
         <v>34</v>
       </c>
-      <c r="F550" s="5">
+      <c r="F550" s="50">
         <v>50401</v>
       </c>
-      <c r="G550" s="2" t="s">
+      <c r="G550" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="H550" s="5">
+      <c r="H550" s="50">
         <v>34</v>
       </c>
-      <c r="I550" s="26">
+      <c r="I550" s="51">
         <v>46048</v>
       </c>
-      <c r="J550" s="26">
+      <c r="J550" s="51">
         <v>46098</v>
       </c>
-      <c r="K550" s="2" t="s">
+      <c r="K550" s="49" t="s">
         <v>391</v>
       </c>
-      <c r="L550" s="2" t="s">
+      <c r="L550" s="49" t="s">
         <v>220</v>
       </c>
       <c r="M550" s="2"/>
@@ -32966,104 +33019,120 @@
       <c r="Y550" s="2"/>
       <c r="Z550" s="2"/>
     </row>
-    <row r="551" spans="1:59" ht="14.25" customHeight="1">
-      <c r="A551" s="56" t="s">
+    <row r="551" spans="1:59" s="73" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A551" s="68" t="s">
         <v>169</v>
       </c>
-      <c r="B551" s="57" t="s">
+      <c r="B551" s="69" t="s">
         <v>481</v>
       </c>
-      <c r="C551" s="57" t="s">
+      <c r="C551" s="69" t="s">
         <v>171</v>
       </c>
-      <c r="D551" s="57" t="s">
+      <c r="D551" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="E551" s="57" t="s">
+      <c r="E551" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="F551" s="58">
+      <c r="F551" s="70">
         <v>50266</v>
       </c>
-      <c r="G551" s="57" t="s">
+      <c r="G551" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="H551" s="58">
+      <c r="H551" s="70">
         <v>49</v>
       </c>
-      <c r="I551" s="59">
+      <c r="I551" s="71">
         <v>46056</v>
       </c>
-      <c r="J551" s="59">
+      <c r="J551" s="71">
         <v>46116</v>
       </c>
-      <c r="K551" s="57" t="s">
+      <c r="K551" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="L551" s="57" t="s">
+      <c r="L551" s="69" t="s">
         <v>107</v>
       </c>
-      <c r="M551" s="49"/>
-      <c r="N551" s="49"/>
-      <c r="O551" s="49"/>
-      <c r="P551" s="49"/>
-      <c r="Q551" s="49"/>
-      <c r="R551" s="49"/>
-      <c r="S551" s="49"/>
-      <c r="T551" s="49"/>
-      <c r="U551" s="49"/>
-      <c r="V551" s="49"/>
-      <c r="W551" s="49"/>
-      <c r="X551" s="49"/>
-      <c r="Y551" s="49"/>
-      <c r="Z551" s="49"/>
-      <c r="AA551" s="50"/>
-      <c r="AB551" s="50"/>
-      <c r="AC551" s="50"/>
-      <c r="AD551" s="50"/>
-      <c r="AE551" s="50"/>
-      <c r="AF551" s="50"/>
-      <c r="AG551" s="50"/>
-      <c r="AH551" s="50"/>
-      <c r="AI551" s="51"/>
-      <c r="AJ551" s="51"/>
-      <c r="AK551" s="51"/>
-      <c r="AL551" s="51"/>
-      <c r="AM551"/>
-      <c r="AN551"/>
-      <c r="AO551"/>
-      <c r="AP551"/>
-      <c r="AQ551"/>
-      <c r="AR551"/>
-      <c r="AS551"/>
-      <c r="AT551"/>
-      <c r="AU551"/>
-      <c r="AV551"/>
-      <c r="AW551"/>
-      <c r="AX551"/>
-      <c r="AY551"/>
-      <c r="AZ551"/>
-      <c r="BA551"/>
-      <c r="BB551"/>
-      <c r="BC551"/>
-      <c r="BD551"/>
-      <c r="BE551"/>
-      <c r="BF551"/>
-      <c r="BG551"/>
+      <c r="M551" s="72"/>
+      <c r="N551" s="72"/>
+      <c r="O551" s="72"/>
+      <c r="P551" s="72"/>
+      <c r="Q551" s="72"/>
+      <c r="R551" s="72"/>
+      <c r="S551" s="72"/>
+      <c r="T551" s="72"/>
+      <c r="U551" s="72"/>
+      <c r="V551" s="72"/>
+      <c r="W551" s="72"/>
+      <c r="X551" s="72"/>
+      <c r="Y551" s="72"/>
+      <c r="Z551" s="72"/>
+      <c r="AI551" s="74"/>
+      <c r="AJ551" s="74"/>
+      <c r="AK551" s="74"/>
+      <c r="AL551" s="74"/>
+      <c r="AM551" s="74"/>
+      <c r="AN551" s="74"/>
+      <c r="AO551" s="74"/>
+      <c r="AP551" s="74"/>
+      <c r="AQ551" s="74"/>
+      <c r="AR551" s="74"/>
+      <c r="AS551" s="74"/>
+      <c r="AT551" s="74"/>
+      <c r="AU551" s="74"/>
+      <c r="AV551" s="74"/>
+      <c r="AW551" s="74"/>
+      <c r="AX551" s="74"/>
+      <c r="AY551" s="74"/>
+      <c r="AZ551" s="74"/>
+      <c r="BA551" s="74"/>
+      <c r="BB551" s="74"/>
+      <c r="BC551" s="74"/>
+      <c r="BD551" s="74"/>
+      <c r="BE551" s="74"/>
+      <c r="BF551" s="74"/>
+      <c r="BG551" s="74"/>
     </row>
     <row r="552" spans="1:59" ht="14.25" customHeight="1">
-      <c r="A552" s="7"/>
-      <c r="B552" s="2"/>
-      <c r="C552" s="2"/>
-      <c r="D552" s="2"/>
-      <c r="E552" s="2"/>
-      <c r="F552" s="5"/>
-      <c r="G552" s="2"/>
-      <c r="H552" s="5"/>
-      <c r="I552" s="8"/>
-      <c r="J552" s="2"/>
-      <c r="K552" s="2"/>
-      <c r="L552" s="2"/>
+      <c r="A552" s="62" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B552" s="75" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C552" s="63" t="s">
+        <v>427</v>
+      </c>
+      <c r="D552" s="63" t="s">
+        <v>332</v>
+      </c>
+      <c r="E552" s="63" t="s">
+        <v>34</v>
+      </c>
+      <c r="F552" s="64">
+        <v>50703</v>
+      </c>
+      <c r="G552" s="63" t="s">
+        <v>52</v>
+      </c>
+      <c r="H552" s="64">
+        <v>89</v>
+      </c>
+      <c r="I552" s="65" t="s">
+        <v>1151</v>
+      </c>
+      <c r="J552" s="66">
+        <v>46098</v>
+      </c>
+      <c r="K552" s="63" t="s">
+        <v>391</v>
+      </c>
+      <c r="L552" s="67" t="s">
+        <v>613</v>
+      </c>
       <c r="M552" s="2"/>
       <c r="N552" s="2"/>
       <c r="O552" s="2"/>
@@ -36467,7 +36536,7 @@
         <v>184</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>34</v>
@@ -36765,7 +36834,7 @@
         <v>626</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>829</v>
@@ -36803,7 +36872,7 @@
         <v>582</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>782</v>
@@ -37677,7 +37746,7 @@
         <v>833</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>437</v>
@@ -37715,7 +37784,7 @@
         <v>833</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>437</v>
@@ -38057,7 +38126,7 @@
         <v>644</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="C56" s="38" t="s">
         <v>427</v>
@@ -38776,7 +38845,7 @@
     </row>
     <row r="75" spans="1:12" ht="15">
       <c r="A75" s="14" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>781</v>
@@ -39007,7 +39076,7 @@
         <v>861</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="C81" s="38" t="s">
         <v>863</v>

--- a/data/warn-scraper/cache/ia/source.xlsx
+++ b/data/warn-scraper/cache/ia/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowamac.sharepoint.com/sites/IWDWorkforceServices/Shared Documents/Rapid Response/WARN/WARN Log/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B1868EF7-8924-45B7-9CE7-1577EC9ABDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BABCBDA1-3D3D-43B9-8C0B-9AA635E01368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6374" uniqueCount="1160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6383" uniqueCount="1165">
   <si>
     <t>Iowa WARN Log</t>
   </si>
@@ -3497,6 +3497,21 @@
   </si>
   <si>
     <t>02/6/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whirlpool Corporatoin </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2800 220th Trail </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amana </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iowa </t>
+  </si>
+  <si>
+    <t>02/17/2026</t>
   </si>
   <si>
     <t>Lynn</t>
@@ -3532,7 +3547,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yy"/>
     <numFmt numFmtId="166" formatCode="m/d/yyyy;@"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3614,18 +3629,6 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="major"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -3693,7 +3696,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3843,9 +3846,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3855,13 +3855,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3877,7 +3870,27 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4146,8 +4159,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L550" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="A2:L550" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L553" totalsRowShown="0" headerRowDxfId="12">
+  <autoFilter ref="A2:L553" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{624CA823-360D-451E-81B4-66E6AEBB7049}" name="Company" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{2CB99E09-68C4-4CD3-8D8C-07722FD0C438}" name="Address Line 1" dataDxfId="10"/>
@@ -4384,20 +4397,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="26.25" customHeight="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="61"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
+      <c r="E1" s="71"/>
+      <c r="F1" s="71"/>
+      <c r="G1" s="71"/>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="71"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
       <c r="A2" s="28" t="s">
@@ -33019,118 +33032,118 @@
       <c r="Y550" s="2"/>
       <c r="Z550" s="2"/>
     </row>
-    <row r="551" spans="1:59" s="73" customFormat="1" ht="14.25" customHeight="1">
-      <c r="A551" s="68" t="s">
+    <row r="551" spans="1:59" s="69" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A551" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="B551" s="69" t="s">
+      <c r="B551" s="65" t="s">
         <v>481</v>
       </c>
-      <c r="C551" s="69" t="s">
+      <c r="C551" s="65" t="s">
         <v>171</v>
       </c>
-      <c r="D551" s="69" t="s">
+      <c r="D551" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="E551" s="69" t="s">
+      <c r="E551" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="F551" s="70">
+      <c r="F551" s="66">
         <v>50266</v>
       </c>
-      <c r="G551" s="69" t="s">
+      <c r="G551" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="H551" s="70">
+      <c r="H551" s="66">
         <v>49</v>
       </c>
-      <c r="I551" s="71">
+      <c r="I551" s="67">
         <v>46056</v>
       </c>
-      <c r="J551" s="71">
+      <c r="J551" s="67">
         <v>46116</v>
       </c>
-      <c r="K551" s="69" t="s">
+      <c r="K551" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="L551" s="69" t="s">
+      <c r="L551" s="65" t="s">
         <v>107</v>
       </c>
-      <c r="M551" s="72"/>
-      <c r="N551" s="72"/>
-      <c r="O551" s="72"/>
-      <c r="P551" s="72"/>
-      <c r="Q551" s="72"/>
-      <c r="R551" s="72"/>
-      <c r="S551" s="72"/>
-      <c r="T551" s="72"/>
-      <c r="U551" s="72"/>
-      <c r="V551" s="72"/>
-      <c r="W551" s="72"/>
-      <c r="X551" s="72"/>
-      <c r="Y551" s="72"/>
-      <c r="Z551" s="72"/>
-      <c r="AI551" s="74"/>
-      <c r="AJ551" s="74"/>
-      <c r="AK551" s="74"/>
-      <c r="AL551" s="74"/>
-      <c r="AM551" s="74"/>
-      <c r="AN551" s="74"/>
-      <c r="AO551" s="74"/>
-      <c r="AP551" s="74"/>
-      <c r="AQ551" s="74"/>
-      <c r="AR551" s="74"/>
-      <c r="AS551" s="74"/>
-      <c r="AT551" s="74"/>
-      <c r="AU551" s="74"/>
-      <c r="AV551" s="74"/>
-      <c r="AW551" s="74"/>
-      <c r="AX551" s="74"/>
-      <c r="AY551" s="74"/>
-      <c r="AZ551" s="74"/>
-      <c r="BA551" s="74"/>
-      <c r="BB551" s="74"/>
-      <c r="BC551" s="74"/>
-      <c r="BD551" s="74"/>
-      <c r="BE551" s="74"/>
-      <c r="BF551" s="74"/>
-      <c r="BG551" s="74"/>
+      <c r="M551" s="68"/>
+      <c r="N551" s="68"/>
+      <c r="O551" s="68"/>
+      <c r="P551" s="68"/>
+      <c r="Q551" s="68"/>
+      <c r="R551" s="68"/>
+      <c r="S551" s="68"/>
+      <c r="T551" s="68"/>
+      <c r="U551" s="68"/>
+      <c r="V551" s="68"/>
+      <c r="W551" s="68"/>
+      <c r="X551" s="68"/>
+      <c r="Y551" s="68"/>
+      <c r="Z551" s="68"/>
+      <c r="AI551" s="70"/>
+      <c r="AJ551" s="70"/>
+      <c r="AK551" s="70"/>
+      <c r="AL551" s="70"/>
+      <c r="AM551" s="70"/>
+      <c r="AN551" s="70"/>
+      <c r="AO551" s="70"/>
+      <c r="AP551" s="70"/>
+      <c r="AQ551" s="70"/>
+      <c r="AR551" s="70"/>
+      <c r="AS551" s="70"/>
+      <c r="AT551" s="70"/>
+      <c r="AU551" s="70"/>
+      <c r="AV551" s="70"/>
+      <c r="AW551" s="70"/>
+      <c r="AX551" s="70"/>
+      <c r="AY551" s="70"/>
+      <c r="AZ551" s="70"/>
+      <c r="BA551" s="70"/>
+      <c r="BB551" s="70"/>
+      <c r="BC551" s="70"/>
+      <c r="BD551" s="70"/>
+      <c r="BE551" s="70"/>
+      <c r="BF551" s="70"/>
+      <c r="BG551" s="70"/>
     </row>
     <row r="552" spans="1:59" ht="14.25" customHeight="1">
-      <c r="A552" s="62" t="s">
+      <c r="A552" s="61" t="s">
         <v>1149</v>
       </c>
-      <c r="B552" s="75" t="s">
+      <c r="B552" s="62" t="s">
         <v>1150</v>
       </c>
-      <c r="C552" s="63" t="s">
+      <c r="C552" s="62" t="s">
         <v>427</v>
       </c>
-      <c r="D552" s="63" t="s">
+      <c r="D552" s="62" t="s">
         <v>332</v>
       </c>
-      <c r="E552" s="63" t="s">
+      <c r="E552" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="F552" s="64">
+      <c r="F552" s="63">
         <v>50703</v>
       </c>
-      <c r="G552" s="63" t="s">
+      <c r="G552" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="H552" s="64">
+      <c r="H552" s="63">
         <v>89</v>
       </c>
-      <c r="I552" s="65" t="s">
+      <c r="I552" s="72" t="s">
         <v>1151</v>
       </c>
-      <c r="J552" s="66">
+      <c r="J552" s="72">
         <v>46098</v>
       </c>
-      <c r="K552" s="63" t="s">
+      <c r="K552" s="62" t="s">
         <v>391</v>
       </c>
-      <c r="L552" s="67" t="s">
+      <c r="L552" s="62" t="s">
         <v>613</v>
       </c>
       <c r="M552" s="2"/>
@@ -33149,18 +33162,42 @@
       <c r="Z552" s="2"/>
     </row>
     <row r="553" spans="1:59" ht="14.25" customHeight="1">
-      <c r="A553" s="7"/>
-      <c r="B553" s="2"/>
-      <c r="C553" s="2"/>
-      <c r="D553" s="2"/>
-      <c r="E553" s="2"/>
-      <c r="F553" s="5"/>
-      <c r="G553" s="2"/>
-      <c r="H553" s="5"/>
-      <c r="I553" s="8"/>
-      <c r="J553" s="2"/>
-      <c r="K553" s="2"/>
-      <c r="L553" s="2"/>
+      <c r="A553" s="73" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B553" s="74" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C553" s="74" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D553" s="74" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E553" s="74" t="s">
+        <v>17</v>
+      </c>
+      <c r="F553" s="75">
+        <v>52203</v>
+      </c>
+      <c r="G553" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="H553" s="75">
+        <v>341</v>
+      </c>
+      <c r="I553" s="76" t="s">
+        <v>1156</v>
+      </c>
+      <c r="J553" s="76">
+        <v>46090</v>
+      </c>
+      <c r="K553" s="74" t="s">
+        <v>366</v>
+      </c>
+      <c r="L553" s="77" t="s">
+        <v>313</v>
+      </c>
       <c r="M553" s="2"/>
       <c r="N553" s="2"/>
       <c r="O553" s="2"/>
@@ -36536,7 +36573,7 @@
         <v>184</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1152</v>
+        <v>1157</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>34</v>
@@ -36834,7 +36871,7 @@
         <v>626</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>829</v>
@@ -36872,7 +36909,7 @@
         <v>582</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>782</v>
@@ -37746,7 +37783,7 @@
         <v>833</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>437</v>
@@ -37784,7 +37821,7 @@
         <v>833</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>437</v>
@@ -38126,7 +38163,7 @@
         <v>644</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>1157</v>
+        <v>1162</v>
       </c>
       <c r="C56" s="38" t="s">
         <v>427</v>
@@ -38845,7 +38882,7 @@
     </row>
     <row r="75" spans="1:12" ht="15">
       <c r="A75" s="14" t="s">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>781</v>
@@ -39076,7 +39113,7 @@
         <v>861</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>1159</v>
+        <v>1164</v>
       </c>
       <c r="C81" s="38" t="s">
         <v>863</v>
@@ -43199,15 +43236,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="465031c5-3d91-457d-a71b-eb9b5941244d">
@@ -43226,7 +43254,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008FFDA55EC64F6340997887DF003F4858" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="610c4182e7e7902e7aea694cdd9432aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb079858-90af-4c1d-b6f1-55332f11d181" xmlns:ns3="465031c5-3d91-457d-a71b-eb9b5941244d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="92492927522a77c15d270bbe3d3d4b37" ns2:_="" ns3:_="">
     <xsd:import namespace="bb079858-90af-4c1d-b6f1-55332f11d181"/>
@@ -43461,14 +43489,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F40177C-67A3-4DD8-A168-9BC85606FD5C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D66E9BA-12AB-4417-9A6A-6113397F4F5F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D66E9BA-12AB-4417-9A6A-6113397F4F5F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6492E40-AF0B-480F-B23D-6DA53B2EBE0E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6492E40-AF0B-480F-B23D-6DA53B2EBE0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F40177C-67A3-4DD8-A168-9BC85606FD5C}"/>
 </file>
--- a/data/warn-scraper/cache/ia/source.xlsx
+++ b/data/warn-scraper/cache/ia/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lkraft\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8607ABD-3F96-4E1E-AB63-1955ECEFEB1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE9E36A9-BB4F-48A3-8FC3-2A04A2328FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -46,12 +46,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6728" uniqueCount="1194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6727" uniqueCount="1192">
   <si>
     <t>Iowa WARN Log</t>
   </si>
   <si>
-    <t>Updated: 04-16-2026</t>
+    <t>Updated: 04-29-2026</t>
   </si>
   <si>
     <t>Company</t>
@@ -459,6 +459,9 @@
     <t>Cedar Rapids</t>
   </si>
   <si>
+    <t>800 S Jordan Creek Pkwy</t>
+  </si>
+  <si>
     <t xml:space="preserve">John Deere Ottumwa Works </t>
   </si>
   <si>
@@ -651,9 +654,6 @@
     <t>Northeast Iowa</t>
   </si>
   <si>
-    <t>800 S Jordan Creek Pkwy</t>
-  </si>
-  <si>
     <t>03/04/2025</t>
   </si>
   <si>
@@ -3447,37 +3447,31 @@
     <t>12/20/2022</t>
   </si>
   <si>
-    <t xml:space="preserve">ABB Inc </t>
+    <t>3277 Daec Rd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tri-City Blacktop, Inc </t>
+  </si>
+  <si>
+    <t>425 S Devils Glen Rd</t>
+  </si>
+  <si>
+    <t>5/14/2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seal and Stripe, Inc </t>
+  </si>
+  <si>
+    <t xml:space="preserve">425 S Devis Glen Rd </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bettendorf </t>
+  </si>
+  <si>
+    <t>ABB Inc</t>
   </si>
   <si>
     <t>510 East Agency Road</t>
-  </si>
-  <si>
-    <t>4/26/21</t>
-  </si>
-  <si>
-    <t>3277 Daec Rd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tri-City Blacktop, Inc </t>
-  </si>
-  <si>
-    <t>425 S Devils Glen Rd</t>
-  </si>
-  <si>
-    <t>5/14/2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seal and Stripe, Inc </t>
-  </si>
-  <si>
-    <t xml:space="preserve">425 S Devis Glen Rd </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bettendorf </t>
-  </si>
-  <si>
-    <t>ABB Inc</t>
   </si>
   <si>
     <t>6/1/2021</t>
@@ -5624,8 +5618,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1BEA32C5-692B-4A99-ADCC-E13692B74419}" name="Table413" displayName="Table413" ref="A2:L23" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="A2:L23" xr:uid="{7470B6DE-4503-4D23-8D41-AC272013CBFF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1BEA32C5-692B-4A99-ADCC-E13692B74419}" name="Table413" displayName="Table413" ref="A2:L22" totalsRowShown="0" headerRowDxfId="12">
+  <autoFilter ref="A2:L22" xr:uid="{7470B6DE-4503-4D23-8D41-AC272013CBFF}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{5EC3C567-DD83-4D25-83FC-574F4BD72715}" name="Company" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{584A3774-9FF7-45FB-94BD-71E440D87D86}" name="Address Line 1" dataDxfId="10"/>
@@ -5842,7 +5836,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BI120"/>
+  <dimension ref="A1:BK120"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.5" style="15" customWidth="1"/>
@@ -9355,19 +9349,43 @@
       <c r="Y64" s="2"/>
       <c r="Z64" s="2"/>
     </row>
-    <row r="65" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A65" s="7"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
-      <c r="L65" s="2"/>
+    <row r="65" spans="1:63" ht="14.25" customHeight="1">
+      <c r="A65" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B65" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="C65" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="D65" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="E65" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" s="48">
+        <v>50266</v>
+      </c>
+      <c r="G65" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="H65" s="48">
+        <v>10</v>
+      </c>
+      <c r="I65" s="49">
+        <v>46140</v>
+      </c>
+      <c r="J65" s="49">
+        <v>46200</v>
+      </c>
+      <c r="K65" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="L65" s="47" t="s">
+        <v>29</v>
+      </c>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9382,8 +9400,11 @@
       <c r="X65" s="2"/>
       <c r="Y65" s="2"/>
       <c r="Z65" s="2"/>
-    </row>
-    <row r="66" spans="1:26" ht="14.25" customHeight="1">
+      <c r="BI65"/>
+      <c r="BJ65"/>
+      <c r="BK65"/>
+    </row>
+    <row r="66" spans="1:63" ht="14.25" customHeight="1">
       <c r="A66" s="7"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -9411,7 +9432,7 @@
       <c r="Y66" s="2"/>
       <c r="Z66" s="2"/>
     </row>
-    <row r="67" spans="1:26" ht="14.25" customHeight="1">
+    <row r="67" spans="1:63" ht="14.25" customHeight="1">
       <c r="A67" s="7"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -9439,7 +9460,7 @@
       <c r="Y67" s="2"/>
       <c r="Z67" s="2"/>
     </row>
-    <row r="68" spans="1:26" ht="14.25" customHeight="1">
+    <row r="68" spans="1:63" ht="14.25" customHeight="1">
       <c r="A68" s="7"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -9467,7 +9488,7 @@
       <c r="Y68" s="2"/>
       <c r="Z68" s="2"/>
     </row>
-    <row r="69" spans="1:26" ht="14.25" customHeight="1">
+    <row r="69" spans="1:63" ht="14.25" customHeight="1">
       <c r="A69" s="7"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -9495,7 +9516,7 @@
       <c r="Y69" s="2"/>
       <c r="Z69" s="2"/>
     </row>
-    <row r="70" spans="1:26" ht="14.25" customHeight="1">
+    <row r="70" spans="1:63" ht="14.25" customHeight="1">
       <c r="A70" s="7"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -9523,7 +9544,7 @@
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
     </row>
-    <row r="71" spans="1:26" ht="14.25" customHeight="1">
+    <row r="71" spans="1:63" ht="14.25" customHeight="1">
       <c r="A71" s="7"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -9551,7 +9572,7 @@
       <c r="Y71" s="2"/>
       <c r="Z71" s="2"/>
     </row>
-    <row r="72" spans="1:26" ht="14.25" customHeight="1">
+    <row r="72" spans="1:63" ht="14.25" customHeight="1">
       <c r="A72" s="7"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -9579,7 +9600,7 @@
       <c r="Y72" s="2"/>
       <c r="Z72" s="2"/>
     </row>
-    <row r="73" spans="1:26" ht="14.25" customHeight="1">
+    <row r="73" spans="1:63" ht="14.25" customHeight="1">
       <c r="A73" s="7"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -9607,7 +9628,7 @@
       <c r="Y73" s="2"/>
       <c r="Z73" s="2"/>
     </row>
-    <row r="74" spans="1:26" ht="14.25" customHeight="1">
+    <row r="74" spans="1:63" ht="14.25" customHeight="1">
       <c r="A74" s="7"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -9635,7 +9656,7 @@
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
     </row>
-    <row r="75" spans="1:26" ht="14.25" customHeight="1">
+    <row r="75" spans="1:63" ht="14.25" customHeight="1">
       <c r="A75" s="7"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -9663,7 +9684,7 @@
       <c r="Y75" s="2"/>
       <c r="Z75" s="2"/>
     </row>
-    <row r="76" spans="1:26" ht="14.25" customHeight="1">
+    <row r="76" spans="1:63" ht="14.25" customHeight="1">
       <c r="A76" s="7"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -9691,7 +9712,7 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
     </row>
-    <row r="77" spans="1:26" ht="14.25" customHeight="1">
+    <row r="77" spans="1:63" ht="14.25" customHeight="1">
       <c r="A77" s="7"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -9719,7 +9740,7 @@
       <c r="Y77" s="2"/>
       <c r="Z77" s="2"/>
     </row>
-    <row r="78" spans="1:26" ht="14.25" customHeight="1">
+    <row r="78" spans="1:63" ht="14.25" customHeight="1">
       <c r="A78" s="7"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -9747,7 +9768,7 @@
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
     </row>
-    <row r="79" spans="1:26" ht="14.25" customHeight="1">
+    <row r="79" spans="1:63" ht="14.25" customHeight="1">
       <c r="A79" s="7"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -9775,7 +9796,7 @@
       <c r="Y79" s="2"/>
       <c r="Z79" s="2"/>
     </row>
-    <row r="80" spans="1:26" ht="14.25" customHeight="1">
+    <row r="80" spans="1:63" ht="14.25" customHeight="1">
       <c r="A80" s="7"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -11017,10 +11038,10 @@
     </row>
     <row r="3" spans="1:12" ht="15">
       <c r="A3" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>38</v>
@@ -11041,7 +11062,7 @@
         <v>75</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J3" s="9">
         <v>45695</v>
@@ -11050,18 +11071,18 @@
         <v>41</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15">
       <c r="A4" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>26</v>
@@ -11079,7 +11100,7 @@
         <v>28</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J4" s="9">
         <v>45667</v>
@@ -11088,21 +11109,21 @@
         <v>28</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15">
       <c r="A5" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -11117,30 +11138,30 @@
         <v>23</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J5" s="9">
         <v>45702</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15">
       <c r="A6" s="17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>18</v>
@@ -11155,7 +11176,7 @@
         <v>53</v>
       </c>
       <c r="I6" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J6" s="20">
         <v>45672</v>
@@ -11164,15 +11185,15 @@
         <v>65</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15">
       <c r="A7" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
@@ -11193,7 +11214,7 @@
         <v>28</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J7" s="9">
         <v>45689</v>
@@ -11202,21 +11223,21 @@
         <v>28</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15">
       <c r="A8" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>64</v>
@@ -11231,7 +11252,7 @@
         <v>298</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J8" s="9">
         <v>45737</v>
@@ -11240,21 +11261,21 @@
         <v>41</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15">
       <c r="A9" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
@@ -11269,7 +11290,7 @@
         <v>34</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J9" s="9">
         <v>45716</v>
@@ -11278,21 +11299,21 @@
         <v>101</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15">
       <c r="A10" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
@@ -11307,27 +11328,27 @@
         <v>41</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J10" s="9">
         <v>45713</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15">
       <c r="A11" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>26</v>
@@ -11339,13 +11360,13 @@
         <v>50009</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H11" s="5">
         <v>1</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J11" s="9">
         <v>45698</v>
@@ -11354,21 +11375,21 @@
         <v>28</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15">
       <c r="A12" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>64</v>
@@ -11383,24 +11404,24 @@
         <v>36</v>
       </c>
       <c r="I12" s="19" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J12" s="20">
         <v>45839</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15">
       <c r="A13" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>116</v>
@@ -11421,27 +11442,27 @@
         <v>32</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J13" s="9">
         <v>45728</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15">
       <c r="A14" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>26</v>
@@ -11459,7 +11480,7 @@
         <v>9</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J14" s="9">
         <v>45747</v>
@@ -11468,18 +11489,18 @@
         <v>45</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15">
       <c r="A15" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>26</v>
@@ -11497,7 +11518,7 @@
         <v>38</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J15" s="9">
         <v>45754</v>
@@ -11506,18 +11527,18 @@
         <v>45</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15">
       <c r="A16" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>26</v>
@@ -11535,7 +11556,7 @@
         <v>72</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J16" s="9">
         <v>45775</v>
@@ -11544,21 +11565,21 @@
         <v>45</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15">
       <c r="A17" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>18</v>
@@ -11573,7 +11594,7 @@
         <v>32</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J17" s="9">
         <v>45779</v>
@@ -11587,10 +11608,10 @@
     </row>
     <row r="18" spans="1:12" ht="15">
       <c r="A18" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>17</v>
@@ -11611,7 +11632,7 @@
         <v>10</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J18" s="9">
         <v>45744</v>
@@ -11625,10 +11646,10 @@
     </row>
     <row r="19" spans="1:12" ht="15">
       <c r="A19" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>124</v>
@@ -11649,13 +11670,13 @@
         <v>3</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J19" s="9">
         <v>45744</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>42</v>
@@ -11663,10 +11684,10 @@
     </row>
     <row r="20" spans="1:12" ht="15">
       <c r="A20" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>57</v>
@@ -11687,13 +11708,13 @@
         <v>2</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J20" s="9">
         <v>45744</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>42</v>
@@ -11701,10 +11722,10 @@
     </row>
     <row r="21" spans="1:12" ht="15">
       <c r="A21" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>17</v>
@@ -11725,7 +11746,7 @@
         <v>6</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J21" s="9">
         <v>45772</v>
@@ -11739,10 +11760,10 @@
     </row>
     <row r="22" spans="1:12" ht="15">
       <c r="A22" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>124</v>
@@ -11763,13 +11784,13 @@
         <v>4</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J22" s="9">
         <v>45772</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>42</v>
@@ -11777,10 +11798,10 @@
     </row>
     <row r="23" spans="1:12" ht="15">
       <c r="A23" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>57</v>
@@ -11801,13 +11822,13 @@
         <v>2</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J23" s="9">
         <v>45772</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>42</v>
@@ -11815,10 +11836,10 @@
     </row>
     <row r="24" spans="1:12" ht="15">
       <c r="A24" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>17</v>
@@ -11839,7 +11860,7 @@
         <v>1</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J24" s="9">
         <v>45835</v>
@@ -11856,7 +11877,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>25</v>
@@ -11962,7 +11983,7 @@
         <v>65</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15">
@@ -11970,7 +11991,7 @@
         <v>211</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>25</v>
@@ -11985,7 +12006,7 @@
         <v>50266</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H28" s="5">
         <v>34</v>
@@ -12052,7 +12073,7 @@
         <v>219</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>18</v>
@@ -12076,7 +12097,7 @@
         <v>65</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15">
@@ -12122,7 +12143,7 @@
         <v>211</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>25</v>
@@ -12137,7 +12158,7 @@
         <v>50266</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H32" s="5">
         <v>14</v>
@@ -12315,7 +12336,7 @@
         <v>238</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D37" s="16" t="s">
         <v>206</v>
@@ -12391,7 +12412,7 @@
         <v>241</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D39" s="16" t="s">
         <v>206</v>
@@ -12453,7 +12474,7 @@
         <v>45810</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>236</v>
@@ -12491,7 +12512,7 @@
         <v>45810</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>236</v>
@@ -12567,7 +12588,7 @@
         <v>45810</v>
       </c>
       <c r="K43" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>236</v>
@@ -12643,7 +12664,7 @@
         <v>45810</v>
       </c>
       <c r="K45" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>236</v>
@@ -12681,7 +12702,7 @@
         <v>45810</v>
       </c>
       <c r="K46" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>236</v>
@@ -12795,7 +12816,7 @@
         <v>45810</v>
       </c>
       <c r="K49" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>236</v>
@@ -12833,7 +12854,7 @@
         <v>45810</v>
       </c>
       <c r="K50" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>236</v>
@@ -12871,7 +12892,7 @@
         <v>45810</v>
       </c>
       <c r="K51" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>236</v>
@@ -12909,7 +12930,7 @@
         <v>45810</v>
       </c>
       <c r="K52" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>236</v>
@@ -12985,7 +13006,7 @@
         <v>45810</v>
       </c>
       <c r="K54" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>236</v>
@@ -13099,7 +13120,7 @@
         <v>45810</v>
       </c>
       <c r="K57" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>236</v>
@@ -13137,7 +13158,7 @@
         <v>45810</v>
       </c>
       <c r="K58" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>236</v>
@@ -13175,7 +13196,7 @@
         <v>45810</v>
       </c>
       <c r="K59" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>236</v>
@@ -13289,7 +13310,7 @@
         <v>45810</v>
       </c>
       <c r="K62" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>236</v>
@@ -13341,10 +13362,10 @@
         <v>285</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D64" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E64" s="16" t="s">
         <v>64</v>
@@ -13441,7 +13462,7 @@
         <v>45810</v>
       </c>
       <c r="K66" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>236</v>
@@ -13528,7 +13549,7 @@
         <v>211</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>25</v>
@@ -13543,7 +13564,7 @@
         <v>50266</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H69" s="5">
         <v>46</v>
@@ -13634,7 +13655,7 @@
         <v>54</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15">
@@ -13669,7 +13690,7 @@
         <v>45861</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>42</v>
@@ -13683,7 +13704,7 @@
         <v>309</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>206</v>
@@ -13794,7 +13815,7 @@
         <v>211</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>25</v>
@@ -13809,7 +13830,7 @@
         <v>50266</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H76" s="5">
         <v>41</v>
@@ -13862,7 +13883,7 @@
         <v>54</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="15">
@@ -13900,7 +13921,7 @@
         <v>54</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="15">
@@ -13946,7 +13967,7 @@
         <v>211</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>25</v>
@@ -13961,7 +13982,7 @@
         <v>50266</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H80" s="5">
         <v>24</v>
@@ -14014,7 +14035,7 @@
         <v>54</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="15">
@@ -14052,7 +14073,7 @@
         <v>54</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="15">
@@ -14090,7 +14111,7 @@
         <v>54</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="15">
@@ -14128,7 +14149,7 @@
         <v>54</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="15">
@@ -14288,7 +14309,7 @@
         <v>211</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>25</v>
@@ -14303,7 +14324,7 @@
         <v>50266</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H89" s="5">
         <v>35</v>
@@ -14353,10 +14374,10 @@
         <v>45856</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="15">
@@ -14394,7 +14415,7 @@
         <v>54</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="15">
@@ -14481,7 +14502,7 @@
         <v>238</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D94" s="16" t="s">
         <v>206</v>
@@ -14557,7 +14578,7 @@
         <v>241</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D96" s="16" t="s">
         <v>206</v>
@@ -14619,7 +14640,7 @@
         <v>45839</v>
       </c>
       <c r="K97" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L97" s="2" t="s">
         <v>236</v>
@@ -14657,7 +14678,7 @@
         <v>45839</v>
       </c>
       <c r="K98" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>236</v>
@@ -14733,7 +14754,7 @@
         <v>45839</v>
       </c>
       <c r="K100" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>236</v>
@@ -14809,7 +14830,7 @@
         <v>45839</v>
       </c>
       <c r="K102" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>236</v>
@@ -14847,7 +14868,7 @@
         <v>45839</v>
       </c>
       <c r="K103" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>236</v>
@@ -14961,7 +14982,7 @@
         <v>45839</v>
       </c>
       <c r="K106" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L106" s="2" t="s">
         <v>236</v>
@@ -14999,7 +15020,7 @@
         <v>45839</v>
       </c>
       <c r="K107" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>236</v>
@@ -15037,7 +15058,7 @@
         <v>45839</v>
       </c>
       <c r="K108" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L108" s="2" t="s">
         <v>236</v>
@@ -15075,7 +15096,7 @@
         <v>45839</v>
       </c>
       <c r="K109" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>236</v>
@@ -15151,7 +15172,7 @@
         <v>45839</v>
       </c>
       <c r="K111" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>236</v>
@@ -15265,7 +15286,7 @@
         <v>45839</v>
       </c>
       <c r="K114" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L114" s="2" t="s">
         <v>236</v>
@@ -15303,7 +15324,7 @@
         <v>45839</v>
       </c>
       <c r="K115" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L115" s="2" t="s">
         <v>236</v>
@@ -15341,7 +15362,7 @@
         <v>45839</v>
       </c>
       <c r="K116" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L116" s="2" t="s">
         <v>236</v>
@@ -15455,7 +15476,7 @@
         <v>45839</v>
       </c>
       <c r="K119" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L119" s="2" t="s">
         <v>236</v>
@@ -15507,10 +15528,10 @@
         <v>285</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D121" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E121" s="16" t="s">
         <v>64</v>
@@ -15607,7 +15628,7 @@
         <v>45839</v>
       </c>
       <c r="K123" s="16" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L123" s="2" t="s">
         <v>236</v>
@@ -15686,7 +15707,7 @@
         <v>54</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="126" spans="1:12" ht="15">
@@ -15694,7 +15715,7 @@
         <v>211</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>25</v>
@@ -15709,7 +15730,7 @@
         <v>50266</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H126" s="5">
         <v>35</v>
@@ -15762,7 +15783,7 @@
         <v>284</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="128" spans="1:12" ht="15">
@@ -15835,7 +15856,7 @@
         <v>45870</v>
       </c>
       <c r="K129" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L129" s="2" t="s">
         <v>236</v>
@@ -15873,7 +15894,7 @@
         <v>45855</v>
       </c>
       <c r="K130" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L130" s="2" t="s">
         <v>42</v>
@@ -15914,7 +15935,7 @@
         <v>54</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="132" spans="1:12" ht="30">
@@ -15928,7 +15949,7 @@
         <v>219</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>18</v>
@@ -15952,7 +15973,7 @@
         <v>65</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="133" spans="1:12" ht="15">
@@ -15960,7 +15981,7 @@
         <v>211</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>25</v>
@@ -15975,7 +15996,7 @@
         <v>50266</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H133" s="5">
         <v>11</v>
@@ -16028,7 +16049,7 @@
         <v>54</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="135" spans="1:12" ht="15">
@@ -16066,7 +16087,7 @@
         <v>54</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="136" spans="1:12" ht="15">
@@ -16104,7 +16125,7 @@
         <v>54</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="137" spans="1:12" ht="15">
@@ -16145,7 +16166,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="30">
+    <row r="138" spans="1:12" ht="30.75">
       <c r="A138" s="7" t="s">
         <v>382</v>
       </c>
@@ -16203,7 +16224,7 @@
         <v>50266</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H139" s="5">
         <v>44</v>
@@ -16256,7 +16277,7 @@
         <v>54</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="141" spans="1:12" ht="15">
@@ -16367,10 +16388,10 @@
         <v>45934</v>
       </c>
       <c r="K143" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L143" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="144" spans="1:12" ht="15">
@@ -16393,7 +16414,7 @@
         <v>50266</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H144" s="5">
         <v>10</v>
@@ -16481,10 +16502,10 @@
         <v>45922</v>
       </c>
       <c r="K146" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="147" spans="1:12" ht="15">
@@ -16507,7 +16528,7 @@
         <v>50266</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H147" s="5">
         <v>10</v>
@@ -16545,7 +16566,7 @@
         <v>50436</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H148" s="5">
         <v>1</v>
@@ -16560,7 +16581,7 @@
         <v>54</v>
       </c>
       <c r="L148" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="149" spans="1:12" ht="15">
@@ -16636,7 +16657,7 @@
         <v>35</v>
       </c>
       <c r="L150" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="151" spans="1:12" ht="30">
@@ -16674,7 +16695,7 @@
         <v>284</v>
       </c>
       <c r="L151" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="152" spans="1:12" ht="15">
@@ -16697,7 +16718,7 @@
         <v>50158</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H152" s="5">
         <v>49</v>
@@ -16712,7 +16733,7 @@
         <v>284</v>
       </c>
       <c r="L152" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="15">
@@ -16735,7 +16756,7 @@
         <v>50436</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H153" s="5">
         <v>3</v>
@@ -16750,7 +16771,7 @@
         <v>54</v>
       </c>
       <c r="L153" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="154" spans="1:12" ht="15">
@@ -16773,7 +16794,7 @@
         <v>50266</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H154" s="5">
         <v>12</v>
@@ -16823,21 +16844,21 @@
         <v>45950</v>
       </c>
       <c r="K155" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L155" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="156" spans="1:12" ht="15">
       <c r="A156" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>404</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>26</v>
@@ -16864,7 +16885,7 @@
         <v>28</v>
       </c>
       <c r="L156" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="157" spans="1:12" ht="15">
@@ -17153,7 +17174,7 @@
         <v>50266</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H164" s="5">
         <v>23</v>
@@ -17229,7 +17250,7 @@
         <v>52001</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H166" s="5">
         <v>2</v>
@@ -17267,7 +17288,7 @@
         <v>50266</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H167" s="5">
         <v>1</v>
@@ -17320,7 +17341,7 @@
         <v>35</v>
       </c>
       <c r="L168" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="169" spans="1:12" ht="15">
@@ -17358,7 +17379,7 @@
         <v>35</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="170" spans="1:12" ht="15">
@@ -17419,7 +17440,7 @@
         <v>50266</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H171" s="5">
         <v>63</v>
@@ -17533,7 +17554,7 @@
         <v>50266</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H174" s="5">
         <v>26</v>
@@ -17583,10 +17604,10 @@
         <v>46073</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L175" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="176" spans="1:12" ht="15">
@@ -17624,7 +17645,7 @@
         <v>54</v>
       </c>
       <c r="L176" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="177" spans="1:12" ht="15">
@@ -17659,10 +17680,10 @@
         <v>46022</v>
       </c>
       <c r="K177" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L177" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="178" spans="1:12" ht="15">
@@ -17837,7 +17858,7 @@
         <v>50266</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H182" s="5">
         <v>14</v>
@@ -18027,7 +18048,7 @@
         <v>50266</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H187" s="5">
         <v>25</v>
@@ -18167,7 +18188,7 @@
         <v>458</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>26</v>
@@ -19897,10 +19918,10 @@
         <v>475</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
@@ -20111,7 +20132,7 @@
         <v>45415</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>72</v>
@@ -20190,18 +20211,18 @@
         <v>45</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15">
       <c r="A15" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>491</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>26</v>
@@ -20228,18 +20249,18 @@
         <v>45</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15">
       <c r="A16" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>491</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>26</v>
@@ -20266,18 +20287,18 @@
         <v>45</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15">
       <c r="A17" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>491</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>26</v>
@@ -20304,18 +20325,18 @@
         <v>45</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15">
       <c r="A18" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>491</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>26</v>
@@ -20342,18 +20363,18 @@
         <v>45</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15">
       <c r="A19" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>491</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>26</v>
@@ -20380,7 +20401,7 @@
         <v>45</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15">
@@ -20418,7 +20439,7 @@
         <v>284</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15">
@@ -20494,7 +20515,7 @@
         <v>54</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15">
@@ -20570,7 +20591,7 @@
         <v>21</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15">
@@ -20581,10 +20602,10 @@
         <v>511</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>64</v>
@@ -20608,7 +20629,7 @@
         <v>21</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15">
@@ -20684,7 +20705,7 @@
         <v>101</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15">
@@ -20722,7 +20743,7 @@
         <v>101</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15">
@@ -20879,7 +20900,7 @@
     </row>
     <row r="33" spans="1:12" ht="15">
       <c r="A33" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>531</v>
@@ -20917,7 +20938,7 @@
     </row>
     <row r="34" spans="1:12" ht="15">
       <c r="A34" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>531</v>
@@ -21026,7 +21047,7 @@
         <v>21</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15">
@@ -21289,7 +21310,7 @@
         <v>45454</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>228</v>
@@ -21303,10 +21324,10 @@
         <v>549</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>18</v>
@@ -21403,10 +21424,10 @@
         <v>45464</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="15">
@@ -21596,7 +21617,7 @@
         <v>45</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15">
@@ -21631,10 +21652,10 @@
         <v>45449</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15">
@@ -21645,7 +21666,7 @@
         <v>566</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>206</v>
@@ -21672,7 +21693,7 @@
         <v>45</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="30">
@@ -21710,7 +21731,7 @@
         <v>45</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="15">
@@ -21748,7 +21769,7 @@
         <v>45</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15">
@@ -21786,7 +21807,7 @@
         <v>54</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="15">
@@ -21862,7 +21883,7 @@
         <v>28</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="15">
@@ -21900,7 +21921,7 @@
         <v>45</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="15">
@@ -21938,7 +21959,7 @@
         <v>45</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="15">
@@ -21976,7 +21997,7 @@
         <v>45</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="15">
@@ -22011,10 +22032,10 @@
         <v>45492</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="15">
@@ -22037,7 +22058,7 @@
         <v>50266</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H63" s="5">
         <v>10</v>
@@ -22090,7 +22111,7 @@
         <v>21</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="15">
@@ -22125,10 +22146,10 @@
         <v>45534</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="15">
@@ -22166,7 +22187,7 @@
         <v>284</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="15">
@@ -22177,7 +22198,7 @@
         <v>594</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>26</v>
@@ -22204,7 +22225,7 @@
         <v>45</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="15">
@@ -22242,7 +22263,7 @@
         <v>54</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="15">
@@ -22265,7 +22286,7 @@
         <v>50266</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H69" s="5">
         <v>24</v>
@@ -22353,10 +22374,10 @@
         <v>45555</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15">
@@ -22391,10 +22412,10 @@
         <v>45555</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="15">
@@ -22429,10 +22450,10 @@
         <v>45555</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="15">
@@ -22470,7 +22491,7 @@
         <v>101</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="15">
@@ -22508,7 +22529,7 @@
         <v>21</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="15">
@@ -22531,7 +22552,7 @@
         <v>50266</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H76" s="5">
         <v>12</v>
@@ -22584,7 +22605,7 @@
         <v>54</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="15">
@@ -22622,7 +22643,7 @@
         <v>54</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="15">
@@ -22660,7 +22681,7 @@
         <v>45</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="15">
@@ -22671,10 +22692,10 @@
         <v>617</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>18</v>
@@ -22695,7 +22716,7 @@
         <v>45505</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>22</v>
@@ -22736,7 +22757,7 @@
         <v>28</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="15">
@@ -22774,7 +22795,7 @@
         <v>28</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="15">
@@ -22812,7 +22833,7 @@
         <v>28</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="15">
@@ -22888,7 +22909,7 @@
         <v>101</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="15">
@@ -22911,7 +22932,7 @@
         <v>50266</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H86" s="5">
         <v>3</v>
@@ -22961,7 +22982,7 @@
         <v>45568</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>293</v>
@@ -23002,7 +23023,7 @@
         <v>45</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="15">
@@ -23025,7 +23046,7 @@
         <v>50266</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H89" s="5">
         <v>16</v>
@@ -23116,7 +23137,7 @@
         <v>101</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="15">
@@ -23154,7 +23175,7 @@
         <v>65</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="15">
@@ -23230,7 +23251,7 @@
         <v>54</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="15">
@@ -23268,7 +23289,7 @@
         <v>45</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="15">
@@ -23306,7 +23327,7 @@
         <v>45</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="15">
@@ -23329,7 +23350,7 @@
         <v>50266</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H97" s="5">
         <v>47</v>
@@ -23355,10 +23376,10 @@
         <v>667</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>18</v>
@@ -23382,7 +23403,7 @@
         <v>101</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="15">
@@ -23595,7 +23616,7 @@
         <v>50010</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H104" s="5">
         <v>3</v>
@@ -23610,7 +23631,7 @@
         <v>45</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="15">
@@ -23633,7 +23654,7 @@
         <v>51106</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H105" s="5">
         <v>6</v>
@@ -23645,10 +23666,10 @@
         <v>45562</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="15">
@@ -23671,7 +23692,7 @@
         <v>50266</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H106" s="5">
         <v>8</v>
@@ -23691,16 +23712,16 @@
     </row>
     <row r="107" spans="1:12" ht="15">
       <c r="A107" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>681</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>18</v>
@@ -23724,7 +23745,7 @@
         <v>284</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="108" spans="1:12" ht="15">
@@ -23762,7 +23783,7 @@
         <v>45</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="109" spans="1:12" ht="15">
@@ -23800,7 +23821,7 @@
         <v>45</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="110" spans="1:12" ht="15">
@@ -23835,10 +23856,10 @@
         <v>45597</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="15">
@@ -23876,7 +23897,7 @@
         <v>21</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="112" spans="1:12" ht="15">
@@ -23914,7 +23935,7 @@
         <v>54</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="113" spans="1:12" ht="15">
@@ -23952,7 +23973,7 @@
         <v>45</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="114" spans="1:12" ht="15">
@@ -23990,7 +24011,7 @@
         <v>54</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="115" spans="1:12" ht="15">
@@ -24028,7 +24049,7 @@
         <v>45</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="116" spans="1:12" ht="15">
@@ -24101,7 +24122,7 @@
         <v>46022</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L117" s="2" t="s">
         <v>29</v>
@@ -24139,7 +24160,7 @@
         <v>45681</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L118" s="14" t="s">
         <v>642</v>
@@ -24150,7 +24171,7 @@
         <v>23</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>25</v>
@@ -24165,7 +24186,7 @@
         <v>50266</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H119" s="5">
         <v>2</v>
@@ -24215,10 +24236,10 @@
         <v>45657</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="121" spans="1:12" ht="15">
@@ -24264,7 +24285,7 @@
         <v>211</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>25</v>
@@ -24279,7 +24300,7 @@
         <v>50266</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H122" s="5">
         <v>2</v>
@@ -24329,10 +24350,10 @@
         <v>45691</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L123" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="124" spans="1:12" ht="15">
@@ -24370,7 +24391,7 @@
         <v>54</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="125" spans="1:12" ht="15">
@@ -24378,7 +24399,7 @@
         <v>211</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>25</v>
@@ -24393,7 +24414,7 @@
         <v>50266</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H125" s="5">
         <v>21</v>
@@ -24484,7 +24505,7 @@
         <v>41</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="128" spans="1:12" ht="15">
@@ -26067,10 +26088,10 @@
     </row>
     <row r="4" spans="1:12" ht="15">
       <c r="A4" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
@@ -26100,7 +26121,7 @@
         <v>45</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15">
@@ -26135,10 +26156,10 @@
         <v>45047</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15">
@@ -26173,7 +26194,7 @@
         <v>45006</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>29</v>
@@ -26556,7 +26577,7 @@
         <v>21</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15">
@@ -26643,10 +26664,10 @@
         <v>792</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>18</v>
@@ -27050,7 +27071,7 @@
         <v>65</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15">
@@ -27088,7 +27109,7 @@
         <v>65</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15">
@@ -27131,7 +27152,7 @@
     </row>
     <row r="32" spans="1:12" ht="15">
       <c r="A32" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>819</v>
@@ -27169,7 +27190,7 @@
     </row>
     <row r="33" spans="1:12" ht="15">
       <c r="A33" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>821</v>
@@ -27207,7 +27228,7 @@
     </row>
     <row r="34" spans="1:12" ht="15">
       <c r="A34" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>823</v>
@@ -27245,7 +27266,7 @@
     </row>
     <row r="35" spans="1:12" ht="15">
       <c r="A35" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>824</v>
@@ -27283,7 +27304,7 @@
     </row>
     <row r="36" spans="1:12" ht="15">
       <c r="A36" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>825</v>
@@ -27321,7 +27342,7 @@
     </row>
     <row r="37" spans="1:12" ht="15">
       <c r="A37" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>827</v>
@@ -27392,7 +27413,7 @@
         <v>54</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15">
@@ -27430,7 +27451,7 @@
         <v>54</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15">
@@ -27544,7 +27565,7 @@
         <v>54</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15">
@@ -27582,7 +27603,7 @@
         <v>804</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15">
@@ -28000,7 +28021,7 @@
         <v>45</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="15">
@@ -28076,7 +28097,7 @@
         <v>54</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="15">
@@ -28114,7 +28135,7 @@
         <v>54</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="15">
@@ -28532,7 +28553,7 @@
         <v>21</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="15">
@@ -28608,7 +28629,7 @@
         <v>101</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="15">
@@ -28760,7 +28781,7 @@
         <v>65</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="15">
@@ -28798,7 +28819,7 @@
         <v>21</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="15">
@@ -28833,10 +28854,10 @@
         <v>45191</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="15">
@@ -29213,7 +29234,7 @@
         <v>45318</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>72</v>
@@ -31095,10 +31116,10 @@
         <v>44680</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15">
@@ -31171,7 +31192,7 @@
         <v>44696</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>950</v>
@@ -31247,7 +31268,7 @@
         <v>44694</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>959</v>
@@ -31288,7 +31309,7 @@
         <v>963</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15">
@@ -31326,7 +31347,7 @@
         <v>969</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15">
@@ -31364,7 +31385,7 @@
         <v>35</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15">
@@ -31399,10 +31420,10 @@
         <v>44742</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15">
@@ -31410,7 +31431,7 @@
         <v>23</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>25</v>
@@ -31451,7 +31472,7 @@
         <v>980</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>26</v>
@@ -31551,7 +31572,7 @@
         <v>44744</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>29</v>
@@ -31592,7 +31613,7 @@
         <v>35</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15">
@@ -31600,7 +31621,7 @@
         <v>211</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>25</v>
@@ -31714,7 +31735,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>25</v>
@@ -32083,7 +32104,7 @@
         <v>44820</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>959</v>
@@ -32094,7 +32115,7 @@
         <v>211</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>25</v>
@@ -32197,7 +32218,7 @@
         <v>44788</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>42</v>
@@ -32252,7 +32273,7 @@
         <v>1019</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>64</v>
@@ -32349,7 +32370,7 @@
         <v>44865</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>293</v>
@@ -32387,7 +32408,7 @@
         <v>44865</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>946</v>
@@ -32398,7 +32419,7 @@
         <v>211</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>25</v>
@@ -32515,7 +32536,7 @@
         <v>1028</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>26</v>
@@ -32577,7 +32598,7 @@
         <v>44865</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>293</v>
@@ -32615,7 +32636,7 @@
         <v>44865</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>946</v>
@@ -32626,7 +32647,7 @@
         <v>211</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>25</v>
@@ -32767,7 +32788,7 @@
         <v>44865</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>946</v>
@@ -32778,7 +32799,7 @@
         <v>23</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>25</v>
@@ -32819,7 +32840,7 @@
         <v>1028</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>26</v>
@@ -33074,7 +33095,7 @@
         <v>1045</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15">
@@ -33082,7 +33103,7 @@
         <v>211</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>25</v>
@@ -33199,7 +33220,7 @@
         <v>1028</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>26</v>
@@ -33299,7 +33320,7 @@
         <v>44830</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>29</v>
@@ -33337,7 +33358,7 @@
         <v>44926</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L62" s="1" t="s">
         <v>293</v>
@@ -33378,7 +33399,7 @@
         <v>35</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="15">
@@ -33489,7 +33510,7 @@
         <v>44865</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>293</v>
@@ -33641,7 +33662,7 @@
         <v>44852</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>297</v>
@@ -33679,10 +33700,10 @@
         <v>44824</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15">
@@ -33690,7 +33711,7 @@
         <v>23</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>472</v>
@@ -33921,7 +33942,7 @@
         <v>1082</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>26</v>
@@ -34021,7 +34042,7 @@
         <v>44960</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>22</v>
@@ -34135,7 +34156,7 @@
         <v>44884</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>42</v>
@@ -34173,7 +34194,7 @@
         <v>44840</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>29</v>
@@ -34211,7 +34232,7 @@
         <v>44874</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>22</v>
@@ -34325,7 +34346,7 @@
         <v>44926</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L88" s="2" t="s">
         <v>22</v>
@@ -34336,7 +34357,7 @@
         <v>23</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>25</v>
@@ -34439,7 +34460,7 @@
         <v>44962</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>42</v>
@@ -34491,7 +34512,7 @@
         <v>1122</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>26</v>
@@ -34518,7 +34539,7 @@
         <v>28</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="15">
@@ -34526,7 +34547,7 @@
         <v>23</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>25</v>
@@ -34705,10 +34726,10 @@
         <v>44911</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="15">
@@ -34746,7 +34767,7 @@
         <v>65</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="15">
@@ -36256,7 +36277,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC2664FB-EEE5-4B9D-9CD3-D928A6EDFE7A}">
-  <dimension ref="A1:L127"/>
+  <dimension ref="A1:L126"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="38.5" style="15" customWidth="1"/>
@@ -36328,79 +36349,79 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="12" t="s">
+        <v>955</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>1133</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="C3" s="12" t="s">
+        <v>957</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="6">
+        <v>52324</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="6">
+        <v>47</v>
+      </c>
+      <c r="I3" s="13">
+        <v>44316</v>
+      </c>
+      <c r="J3" s="13">
+        <v>44377</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15">
+      <c r="A4" s="7" t="s">
         <v>1134</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="B4" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="5">
-        <v>52655</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="H3" s="5">
-        <v>188</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>1135</v>
-      </c>
-      <c r="J3" s="24">
-        <v>44372</v>
-      </c>
-      <c r="K3" s="2" t="s">
+      <c r="F4" s="5">
+        <v>52722</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="5">
+        <v>30</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>1136</v>
+      </c>
+      <c r="J4" s="9">
+        <v>44360</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15">
-      <c r="A4" s="12" t="s">
-        <v>955</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>1136</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>957</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="6">
-        <v>52324</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="6">
-        <v>47</v>
-      </c>
-      <c r="I4" s="13">
-        <v>44316</v>
-      </c>
-      <c r="J4" s="13">
-        <v>44377</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>186</v>
-      </c>
       <c r="L4" s="2" t="s">
-        <v>959</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15">
@@ -36411,7 +36432,7 @@
         <v>1138</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>418</v>
+        <v>1139</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>269</v>
@@ -36426,10 +36447,10 @@
         <v>19</v>
       </c>
       <c r="H5" s="5">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>1139</v>
+        <v>1136</v>
       </c>
       <c r="J5" s="9">
         <v>44360</v>
@@ -36438,7 +36459,7 @@
         <v>35</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15">
@@ -36449,42 +36470,42 @@
         <v>1141</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>1142</v>
+        <v>289</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>269</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>64</v>
       </c>
       <c r="F6" s="5">
-        <v>52722</v>
+        <v>52655</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>19</v>
+        <v>570</v>
       </c>
       <c r="H6" s="5">
-        <v>10</v>
+        <v>234</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
       <c r="J6" s="9">
-        <v>44360</v>
+        <v>44407</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>35</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15">
       <c r="A7" s="7" t="s">
-        <v>1143</v>
+        <v>1140</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1134</v>
+        <v>1141</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>289</v>
@@ -36499,631 +36520,607 @@
         <v>52655</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>570</v>
+        <v>497</v>
       </c>
       <c r="H7" s="5">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="J7" s="9">
-        <v>44407</v>
+        <v>44421</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>35</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15">
       <c r="A8" s="7" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>1134</v>
+        <v>1145</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>266</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>64</v>
       </c>
       <c r="F8" s="5">
-        <v>52655</v>
+        <v>52241</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>497</v>
+        <v>19</v>
       </c>
       <c r="H8" s="5">
-        <v>236</v>
+        <v>96</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="J8" s="9">
-        <v>44421</v>
+        <v>44425</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>35</v>
+        <v>187</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>152</v>
+        <v>217</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15">
       <c r="A9" s="7" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1147</v>
+        <v>1141</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>265</v>
+        <v>289</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>266</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>64</v>
       </c>
       <c r="F9" s="5">
-        <v>52241</v>
+        <v>52655</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>19</v>
+        <v>570</v>
       </c>
       <c r="H9" s="5">
-        <v>96</v>
+        <v>238</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="J9" s="9">
-        <v>44425</v>
+        <v>44435</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>186</v>
+        <v>35</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>217</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15">
       <c r="A10" s="7" t="s">
-        <v>1143</v>
+        <v>1148</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>1134</v>
+        <v>1149</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>289</v>
+        <v>136</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="5">
+        <v>52404</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="5">
+        <v>43</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>1150</v>
+      </c>
+      <c r="J10" s="9">
+        <v>44439</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="30">
+      <c r="A11" s="7" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="5">
-        <v>52655</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="H10" s="5">
-        <v>238</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>1149</v>
-      </c>
-      <c r="J10" s="9">
-        <v>44435</v>
-      </c>
-      <c r="K10" s="2" t="s">
+      <c r="F11" s="5">
+        <v>51454</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" s="5">
+        <v>34</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>1154</v>
+      </c>
+      <c r="J11" s="9">
+        <v>44407</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15">
+      <c r="A12" s="7" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="5">
+        <v>52804</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H12" s="5">
+        <v>49</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>1154</v>
+      </c>
+      <c r="J12" s="9">
+        <v>44421</v>
+      </c>
+      <c r="K12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15">
-      <c r="A11" s="7" t="s">
-        <v>1150</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>1151</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="5">
-        <v>52404</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="5">
-        <v>43</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>1152</v>
-      </c>
-      <c r="J11" s="9">
-        <v>44439</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="30">
-      <c r="A12" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1154</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>1155</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F12" s="5">
-        <v>51454</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="5">
-        <v>34</v>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>1156</v>
-      </c>
-      <c r="J12" s="9">
-        <v>44407</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>963</v>
-      </c>
       <c r="L12" s="2" t="s">
-        <v>1157</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15">
       <c r="A13" s="7" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="5">
+        <v>52655</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="H13" s="5">
+        <v>239</v>
+      </c>
+      <c r="I13" s="8" t="s">
         <v>1158</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="5">
-        <v>52804</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="5">
-        <v>49</v>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>1156</v>
-      </c>
       <c r="J13" s="9">
-        <v>44421</v>
+        <v>44449</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>35</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15">
       <c r="A14" s="7" t="s">
-        <v>1143</v>
+        <v>1159</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>1134</v>
+        <v>1160</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>289</v>
+        <v>621</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>17</v>
+        <v>622</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="F14" s="5">
-        <v>52655</v>
+        <v>50208</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>570</v>
+        <v>33</v>
       </c>
       <c r="H14" s="5">
-        <v>239</v>
+        <v>82</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="J14" s="9">
-        <v>44449</v>
+        <v>44488</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15">
       <c r="A15" s="7" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>621</v>
+        <v>136</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>622</v>
+        <v>76</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="F15" s="5">
-        <v>50208</v>
+        <v>52498</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="H15" s="5">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="J15" s="9">
-        <v>44488</v>
+        <v>44470</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>28</v>
+        <v>187</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15">
       <c r="A16" s="7" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>136</v>
+        <v>17</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="F16" s="5">
-        <v>52498</v>
+        <v>50392</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>27</v>
       </c>
       <c r="H16" s="5">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="J16" s="9">
-        <v>44470</v>
+        <v>44480</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>186</v>
+        <v>28</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>140</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15">
       <c r="A17" s="7" t="s">
-        <v>1167</v>
+        <v>196</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>1168</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>17</v>
+        <v>225</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>26</v>
+        <v>226</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="5">
-        <v>50392</v>
+        <v>50010</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>27</v>
       </c>
       <c r="H17" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I17" s="8" t="s">
         <v>1169</v>
       </c>
       <c r="J17" s="9">
-        <v>44480</v>
+        <v>44491</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>28</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>29</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15">
       <c r="A18" s="7" t="s">
-        <v>195</v>
+        <v>1170</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>225</v>
+        <v>136</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>226</v>
+        <v>76</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="5">
-        <v>50010</v>
+        <v>52404</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="H18" s="5">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="J18" s="9">
-        <v>44491</v>
+        <v>44535</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>28</v>
+        <v>187</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="15">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="30">
       <c r="A19" s="7" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>136</v>
+        <v>1176</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>76</v>
+        <v>1177</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="5">
-        <v>52404</v>
+        <v>51334</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="H19" s="5">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="J19" s="9">
-        <v>44535</v>
+        <v>44505</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>186</v>
+        <v>969</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="30">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15">
       <c r="A20" s="7" t="s">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>1177</v>
+        <v>1180</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>1178</v>
+        <v>621</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1179</v>
+        <v>622</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="5">
-        <v>51334</v>
+        <v>50208</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="H20" s="5">
-        <v>59</v>
+        <v>710</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="J20" s="9">
-        <v>44505</v>
+        <v>44561</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>969</v>
+        <v>28</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>1157</v>
+        <v>950</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15">
       <c r="A21" s="7" t="s">
-        <v>1181</v>
+        <v>1140</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>1182</v>
+        <v>1141</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>621</v>
+        <v>289</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>622</v>
+        <v>17</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="5">
-        <v>50208</v>
+        <v>52655</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>497</v>
       </c>
       <c r="H21" s="5">
-        <v>710</v>
+        <v>247</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="J21" s="9">
-        <v>44561</v>
+        <v>44547</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>950</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15">
       <c r="A22" s="7" t="s">
-        <v>1143</v>
+        <v>1165</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>1134</v>
+        <v>1182</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>289</v>
+        <v>346</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
       <c r="F22" s="5">
-        <v>52655</v>
+        <v>50392</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>497</v>
       </c>
       <c r="H22" s="5">
-        <v>247</v>
+        <v>30</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>1183</v>
       </c>
       <c r="J22" s="9">
-        <v>44547</v>
+        <v>44519</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>152</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15">
-      <c r="A23" s="7" t="s">
-        <v>1167</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F23" s="5">
-        <v>50392</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="H23" s="5">
-        <v>30</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>1185</v>
-      </c>
-      <c r="J23" s="9">
-        <v>44519</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="A23" s="7"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
     </row>
     <row r="24" spans="1:12" ht="15">
       <c r="A24" s="7"/>
@@ -38566,20 +38563,6 @@
       <c r="J126" s="2"/>
       <c r="K126" s="2"/>
       <c r="L126" s="2"/>
-    </row>
-    <row r="127" spans="1:12" ht="15">
-      <c r="A127" s="7"/>
-      <c r="B127" s="2"/>
-      <c r="C127" s="2"/>
-      <c r="D127" s="2"/>
-      <c r="E127" s="2"/>
-      <c r="F127" s="5"/>
-      <c r="G127" s="2"/>
-      <c r="H127" s="5"/>
-      <c r="I127" s="8"/>
-      <c r="J127" s="2"/>
-      <c r="K127" s="2"/>
-      <c r="L127" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -38615,7 +38598,7 @@
         <v>594</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>26</v>
@@ -38642,7 +38625,7 @@
         <v>45</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="135">
@@ -38718,7 +38701,7 @@
         <v>54</v>
       </c>
       <c r="L4" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="135">
@@ -38761,16 +38744,16 @@
     </row>
     <row r="6" spans="1:12" ht="15">
       <c r="A6" s="35" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D6" s="36" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E6" s="36" t="s">
         <v>18</v>
@@ -38946,7 +38929,7 @@
         <v>41</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15">
@@ -38981,10 +38964,10 @@
         <v>45691</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15">
@@ -39060,7 +39043,7 @@
         <v>65</v>
       </c>
       <c r="L13" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15">
@@ -39074,7 +39057,7 @@
         <v>357</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>18</v>
@@ -39095,10 +39078,10 @@
         <v>45856</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15">
@@ -39136,7 +39119,7 @@
         <v>54</v>
       </c>
       <c r="L15" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15">
@@ -39174,7 +39157,7 @@
         <v>45</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15">
@@ -39372,7 +39355,7 @@
         <v>480</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>677</v>
@@ -39410,7 +39393,7 @@
         <v>553</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>629</v>
@@ -39478,7 +39461,7 @@
         <v>45</v>
       </c>
       <c r="L24" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15">
@@ -39501,7 +39484,7 @@
         <v>50010</v>
       </c>
       <c r="G25" s="36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H25" s="36">
         <v>3</v>
@@ -39516,15 +39499,15 @@
         <v>45</v>
       </c>
       <c r="L25" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15">
       <c r="A26" s="35" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C26" s="36" t="s">
         <v>17</v>
@@ -39554,7 +39537,7 @@
         <v>28</v>
       </c>
       <c r="L26" s="36" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15">
@@ -39749,10 +39732,10 @@
     </row>
     <row r="32" spans="1:12" ht="15">
       <c r="A32" s="35" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C32" s="36" t="s">
         <v>116</v>
@@ -39779,10 +39762,10 @@
         <v>45728</v>
       </c>
       <c r="K32" s="36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L32" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="15">
@@ -39820,7 +39803,7 @@
         <v>54</v>
       </c>
       <c r="L33" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15">
@@ -39858,7 +39841,7 @@
         <v>54</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15">
@@ -39896,7 +39879,7 @@
         <v>28</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15">
@@ -39934,7 +39917,7 @@
         <v>28</v>
       </c>
       <c r="L36" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15">
@@ -39972,7 +39955,7 @@
         <v>28</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15" hidden="1">
@@ -40010,7 +39993,7 @@
         <v>45</v>
       </c>
       <c r="L38" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" hidden="1">
@@ -40048,7 +40031,7 @@
         <v>45</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="30">
@@ -40086,7 +40069,7 @@
         <v>54</v>
       </c>
       <c r="L40" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="30">
@@ -40135,7 +40118,7 @@
         <v>309</v>
       </c>
       <c r="C42" s="36" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D42" s="36" t="s">
         <v>206</v>
@@ -40167,13 +40150,13 @@
     </row>
     <row r="43" spans="1:12" ht="15">
       <c r="A43" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>26</v>
@@ -40200,18 +40183,18 @@
         <v>28</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15">
       <c r="A44" s="35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C44" s="36" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D44" s="36" t="s">
         <v>26</v>
@@ -40223,7 +40206,7 @@
         <v>50009</v>
       </c>
       <c r="G44" s="36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H44" s="36">
         <v>1</v>
@@ -40238,7 +40221,7 @@
         <v>28</v>
       </c>
       <c r="L44" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="15">
@@ -40273,7 +40256,7 @@
         <v>45681</v>
       </c>
       <c r="K45" s="36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L45" s="36" t="s">
         <v>642</v>
@@ -40281,16 +40264,16 @@
     </row>
     <row r="46" spans="1:12" ht="15">
       <c r="A46" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>18</v>
@@ -40314,21 +40297,21 @@
         <v>284</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="15">
       <c r="A47" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>64</v>
@@ -40352,7 +40335,7 @@
         <v>41</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="30">
@@ -40390,18 +40373,18 @@
         <v>21</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="30">
       <c r="A49" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>26</v>
@@ -40428,18 +40411,18 @@
         <v>45</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="30">
       <c r="A50" s="35" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B50" s="36" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C50" s="36" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D50" s="36" t="s">
         <v>26</v>
@@ -40466,18 +40449,18 @@
         <v>45</v>
       </c>
       <c r="L50" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="30">
       <c r="A51" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>26</v>
@@ -40504,7 +40487,7 @@
         <v>45</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15">
@@ -40542,7 +40525,7 @@
         <v>54</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15">
@@ -40580,15 +40563,15 @@
         <v>45</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="15">
       <c r="A54" s="35" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B54" s="36" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C54" s="36" t="s">
         <v>38</v>
@@ -40618,7 +40601,7 @@
         <v>41</v>
       </c>
       <c r="L54" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="15">
@@ -40653,10 +40636,10 @@
         <v>45555</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15">
@@ -40664,7 +40647,7 @@
         <v>395</v>
       </c>
       <c r="B56" s="36" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C56" s="36" t="s">
         <v>57</v>
@@ -40691,10 +40674,10 @@
         <v>45555</v>
       </c>
       <c r="K56" s="36" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L56" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="15">
@@ -40729,10 +40712,10 @@
         <v>45555</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="15">
@@ -40770,7 +40753,7 @@
         <v>54</v>
       </c>
       <c r="L58" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="15">
@@ -40808,7 +40791,7 @@
         <v>54</v>
       </c>
       <c r="L59" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="15">
@@ -40819,10 +40802,10 @@
         <v>617</v>
       </c>
       <c r="C60" s="36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D60" s="36" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E60" s="36" t="s">
         <v>18</v>
@@ -40843,7 +40826,7 @@
         <v>45505</v>
       </c>
       <c r="K60" s="36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L60" s="36" t="s">
         <v>22</v>
@@ -40851,16 +40834,16 @@
     </row>
     <row r="61" spans="1:12" ht="15">
       <c r="A61" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>18</v>
@@ -40884,7 +40867,7 @@
         <v>65</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="30">
@@ -40922,7 +40905,7 @@
         <v>65</v>
       </c>
       <c r="L62" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="15">
@@ -40960,15 +40943,15 @@
         <v>284</v>
       </c>
       <c r="L63" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="15">
       <c r="A64" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>17</v>
@@ -41003,10 +40986,10 @@
     </row>
     <row r="65" spans="1:12" ht="15">
       <c r="A65" s="35" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B65" s="36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C65" s="36" t="s">
         <v>124</v>
@@ -41033,7 +41016,7 @@
         <v>45744</v>
       </c>
       <c r="K65" s="36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L65" s="36" t="s">
         <v>42</v>
@@ -41041,10 +41024,10 @@
     </row>
     <row r="66" spans="1:12" ht="15">
       <c r="A66" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>57</v>
@@ -41071,7 +41054,7 @@
         <v>45744</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>42</v>
@@ -41079,10 +41062,10 @@
     </row>
     <row r="67" spans="1:12" ht="15">
       <c r="A67" s="35" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B67" s="36" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C67" s="36" t="s">
         <v>17</v>
@@ -41117,10 +41100,10 @@
     </row>
     <row r="68" spans="1:12" ht="15">
       <c r="A68" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>124</v>
@@ -41147,7 +41130,7 @@
         <v>45772</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L68" s="1" t="s">
         <v>42</v>
@@ -41155,10 +41138,10 @@
     </row>
     <row r="69" spans="1:12" ht="15">
       <c r="A69" s="35" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B69" s="36" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C69" s="36" t="s">
         <v>57</v>
@@ -41185,7 +41168,7 @@
         <v>45772</v>
       </c>
       <c r="K69" s="36" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L69" s="36" t="s">
         <v>42</v>
@@ -41193,10 +41176,10 @@
     </row>
     <row r="70" spans="1:12" ht="15">
       <c r="A70" s="12" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>17</v>
@@ -41261,7 +41244,7 @@
         <v>45861</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L71" s="1" t="s">
         <v>42</v>
@@ -41340,7 +41323,7 @@
         <v>54</v>
       </c>
       <c r="L73" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="15">
@@ -41383,7 +41366,7 @@
     </row>
     <row r="75" spans="1:12" ht="15">
       <c r="A75" s="12" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>628</v>
@@ -41416,21 +41399,21 @@
         <v>101</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="15">
       <c r="A76" s="35" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C76" s="36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D76" s="36" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E76" s="36" t="s">
         <v>18</v>
@@ -41454,7 +41437,7 @@
         <v>101</v>
       </c>
       <c r="L76" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="30">
@@ -41465,10 +41448,10 @@
         <v>667</v>
       </c>
       <c r="C77" s="36" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D77" s="36" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E77" s="36" t="s">
         <v>18</v>
@@ -41492,7 +41475,7 @@
         <v>101</v>
       </c>
       <c r="L77" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="15">
@@ -41527,10 +41510,10 @@
         <v>45597</v>
       </c>
       <c r="K78" s="36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L78" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="15">
@@ -41573,16 +41556,16 @@
     </row>
     <row r="80" spans="1:12" ht="30">
       <c r="A80" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>64</v>
@@ -41603,10 +41586,10 @@
         <v>45839</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L80" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="15">
@@ -41614,7 +41597,7 @@
         <v>710</v>
       </c>
       <c r="B81" s="36" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="C81" s="36" t="s">
         <v>712</v>
@@ -41641,10 +41624,10 @@
         <v>45657</v>
       </c>
       <c r="K81" s="36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L81" s="36" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="15">
@@ -41720,7 +41703,7 @@
         <v>54</v>
       </c>
       <c r="L83" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="15">
@@ -41758,21 +41741,21 @@
         <v>45</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="30">
       <c r="A85" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>18</v>
@@ -41793,10 +41776,10 @@
         <v>45713</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="30">
@@ -41834,7 +41817,7 @@
         <v>45</v>
       </c>
       <c r="L86" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="15">
@@ -41910,7 +41893,7 @@
         <v>101</v>
       </c>
       <c r="L88" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="15">
@@ -41953,16 +41936,16 @@
     </row>
     <row r="90" spans="1:12" ht="15">
       <c r="A90" s="35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B90" s="36" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C90" s="36" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D90" s="36" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E90" s="36" t="s">
         <v>18</v>
@@ -41983,10 +41966,10 @@
         <v>45702</v>
       </c>
       <c r="K90" s="36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L90" s="36" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="15">
@@ -42021,7 +42004,7 @@
         <v>45568</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L91" s="1" t="s">
         <v>293</v>
@@ -42059,7 +42042,7 @@
         <v>46022</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L92" s="1" t="s">
         <v>29</v>
@@ -42100,7 +42083,7 @@
         <v>54</v>
       </c>
       <c r="L93" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="15" hidden="1">
@@ -42138,7 +42121,7 @@
         <v>45</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="30">
@@ -42225,7 +42208,7 @@
         <v>238</v>
       </c>
       <c r="C97" s="38" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D97" s="36" t="s">
         <v>206</v>
@@ -42301,7 +42284,7 @@
         <v>241</v>
       </c>
       <c r="C99" s="38" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D99" s="36" t="s">
         <v>206</v>
@@ -42363,7 +42346,7 @@
         <v>45810</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L100" s="1" t="s">
         <v>236</v>
@@ -42401,7 +42384,7 @@
         <v>45810</v>
       </c>
       <c r="K101" s="36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L101" s="36" t="s">
         <v>236</v>
@@ -42477,7 +42460,7 @@
         <v>45810</v>
       </c>
       <c r="K103" s="36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L103" s="36" t="s">
         <v>236</v>
@@ -42553,7 +42536,7 @@
         <v>45810</v>
       </c>
       <c r="K105" s="36" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L105" s="36" t="s">
         <v>236</v>
@@ -42591,7 +42574,7 @@
         <v>45810</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L106" s="1" t="s">
         <v>236</v>
@@ -42705,7 +42688,7 @@
         <v>45810</v>
       </c>
       <c r="K109" s="36" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L109" s="36" t="s">
         <v>236</v>
@@ -42743,7 +42726,7 @@
         <v>45810</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L110" s="1" t="s">
         <v>236</v>
@@ -42781,7 +42764,7 @@
         <v>45810</v>
       </c>
       <c r="K111" s="36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L111" s="36" t="s">
         <v>236</v>
@@ -42819,7 +42802,7 @@
         <v>45810</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L112" s="1" t="s">
         <v>236</v>
@@ -42895,7 +42878,7 @@
         <v>45810</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L114" s="1" t="s">
         <v>236</v>
@@ -43009,7 +42992,7 @@
         <v>45810</v>
       </c>
       <c r="K117" s="36" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L117" s="36" t="s">
         <v>236</v>
@@ -43047,7 +43030,7 @@
         <v>45810</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L118" s="1" t="s">
         <v>236</v>
@@ -43085,7 +43068,7 @@
         <v>45810</v>
       </c>
       <c r="K119" s="36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L119" s="36" t="s">
         <v>236</v>
@@ -43199,7 +43182,7 @@
         <v>45810</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L122" s="1" t="s">
         <v>236</v>
@@ -43251,10 +43234,10 @@
         <v>285</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>64</v>
@@ -43351,7 +43334,7 @@
         <v>45810</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L126" s="1" t="s">
         <v>236</v>
@@ -43479,7 +43462,7 @@
         <v>238</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>206</v>
@@ -43555,7 +43538,7 @@
         <v>241</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>206</v>
@@ -43617,7 +43600,7 @@
         <v>45839</v>
       </c>
       <c r="K133" s="36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L133" s="36" t="s">
         <v>236</v>
@@ -43655,7 +43638,7 @@
         <v>45839</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L134" s="1" t="s">
         <v>236</v>
@@ -43731,7 +43714,7 @@
         <v>45839</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L136" s="1" t="s">
         <v>236</v>
@@ -43807,7 +43790,7 @@
         <v>45839</v>
       </c>
       <c r="K138" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L138" s="1" t="s">
         <v>236</v>
@@ -43845,7 +43828,7 @@
         <v>45839</v>
       </c>
       <c r="K139" s="36" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L139" s="36" t="s">
         <v>236</v>
@@ -43959,7 +43942,7 @@
         <v>45839</v>
       </c>
       <c r="K142" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L142" s="1" t="s">
         <v>236</v>
@@ -43997,7 +43980,7 @@
         <v>45839</v>
       </c>
       <c r="K143" s="36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L143" s="36" t="s">
         <v>236</v>
@@ -44035,7 +44018,7 @@
         <v>45839</v>
       </c>
       <c r="K144" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L144" s="1" t="s">
         <v>236</v>
@@ -44073,7 +44056,7 @@
         <v>45839</v>
       </c>
       <c r="K145" s="36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L145" s="36" t="s">
         <v>236</v>
@@ -44149,7 +44132,7 @@
         <v>45839</v>
       </c>
       <c r="K147" s="36" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L147" s="36" t="s">
         <v>236</v>
@@ -44263,7 +44246,7 @@
         <v>45839</v>
       </c>
       <c r="K150" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L150" s="1" t="s">
         <v>236</v>
@@ -44301,7 +44284,7 @@
         <v>45839</v>
       </c>
       <c r="K151" s="36" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L151" s="36" t="s">
         <v>236</v>
@@ -44339,7 +44322,7 @@
         <v>45839</v>
       </c>
       <c r="K152" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L152" s="1" t="s">
         <v>236</v>
@@ -44453,7 +44436,7 @@
         <v>45839</v>
       </c>
       <c r="K155" s="36" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L155" s="36" t="s">
         <v>236</v>
@@ -44505,10 +44488,10 @@
         <v>285</v>
       </c>
       <c r="C157" s="38" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D157" s="36" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E157" s="36" t="s">
         <v>64</v>
@@ -44605,7 +44588,7 @@
         <v>45839</v>
       </c>
       <c r="K159" s="36" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L159" s="36" t="s">
         <v>236</v>
@@ -44669,7 +44652,7 @@
         <v>50266</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H161" s="1">
         <v>24</v>
@@ -44707,7 +44690,7 @@
         <v>50266</v>
       </c>
       <c r="G162" s="36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H162" s="36">
         <v>3</v>
@@ -44745,7 +44728,7 @@
         <v>50266</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H163" s="1">
         <v>16</v>
@@ -44768,7 +44751,7 @@
         <v>23</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>25</v>
@@ -44783,7 +44766,7 @@
         <v>50266</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H164" s="1">
         <v>2</v>
@@ -44806,7 +44789,7 @@
         <v>23</v>
       </c>
       <c r="B165" s="36" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C165" s="36" t="s">
         <v>25</v>
@@ -44859,7 +44842,7 @@
         <v>50266</v>
       </c>
       <c r="G166" s="36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H166" s="36">
         <v>12</v>
@@ -44897,7 +44880,7 @@
         <v>50266</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H167" s="1">
         <v>47</v>
@@ -44935,7 +44918,7 @@
         <v>50266</v>
       </c>
       <c r="G168" s="36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H168" s="36">
         <v>8</v>
@@ -44996,7 +44979,7 @@
         <v>211</v>
       </c>
       <c r="B170" s="36" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C170" s="36" t="s">
         <v>25</v>
@@ -45011,7 +44994,7 @@
         <v>50266</v>
       </c>
       <c r="G170" s="36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H170" s="36">
         <v>2</v>
@@ -45034,7 +45017,7 @@
         <v>211</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>25</v>
@@ -45049,7 +45032,7 @@
         <v>50266</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H171" s="1">
         <v>21</v>
@@ -45072,7 +45055,7 @@
         <v>211</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>25</v>
@@ -45087,7 +45070,7 @@
         <v>50266</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H172" s="1">
         <v>34</v>
@@ -45110,7 +45093,7 @@
         <v>211</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>25</v>
@@ -45125,7 +45108,7 @@
         <v>50266</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H173" s="1">
         <v>14</v>
@@ -45148,7 +45131,7 @@
         <v>211</v>
       </c>
       <c r="B174" s="36" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C174" s="36" t="s">
         <v>25</v>
@@ -45163,7 +45146,7 @@
         <v>50266</v>
       </c>
       <c r="G174" s="36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H174" s="36">
         <v>46</v>
@@ -45186,7 +45169,7 @@
         <v>211</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>25</v>
@@ -45201,7 +45184,7 @@
         <v>50266</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H175" s="1">
         <v>41</v>
@@ -45224,7 +45207,7 @@
         <v>211</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>25</v>
@@ -45239,7 +45222,7 @@
         <v>50266</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H176" s="1">
         <v>24</v>
@@ -45262,7 +45245,7 @@
         <v>211</v>
       </c>
       <c r="B177" s="36" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C177" s="36" t="s">
         <v>25</v>
@@ -45277,7 +45260,7 @@
         <v>50266</v>
       </c>
       <c r="G177" s="36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H177" s="36">
         <v>35</v>
@@ -45300,7 +45283,7 @@
         <v>211</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>25</v>
@@ -45315,7 +45298,7 @@
         <v>50266</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H178" s="1">
         <v>35</v>
@@ -45368,7 +45351,7 @@
         <v>21</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="180" spans="1:12" ht="15">
@@ -45382,7 +45365,7 @@
         <v>219</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>18</v>
@@ -45406,7 +45389,7 @@
         <v>65</v>
       </c>
       <c r="L180" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="181" spans="1:12" ht="15">
@@ -45444,7 +45427,7 @@
         <v>101</v>
       </c>
       <c r="L181" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="182" spans="1:12" ht="15">
@@ -45467,7 +45450,7 @@
         <v>51106</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H182" s="1">
         <v>6</v>
@@ -45479,10 +45462,10 @@
         <v>45562</v>
       </c>
       <c r="K182" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L182" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="183" spans="1:12" ht="15">
@@ -45520,7 +45503,7 @@
         <v>54</v>
       </c>
       <c r="L183" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="184" spans="1:12" ht="15">
@@ -45558,7 +45541,7 @@
         <v>54</v>
       </c>
       <c r="L184" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="185" spans="1:12" ht="15">
@@ -45596,7 +45579,7 @@
         <v>54</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="186" spans="1:12" ht="15">
@@ -45634,7 +45617,7 @@
         <v>54</v>
       </c>
       <c r="L186" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="187" spans="1:12" ht="15">
@@ -45672,7 +45655,7 @@
         <v>54</v>
       </c>
       <c r="L187" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="188" spans="1:12" ht="15">
@@ -45710,7 +45693,7 @@
         <v>54</v>
       </c>
       <c r="L188" s="36" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="189" spans="1:12">

--- a/data/warn-scraper/cache/ia/source.xlsx
+++ b/data/warn-scraper/cache/ia/source.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30117"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lkraft\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5DB138C3-3B68-4C73-A6EF-D78774B667FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D225EC7-CA92-4026-A717-C2C4484AB32A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,12 +46,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6725" uniqueCount="1188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6733" uniqueCount="1188">
   <si>
     <t>Iowa WARN Log</t>
   </si>
   <si>
-    <t>Updated: 05-19-2026</t>
+    <t>Updated: 05-27-2026</t>
   </si>
   <si>
     <t>Company</t>
@@ -474,6 +474,9 @@
     <t>Clive</t>
   </si>
   <si>
+    <t>Amendment - Additional Employees</t>
+  </si>
+  <si>
     <t xml:space="preserve">John Deere Ottumwa Works </t>
   </si>
   <si>
@@ -589,9 +592,6 @@
   </si>
   <si>
     <t>01/24/2025</t>
-  </si>
-  <si>
-    <t>Amendment - Additional Employees</t>
   </si>
   <si>
     <t>2/10/2025</t>
@@ -3791,7 +3791,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3991,6 +3991,23 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5504,8 +5521,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L68" totalsRowShown="0" headerRowDxfId="77">
-  <autoFilter ref="A2:L68" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L69" totalsRowShown="0" headerRowDxfId="77">
+  <autoFilter ref="A2:L69" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{624CA823-360D-451E-81B4-66E6AEBB7049}" name="Company" dataDxfId="76"/>
     <tableColumn id="2" xr3:uid="{2CB99E09-68C4-4CD3-8D8C-07722FD0C438}" name="Address Line 1" dataDxfId="75"/>
@@ -9563,18 +9580,42 @@
       <c r="BK68"/>
     </row>
     <row r="69" spans="1:63" ht="14.25" customHeight="1">
-      <c r="A69" s="6"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="2"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="5"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="5"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="2"/>
-      <c r="K69" s="2"/>
-      <c r="L69" s="2"/>
+      <c r="A69" s="79" t="s">
+        <v>23</v>
+      </c>
+      <c r="B69" s="80" t="s">
+        <v>137</v>
+      </c>
+      <c r="C69" s="80" t="s">
+        <v>25</v>
+      </c>
+      <c r="D69" s="80" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="F69" s="81">
+        <v>50266</v>
+      </c>
+      <c r="G69" s="52" t="s">
+        <v>142</v>
+      </c>
+      <c r="H69" s="81">
+        <v>1</v>
+      </c>
+      <c r="I69" s="82">
+        <v>46168</v>
+      </c>
+      <c r="J69" s="82">
+        <v>46228</v>
+      </c>
+      <c r="K69" s="80" t="s">
+        <v>28</v>
+      </c>
+      <c r="L69" s="80" t="s">
+        <v>29</v>
+      </c>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9584,11 +9625,48 @@
       <c r="S69" s="2"/>
       <c r="T69" s="2"/>
       <c r="U69" s="2"/>
-      <c r="V69" s="2"/>
-      <c r="W69" s="2"/>
-      <c r="X69" s="2"/>
-      <c r="Y69" s="2"/>
-      <c r="Z69" s="2"/>
+      <c r="V69" s="83"/>
+      <c r="W69" s="83"/>
+      <c r="X69" s="83"/>
+      <c r="Y69" s="83"/>
+      <c r="Z69" s="83"/>
+      <c r="AA69" s="84"/>
+      <c r="AB69" s="84"/>
+      <c r="AC69" s="84"/>
+      <c r="AD69" s="84"/>
+      <c r="AE69" s="84"/>
+      <c r="AF69" s="84"/>
+      <c r="AG69" s="84"/>
+      <c r="AH69" s="84"/>
+      <c r="AI69" s="84"/>
+      <c r="AJ69" s="84"/>
+      <c r="AK69" s="84"/>
+      <c r="AL69" s="84"/>
+      <c r="AM69" s="84"/>
+      <c r="AN69" s="84"/>
+      <c r="AO69" s="84"/>
+      <c r="AP69" s="84"/>
+      <c r="AQ69" s="84"/>
+      <c r="AR69" s="84"/>
+      <c r="AS69" s="84"/>
+      <c r="AT69" s="84"/>
+      <c r="AU69" s="84"/>
+      <c r="AV69" s="84"/>
+      <c r="AW69" s="84"/>
+      <c r="AX69" s="84"/>
+      <c r="AY69" s="84"/>
+      <c r="AZ69" s="84"/>
+      <c r="BA69" s="84"/>
+      <c r="BB69" s="84"/>
+      <c r="BC69" s="84"/>
+      <c r="BD69" s="84"/>
+      <c r="BE69" s="84"/>
+      <c r="BF69" s="84"/>
+      <c r="BG69" s="84"/>
+      <c r="BH69" s="84"/>
+      <c r="BI69" s="85"/>
+      <c r="BJ69" s="85"/>
+      <c r="BK69"/>
     </row>
     <row r="70" spans="1:63" ht="14.25" customHeight="1">
       <c r="A70" s="6"/>
@@ -11112,10 +11190,10 @@
     </row>
     <row r="3" spans="1:12" ht="15" hidden="1">
       <c r="A3" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>38</v>
@@ -11136,7 +11214,7 @@
         <v>75</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J3" s="8">
         <v>45695</v>
@@ -11145,18 +11223,18 @@
         <v>41</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" hidden="1">
       <c r="A4" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>26</v>
@@ -11174,7 +11252,7 @@
         <v>28</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J4" s="8">
         <v>45667</v>
@@ -11183,21 +11261,21 @@
         <v>28</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" hidden="1">
       <c r="A5" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
@@ -11212,30 +11290,30 @@
         <v>23</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J5" s="8">
         <v>45702</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" hidden="1">
       <c r="A6" s="15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>18</v>
@@ -11250,7 +11328,7 @@
         <v>53</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J6" s="18">
         <v>45672</v>
@@ -11259,15 +11337,15 @@
         <v>65</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" hidden="1">
       <c r="A7" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>17</v>
@@ -11288,7 +11366,7 @@
         <v>28</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J7" s="8">
         <v>45689</v>
@@ -11297,21 +11375,21 @@
         <v>28</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" hidden="1">
       <c r="A8" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>64</v>
@@ -11326,7 +11404,7 @@
         <v>298</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J8" s="8">
         <v>45737</v>
@@ -11335,21 +11413,21 @@
         <v>41</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" hidden="1">
       <c r="A9" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>18</v>
@@ -11364,7 +11442,7 @@
         <v>34</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J9" s="8">
         <v>45716</v>
@@ -11373,21 +11451,21 @@
         <v>101</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" hidden="1">
       <c r="A10" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>18</v>
@@ -11402,27 +11480,27 @@
         <v>41</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J10" s="8">
         <v>45713</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" hidden="1">
       <c r="A11" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>26</v>
@@ -11434,7 +11512,7 @@
         <v>50009</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H11" s="5">
         <v>1</v>
@@ -11449,7 +11527,7 @@
         <v>28</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" hidden="1">
@@ -11484,7 +11562,7 @@
         <v>45839</v>
       </c>
       <c r="K12" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L12" s="14" t="s">
         <v>188</v>
@@ -11525,7 +11603,7 @@
         <v>191</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" hidden="1">
@@ -11563,7 +11641,7 @@
         <v>45</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" hidden="1">
@@ -11601,7 +11679,7 @@
         <v>45</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" hidden="1">
@@ -11639,7 +11717,7 @@
         <v>45</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15">
@@ -11750,7 +11828,7 @@
         <v>45744</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>42</v>
@@ -11864,7 +11942,7 @@
         <v>45772</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>42</v>
@@ -12057,7 +12135,7 @@
         <v>65</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15" hidden="1">
@@ -12080,7 +12158,7 @@
         <v>50266</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H28" s="5">
         <v>34</v>
@@ -12147,7 +12225,7 @@
         <v>223</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>18</v>
@@ -12171,7 +12249,7 @@
         <v>65</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" hidden="1">
@@ -12232,7 +12310,7 @@
         <v>50266</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H32" s="5">
         <v>14</v>
@@ -12410,7 +12488,7 @@
         <v>242</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D37" s="14" t="s">
         <v>210</v>
@@ -12548,7 +12626,7 @@
         <v>45810</v>
       </c>
       <c r="K40" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>240</v>
@@ -12586,7 +12664,7 @@
         <v>45810</v>
       </c>
       <c r="K41" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>240</v>
@@ -12662,7 +12740,7 @@
         <v>45810</v>
       </c>
       <c r="K43" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>240</v>
@@ -12776,7 +12854,7 @@
         <v>45810</v>
       </c>
       <c r="K46" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>240</v>
@@ -13638,7 +13716,7 @@
         <v>50266</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H69" s="5">
         <v>46</v>
@@ -13729,7 +13807,7 @@
         <v>54</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" hidden="1">
@@ -13764,7 +13842,7 @@
         <v>45861</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>42</v>
@@ -13904,7 +13982,7 @@
         <v>50266</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H76" s="5">
         <v>41</v>
@@ -13957,7 +14035,7 @@
         <v>54</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="15" hidden="1">
@@ -13995,7 +14073,7 @@
         <v>54</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="15" hidden="1">
@@ -14056,7 +14134,7 @@
         <v>50266</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H80" s="5">
         <v>24</v>
@@ -14109,7 +14187,7 @@
         <v>54</v>
       </c>
       <c r="L81" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="15" hidden="1">
@@ -14147,7 +14225,7 @@
         <v>54</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="15" hidden="1">
@@ -14185,7 +14263,7 @@
         <v>54</v>
       </c>
       <c r="L83" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="15" hidden="1">
@@ -14223,7 +14301,7 @@
         <v>54</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="15" hidden="1">
@@ -14398,7 +14476,7 @@
         <v>50266</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H89" s="5">
         <v>35</v>
@@ -14451,7 +14529,7 @@
         <v>191</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="15" hidden="1">
@@ -14489,7 +14567,7 @@
         <v>54</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="15" hidden="1">
@@ -14576,7 +14654,7 @@
         <v>242</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D94" s="14" t="s">
         <v>210</v>
@@ -14714,7 +14792,7 @@
         <v>45839</v>
       </c>
       <c r="K97" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L97" s="2" t="s">
         <v>240</v>
@@ -14752,7 +14830,7 @@
         <v>45839</v>
       </c>
       <c r="K98" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>240</v>
@@ -14828,7 +14906,7 @@
         <v>45839</v>
       </c>
       <c r="K100" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L100" s="2" t="s">
         <v>240</v>
@@ -14942,7 +15020,7 @@
         <v>45839</v>
       </c>
       <c r="K103" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>240</v>
@@ -15781,7 +15859,7 @@
         <v>54</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="126" spans="1:12" ht="15" hidden="1">
@@ -15804,7 +15882,7 @@
         <v>50266</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H126" s="5">
         <v>35</v>
@@ -15857,7 +15935,7 @@
         <v>288</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="128" spans="1:12" ht="15" hidden="1">
@@ -16009,7 +16087,7 @@
         <v>54</v>
       </c>
       <c r="L131" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="132" spans="1:12" ht="30" hidden="1">
@@ -16023,7 +16101,7 @@
         <v>223</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>18</v>
@@ -16047,7 +16125,7 @@
         <v>65</v>
       </c>
       <c r="L132" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="133" spans="1:12" ht="15" hidden="1">
@@ -16070,7 +16148,7 @@
         <v>50266</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H133" s="5">
         <v>11</v>
@@ -16123,7 +16201,7 @@
         <v>54</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="135" spans="1:12" ht="15" hidden="1">
@@ -16161,7 +16239,7 @@
         <v>54</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="136" spans="1:12" ht="15" hidden="1">
@@ -16199,7 +16277,7 @@
         <v>54</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="137" spans="1:12" ht="15" hidden="1">
@@ -16298,7 +16376,7 @@
         <v>50266</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H139" s="5">
         <v>44</v>
@@ -16351,7 +16429,7 @@
         <v>54</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="141" spans="1:12" ht="15" hidden="1">
@@ -16465,7 +16543,7 @@
         <v>191</v>
       </c>
       <c r="L143" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="144" spans="1:12" ht="15" hidden="1">
@@ -16488,7 +16566,7 @@
         <v>50266</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H144" s="5">
         <v>10</v>
@@ -16579,7 +16657,7 @@
         <v>205</v>
       </c>
       <c r="L146" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="147" spans="1:12" ht="15" hidden="1">
@@ -16602,7 +16680,7 @@
         <v>50266</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H147" s="5">
         <v>10</v>
@@ -16640,7 +16718,7 @@
         <v>50436</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H148" s="5">
         <v>1</v>
@@ -16655,7 +16733,7 @@
         <v>54</v>
       </c>
       <c r="L148" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="149" spans="1:12" ht="15" hidden="1">
@@ -16731,7 +16809,7 @@
         <v>35</v>
       </c>
       <c r="L150" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="151" spans="1:12" ht="30" hidden="1">
@@ -16769,7 +16847,7 @@
         <v>288</v>
       </c>
       <c r="L151" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="152" spans="1:12" ht="15" hidden="1">
@@ -16792,7 +16870,7 @@
         <v>50158</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H152" s="5">
         <v>49</v>
@@ -16807,7 +16885,7 @@
         <v>288</v>
       </c>
       <c r="L152" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="15" hidden="1">
@@ -16830,7 +16908,7 @@
         <v>50436</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H153" s="5">
         <v>3</v>
@@ -16845,7 +16923,7 @@
         <v>54</v>
       </c>
       <c r="L153" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="154" spans="1:12" ht="15" hidden="1">
@@ -16868,7 +16946,7 @@
         <v>50266</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H154" s="5">
         <v>12</v>
@@ -16921,7 +16999,7 @@
         <v>205</v>
       </c>
       <c r="L155" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="156" spans="1:12" ht="15" hidden="1">
@@ -16959,7 +17037,7 @@
         <v>28</v>
       </c>
       <c r="L156" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="157" spans="1:12" ht="15">
@@ -17248,7 +17326,7 @@
         <v>50266</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H164" s="5">
         <v>23</v>
@@ -17324,7 +17402,7 @@
         <v>52001</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H166" s="5">
         <v>2</v>
@@ -17362,7 +17440,7 @@
         <v>50266</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H167" s="5">
         <v>1</v>
@@ -17415,7 +17493,7 @@
         <v>35</v>
       </c>
       <c r="L168" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="169" spans="1:12" ht="15">
@@ -17453,7 +17531,7 @@
         <v>35</v>
       </c>
       <c r="L169" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="170" spans="1:12" ht="15" hidden="1">
@@ -17514,7 +17592,7 @@
         <v>50266</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H171" s="5">
         <v>63</v>
@@ -17628,7 +17706,7 @@
         <v>50266</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H174" s="5">
         <v>26</v>
@@ -17681,7 +17759,7 @@
         <v>205</v>
       </c>
       <c r="L175" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="176" spans="1:12" ht="15" hidden="1">
@@ -17719,7 +17797,7 @@
         <v>54</v>
       </c>
       <c r="L176" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="177" spans="1:12" ht="15" hidden="1">
@@ -17757,7 +17835,7 @@
         <v>191</v>
       </c>
       <c r="L177" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="178" spans="1:12" ht="15" hidden="1">
@@ -17932,7 +18010,7 @@
         <v>50266</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H182" s="5">
         <v>14</v>
@@ -18122,7 +18200,7 @@
         <v>50266</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H187" s="5">
         <v>25</v>
@@ -20206,7 +20284,7 @@
         <v>45415</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>72</v>
@@ -20285,7 +20363,7 @@
         <v>45</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15">
@@ -20323,7 +20401,7 @@
         <v>45</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15">
@@ -20361,7 +20439,7 @@
         <v>45</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15">
@@ -20399,7 +20477,7 @@
         <v>45</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15">
@@ -20437,7 +20515,7 @@
         <v>45</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15">
@@ -20475,7 +20553,7 @@
         <v>45</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15">
@@ -20513,7 +20591,7 @@
         <v>288</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15">
@@ -20589,7 +20667,7 @@
         <v>54</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15">
@@ -20665,7 +20743,7 @@
         <v>21</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15">
@@ -20703,7 +20781,7 @@
         <v>21</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15">
@@ -20779,7 +20857,7 @@
         <v>101</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15">
@@ -20817,7 +20895,7 @@
         <v>101</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15">
@@ -21121,7 +21199,7 @@
         <v>21</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15">
@@ -21398,10 +21476,10 @@
         <v>553</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>18</v>
@@ -21501,7 +21579,7 @@
         <v>205</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="15">
@@ -21691,7 +21769,7 @@
         <v>45</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15">
@@ -21729,7 +21807,7 @@
         <v>205</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15">
@@ -21767,7 +21845,7 @@
         <v>45</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="30">
@@ -21805,7 +21883,7 @@
         <v>45</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="15">
@@ -21843,7 +21921,7 @@
         <v>45</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15">
@@ -21881,7 +21959,7 @@
         <v>54</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="15">
@@ -21957,7 +22035,7 @@
         <v>28</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="15">
@@ -21995,7 +22073,7 @@
         <v>45</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="15">
@@ -22033,7 +22111,7 @@
         <v>45</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="15">
@@ -22071,7 +22149,7 @@
         <v>45</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="15">
@@ -22106,10 +22184,10 @@
         <v>45492</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="15">
@@ -22132,7 +22210,7 @@
         <v>50266</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H63" s="5">
         <v>10</v>
@@ -22185,7 +22263,7 @@
         <v>21</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="15">
@@ -22223,7 +22301,7 @@
         <v>205</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="15">
@@ -22261,7 +22339,7 @@
         <v>288</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="15">
@@ -22272,7 +22350,7 @@
         <v>598</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>26</v>
@@ -22299,7 +22377,7 @@
         <v>45</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="15">
@@ -22337,7 +22415,7 @@
         <v>54</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="15">
@@ -22360,7 +22438,7 @@
         <v>50266</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H69" s="5">
         <v>24</v>
@@ -22451,7 +22529,7 @@
         <v>205</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15">
@@ -22489,7 +22567,7 @@
         <v>205</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="15">
@@ -22527,7 +22605,7 @@
         <v>205</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="15">
@@ -22565,7 +22643,7 @@
         <v>101</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="15">
@@ -22603,7 +22681,7 @@
         <v>21</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="15">
@@ -22626,7 +22704,7 @@
         <v>50266</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H76" s="5">
         <v>12</v>
@@ -22679,7 +22757,7 @@
         <v>54</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="15">
@@ -22717,7 +22795,7 @@
         <v>54</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="15">
@@ -22755,7 +22833,7 @@
         <v>45</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="15">
@@ -22766,10 +22844,10 @@
         <v>621</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>18</v>
@@ -22831,7 +22909,7 @@
         <v>28</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="15">
@@ -22869,7 +22947,7 @@
         <v>28</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="15">
@@ -22907,7 +22985,7 @@
         <v>28</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="15">
@@ -22983,7 +23061,7 @@
         <v>101</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="15">
@@ -23006,7 +23084,7 @@
         <v>50266</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H86" s="5">
         <v>3</v>
@@ -23097,7 +23175,7 @@
         <v>45</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="15">
@@ -23120,7 +23198,7 @@
         <v>50266</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H89" s="5">
         <v>16</v>
@@ -23211,7 +23289,7 @@
         <v>101</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="15">
@@ -23249,7 +23327,7 @@
         <v>65</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="15">
@@ -23325,7 +23403,7 @@
         <v>54</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="15">
@@ -23363,7 +23441,7 @@
         <v>45</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="15">
@@ -23401,7 +23479,7 @@
         <v>45</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="15">
@@ -23424,7 +23502,7 @@
         <v>50266</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H97" s="5">
         <v>47</v>
@@ -23450,10 +23528,10 @@
         <v>671</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>18</v>
@@ -23477,7 +23555,7 @@
         <v>101</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="15">
@@ -23690,7 +23768,7 @@
         <v>50010</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H104" s="5">
         <v>3</v>
@@ -23705,7 +23783,7 @@
         <v>45</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="15">
@@ -23728,7 +23806,7 @@
         <v>51106</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H105" s="5">
         <v>6</v>
@@ -23740,10 +23818,10 @@
         <v>45562</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="15">
@@ -23766,7 +23844,7 @@
         <v>50266</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H106" s="5">
         <v>8</v>
@@ -23786,16 +23864,16 @@
     </row>
     <row r="107" spans="1:12" ht="15">
       <c r="A107" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>685</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>18</v>
@@ -23819,7 +23897,7 @@
         <v>288</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="108" spans="1:12" ht="15">
@@ -23857,7 +23935,7 @@
         <v>45</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:12" ht="15">
@@ -23895,7 +23973,7 @@
         <v>45</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="110" spans="1:12" ht="15">
@@ -23930,10 +24008,10 @@
         <v>45597</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="111" spans="1:12" ht="15">
@@ -23971,7 +24049,7 @@
         <v>21</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="112" spans="1:12" ht="15">
@@ -24009,7 +24087,7 @@
         <v>54</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="113" spans="1:12" ht="15">
@@ -24047,7 +24125,7 @@
         <v>45</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="114" spans="1:12" ht="15">
@@ -24085,7 +24163,7 @@
         <v>54</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="115" spans="1:12" ht="15">
@@ -24123,7 +24201,7 @@
         <v>45</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="116" spans="1:12" ht="15">
@@ -24234,7 +24312,7 @@
         <v>45681</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L118" s="12" t="s">
         <v>646</v>
@@ -24260,7 +24338,7 @@
         <v>50266</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H119" s="5">
         <v>2</v>
@@ -24310,10 +24388,10 @@
         <v>45657</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="121" spans="1:12" ht="15">
@@ -24374,7 +24452,7 @@
         <v>50266</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H122" s="5">
         <v>2</v>
@@ -24424,10 +24502,10 @@
         <v>45691</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L123" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="124" spans="1:12" ht="15">
@@ -24465,7 +24543,7 @@
         <v>54</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="125" spans="1:12" ht="15">
@@ -24488,7 +24566,7 @@
         <v>50266</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H125" s="5">
         <v>21</v>
@@ -24579,7 +24657,7 @@
         <v>41</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="128" spans="1:12" ht="15">
@@ -26162,10 +26240,10 @@
     </row>
     <row r="4" spans="1:12" ht="15">
       <c r="A4" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
@@ -26195,7 +26273,7 @@
         <v>45</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15">
@@ -26233,7 +26311,7 @@
         <v>191</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15">
@@ -26738,10 +26816,10 @@
         <v>796</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>18</v>
@@ -27145,7 +27223,7 @@
         <v>65</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15">
@@ -27183,7 +27261,7 @@
         <v>65</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15">
@@ -27677,7 +27755,7 @@
         <v>807</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15">
@@ -28095,7 +28173,7 @@
         <v>45</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="15">
@@ -28171,7 +28249,7 @@
         <v>54</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="15">
@@ -28209,7 +28287,7 @@
         <v>54</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="15">
@@ -28627,7 +28705,7 @@
         <v>21</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="15">
@@ -28703,7 +28781,7 @@
         <v>101</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="15">
@@ -28855,7 +28933,7 @@
         <v>65</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="15">
@@ -28893,7 +28971,7 @@
         <v>21</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="15">
@@ -28931,7 +29009,7 @@
         <v>205</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="15">
@@ -29308,7 +29386,7 @@
         <v>45318</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>72</v>
@@ -31193,7 +31271,7 @@
         <v>191</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15">
@@ -31383,7 +31461,7 @@
         <v>966</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15">
@@ -31421,7 +31499,7 @@
         <v>972</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15">
@@ -31459,7 +31537,7 @@
         <v>35</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15">
@@ -31497,7 +31575,7 @@
         <v>205</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15">
@@ -31687,7 +31765,7 @@
         <v>35</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15">
@@ -32347,7 +32425,7 @@
         <v>1022</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>64</v>
@@ -33169,7 +33247,7 @@
         <v>1048</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15">
@@ -33473,7 +33551,7 @@
         <v>35</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="15">
@@ -33777,7 +33855,7 @@
         <v>205</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15">
@@ -34613,7 +34691,7 @@
         <v>28</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="15">
@@ -34803,7 +34881,7 @@
         <v>191</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="15">
@@ -34841,7 +34919,7 @@
         <v>65</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="15">
@@ -36457,7 +36535,7 @@
         <v>35</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15">
@@ -36495,7 +36573,7 @@
         <v>35</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15">
@@ -36571,7 +36649,7 @@
         <v>35</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15">
@@ -36685,7 +36763,7 @@
         <v>35</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15">
@@ -36723,7 +36801,7 @@
         <v>35</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15">
@@ -36761,7 +36839,7 @@
         <v>28</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15">
@@ -36799,7 +36877,7 @@
         <v>191</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15">
@@ -37027,7 +37105,7 @@
         <v>35</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15">
@@ -38558,7 +38636,7 @@
         <v>598</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>26</v>
@@ -38585,7 +38663,7 @@
         <v>45</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="135">
@@ -38661,7 +38739,7 @@
         <v>54</v>
       </c>
       <c r="L4" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="135">
@@ -38889,7 +38967,7 @@
         <v>41</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15">
@@ -38924,10 +39002,10 @@
         <v>45691</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15">
@@ -39003,7 +39081,7 @@
         <v>65</v>
       </c>
       <c r="L13" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15">
@@ -39041,7 +39119,7 @@
         <v>191</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15">
@@ -39079,7 +39157,7 @@
         <v>54</v>
       </c>
       <c r="L15" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15">
@@ -39117,7 +39195,7 @@
         <v>45</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15">
@@ -39421,7 +39499,7 @@
         <v>45</v>
       </c>
       <c r="L24" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15">
@@ -39444,7 +39522,7 @@
         <v>50010</v>
       </c>
       <c r="G25" s="34" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H25" s="34">
         <v>3</v>
@@ -39459,15 +39537,15 @@
         <v>45</v>
       </c>
       <c r="L25" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15">
       <c r="A26" s="33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B26" s="34" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C26" s="34" t="s">
         <v>17</v>
@@ -39497,7 +39575,7 @@
         <v>28</v>
       </c>
       <c r="L26" s="34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15">
@@ -39725,7 +39803,7 @@
         <v>191</v>
       </c>
       <c r="L32" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="15">
@@ -39763,7 +39841,7 @@
         <v>54</v>
       </c>
       <c r="L33" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15">
@@ -39801,7 +39879,7 @@
         <v>54</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15">
@@ -39839,7 +39917,7 @@
         <v>28</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15">
@@ -39877,7 +39955,7 @@
         <v>28</v>
       </c>
       <c r="L36" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15">
@@ -39915,7 +39993,7 @@
         <v>28</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15" hidden="1">
@@ -39953,7 +40031,7 @@
         <v>45</v>
       </c>
       <c r="L38" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" hidden="1">
@@ -39991,7 +40069,7 @@
         <v>45</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="30">
@@ -40029,7 +40107,7 @@
         <v>54</v>
       </c>
       <c r="L40" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="30">
@@ -40110,13 +40188,13 @@
     </row>
     <row r="43" spans="1:12" ht="15">
       <c r="A43" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>26</v>
@@ -40143,18 +40221,18 @@
         <v>28</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15">
       <c r="A44" s="33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B44" s="34" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C44" s="34" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D44" s="34" t="s">
         <v>26</v>
@@ -40166,7 +40244,7 @@
         <v>50009</v>
       </c>
       <c r="G44" s="34" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H44" s="34">
         <v>1</v>
@@ -40181,7 +40259,7 @@
         <v>28</v>
       </c>
       <c r="L44" s="34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="15">
@@ -40216,7 +40294,7 @@
         <v>45681</v>
       </c>
       <c r="K45" s="34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L45" s="34" t="s">
         <v>646</v>
@@ -40224,16 +40302,16 @@
     </row>
     <row r="46" spans="1:12" ht="15">
       <c r="A46" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>1183</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>18</v>
@@ -40257,21 +40335,21 @@
         <v>288</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="15">
       <c r="A47" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>1184</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>64</v>
@@ -40295,7 +40373,7 @@
         <v>41</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="30">
@@ -40333,7 +40411,7 @@
         <v>21</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="30">
@@ -40371,7 +40449,7 @@
         <v>45</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="30">
@@ -40409,7 +40487,7 @@
         <v>45</v>
       </c>
       <c r="L50" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="30">
@@ -40447,7 +40525,7 @@
         <v>45</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15">
@@ -40485,7 +40563,7 @@
         <v>54</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15">
@@ -40523,15 +40601,15 @@
         <v>45</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="15">
       <c r="A54" s="33" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B54" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C54" s="34" t="s">
         <v>38</v>
@@ -40561,7 +40639,7 @@
         <v>41</v>
       </c>
       <c r="L54" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="15">
@@ -40599,7 +40677,7 @@
         <v>205</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15">
@@ -40637,7 +40715,7 @@
         <v>205</v>
       </c>
       <c r="L56" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="15">
@@ -40675,7 +40753,7 @@
         <v>205</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="15">
@@ -40713,7 +40791,7 @@
         <v>54</v>
       </c>
       <c r="L58" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="15">
@@ -40751,7 +40829,7 @@
         <v>54</v>
       </c>
       <c r="L59" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="15">
@@ -40762,10 +40840,10 @@
         <v>621</v>
       </c>
       <c r="C60" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D60" s="34" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E60" s="34" t="s">
         <v>18</v>
@@ -40794,16 +40872,16 @@
     </row>
     <row r="61" spans="1:12" ht="15">
       <c r="A61" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>18</v>
@@ -40827,7 +40905,7 @@
         <v>65</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="30">
@@ -40865,7 +40943,7 @@
         <v>65</v>
       </c>
       <c r="L62" s="34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="15">
@@ -40903,7 +40981,7 @@
         <v>288</v>
       </c>
       <c r="L63" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="15">
@@ -40976,7 +41054,7 @@
         <v>45744</v>
       </c>
       <c r="K65" s="34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L65" s="34" t="s">
         <v>42</v>
@@ -41090,7 +41168,7 @@
         <v>45772</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L68" s="1" t="s">
         <v>42</v>
@@ -41204,7 +41282,7 @@
         <v>45861</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L71" s="1" t="s">
         <v>42</v>
@@ -41283,7 +41361,7 @@
         <v>54</v>
       </c>
       <c r="L73" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="15">
@@ -41359,21 +41437,21 @@
         <v>101</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="15">
       <c r="A76" s="33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B76" s="34" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C76" s="34" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D76" s="34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E76" s="34" t="s">
         <v>18</v>
@@ -41397,7 +41475,7 @@
         <v>101</v>
       </c>
       <c r="L76" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="30">
@@ -41408,10 +41486,10 @@
         <v>671</v>
       </c>
       <c r="C77" s="34" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D77" s="34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E77" s="34" t="s">
         <v>18</v>
@@ -41435,7 +41513,7 @@
         <v>101</v>
       </c>
       <c r="L77" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="15">
@@ -41470,10 +41548,10 @@
         <v>45597</v>
       </c>
       <c r="K78" s="34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L78" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="15">
@@ -41546,7 +41624,7 @@
         <v>45839</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L80" s="1" t="s">
         <v>188</v>
@@ -41584,10 +41662,10 @@
         <v>45657</v>
       </c>
       <c r="K81" s="34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L81" s="34" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="15">
@@ -41663,7 +41741,7 @@
         <v>54</v>
       </c>
       <c r="L83" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="15">
@@ -41701,21 +41779,21 @@
         <v>45</v>
       </c>
       <c r="L84" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="30">
       <c r="A85" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>18</v>
@@ -41736,10 +41814,10 @@
         <v>45713</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="30">
@@ -41777,7 +41855,7 @@
         <v>45</v>
       </c>
       <c r="L86" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="15">
@@ -41853,7 +41931,7 @@
         <v>101</v>
       </c>
       <c r="L88" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="15">
@@ -41896,16 +41974,16 @@
     </row>
     <row r="90" spans="1:12" ht="15">
       <c r="A90" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B90" s="34" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C90" s="34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D90" s="34" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E90" s="34" t="s">
         <v>18</v>
@@ -41926,10 +42004,10 @@
         <v>45702</v>
       </c>
       <c r="K90" s="34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L90" s="34" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="15">
@@ -42043,7 +42121,7 @@
         <v>54</v>
       </c>
       <c r="L93" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="15" hidden="1">
@@ -42081,7 +42159,7 @@
         <v>45</v>
       </c>
       <c r="L94" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="30">
@@ -42168,7 +42246,7 @@
         <v>242</v>
       </c>
       <c r="C97" s="36" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D97" s="34" t="s">
         <v>210</v>
@@ -42306,7 +42384,7 @@
         <v>45810</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L100" s="1" t="s">
         <v>240</v>
@@ -42344,7 +42422,7 @@
         <v>45810</v>
       </c>
       <c r="K101" s="34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L101" s="34" t="s">
         <v>240</v>
@@ -42420,7 +42498,7 @@
         <v>45810</v>
       </c>
       <c r="K103" s="34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L103" s="34" t="s">
         <v>240</v>
@@ -42534,7 +42612,7 @@
         <v>45810</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L106" s="1" t="s">
         <v>240</v>
@@ -43422,7 +43500,7 @@
         <v>242</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>210</v>
@@ -43560,7 +43638,7 @@
         <v>45839</v>
       </c>
       <c r="K133" s="34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L133" s="34" t="s">
         <v>240</v>
@@ -43598,7 +43676,7 @@
         <v>45839</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L134" s="1" t="s">
         <v>240</v>
@@ -43674,7 +43752,7 @@
         <v>45839</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L136" s="1" t="s">
         <v>240</v>
@@ -43788,7 +43866,7 @@
         <v>45839</v>
       </c>
       <c r="K139" s="34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L139" s="34" t="s">
         <v>240</v>
@@ -44612,7 +44690,7 @@
         <v>50266</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H161" s="1">
         <v>24</v>
@@ -44650,7 +44728,7 @@
         <v>50266</v>
       </c>
       <c r="G162" s="34" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H162" s="34">
         <v>3</v>
@@ -44688,7 +44766,7 @@
         <v>50266</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H163" s="1">
         <v>16</v>
@@ -44726,7 +44804,7 @@
         <v>50266</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H164" s="1">
         <v>2</v>
@@ -44802,7 +44880,7 @@
         <v>50266</v>
       </c>
       <c r="G166" s="34" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H166" s="34">
         <v>12</v>
@@ -44840,7 +44918,7 @@
         <v>50266</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H167" s="1">
         <v>47</v>
@@ -44878,7 +44956,7 @@
         <v>50266</v>
       </c>
       <c r="G168" s="34" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H168" s="34">
         <v>8</v>
@@ -44954,7 +45032,7 @@
         <v>50266</v>
       </c>
       <c r="G170" s="34" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H170" s="34">
         <v>2</v>
@@ -44992,7 +45070,7 @@
         <v>50266</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H171" s="1">
         <v>21</v>
@@ -45030,7 +45108,7 @@
         <v>50266</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H172" s="1">
         <v>34</v>
@@ -45068,7 +45146,7 @@
         <v>50266</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H173" s="1">
         <v>14</v>
@@ -45106,7 +45184,7 @@
         <v>50266</v>
       </c>
       <c r="G174" s="34" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H174" s="34">
         <v>46</v>
@@ -45144,7 +45222,7 @@
         <v>50266</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H175" s="1">
         <v>41</v>
@@ -45182,7 +45260,7 @@
         <v>50266</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H176" s="1">
         <v>24</v>
@@ -45220,7 +45298,7 @@
         <v>50266</v>
       </c>
       <c r="G177" s="34" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H177" s="34">
         <v>35</v>
@@ -45258,7 +45336,7 @@
         <v>50266</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H178" s="1">
         <v>35</v>
@@ -45311,7 +45389,7 @@
         <v>21</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="180" spans="1:12" ht="15">
@@ -45325,7 +45403,7 @@
         <v>223</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>18</v>
@@ -45349,7 +45427,7 @@
         <v>65</v>
       </c>
       <c r="L180" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="181" spans="1:12" ht="15">
@@ -45387,7 +45465,7 @@
         <v>101</v>
       </c>
       <c r="L181" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="182" spans="1:12" ht="15">
@@ -45410,7 +45488,7 @@
         <v>51106</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="H182" s="1">
         <v>6</v>
@@ -45422,10 +45500,10 @@
         <v>45562</v>
       </c>
       <c r="K182" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L182" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="183" spans="1:12" ht="15">
@@ -45463,7 +45541,7 @@
         <v>54</v>
       </c>
       <c r="L183" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="184" spans="1:12" ht="15">
@@ -45501,7 +45579,7 @@
         <v>54</v>
       </c>
       <c r="L184" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="185" spans="1:12" ht="15">
@@ -45539,7 +45617,7 @@
         <v>54</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="186" spans="1:12" ht="15">
@@ -45577,7 +45655,7 @@
         <v>54</v>
       </c>
       <c r="L186" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="187" spans="1:12" ht="15">
@@ -45615,7 +45693,7 @@
         <v>54</v>
       </c>
       <c r="L187" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="188" spans="1:12" ht="15">
@@ -45653,7 +45731,7 @@
         <v>54</v>
       </c>
       <c r="L188" s="34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="189" spans="1:12">
@@ -45680,6 +45758,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008FFDA55EC64F6340997887DF003F4858" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="610c4182e7e7902e7aea694cdd9432aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb079858-90af-4c1d-b6f1-55332f11d181" xmlns:ns3="465031c5-3d91-457d-a71b-eb9b5941244d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="92492927522a77c15d270bbe3d3d4b37" ns2:_="" ns3:_="">
     <xsd:import namespace="bb079858-90af-4c1d-b6f1-55332f11d181"/>
@@ -45914,7 +46001,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="465031c5-3d91-457d-a71b-eb9b5941244d">
@@ -45933,23 +46020,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F40177C-67A3-4DD8-A168-9BC85606FD5C}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6492E40-AF0B-480F-B23D-6DA53B2EBE0E}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D66E9BA-12AB-4417-9A6A-6113397F4F5F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F40177C-67A3-4DD8-A168-9BC85606FD5C}"/>
 </file>
--- a/data/warn-scraper/cache/ia/source.xlsx
+++ b/data/warn-scraper/cache/ia/source.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lkraft\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39981AB9-35BF-4FE3-9300-026352FE2041}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F187B606-0CA0-4FF3-9B34-6B8AEFCEA6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,12 +46,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6749" uniqueCount="1195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6757" uniqueCount="1195">
   <si>
     <t>Iowa WARN Log</t>
   </si>
   <si>
-    <t>Updated: 07-17-2026</t>
+    <t>Updated: 07-22-2026</t>
   </si>
   <si>
     <t>Company</t>
@@ -5558,8 +5558,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L80" totalsRowShown="0" headerRowDxfId="77">
-  <autoFilter ref="A2:L80" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L81" totalsRowShown="0" headerRowDxfId="77">
+  <autoFilter ref="A2:L81" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}">
+    <filterColumn colId="11">
+      <filters>
+        <filter val="Manufacturing"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{624CA823-360D-451E-81B4-66E6AEBB7049}" name="Company" dataDxfId="76"/>
     <tableColumn id="2" xr3:uid="{2CB99E09-68C4-4CD3-8D8C-07722FD0C438}" name="Address Line 1" dataDxfId="75"/>
@@ -5881,7 +5887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L80"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.5" style="13" customWidth="1"/>
@@ -8693,116 +8699,116 @@
       </c>
     </row>
     <row r="75" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A75" s="84" t="s">
+      <c r="A75" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F75" s="5">
+        <v>52211</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" s="5">
+        <v>5</v>
+      </c>
+      <c r="I75" s="22">
+        <v>46203</v>
+      </c>
+      <c r="J75" s="22">
+        <v>46296</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L75" s="63" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="14.25" customHeight="1">
+      <c r="A76" s="66" t="s">
+        <v>156</v>
+      </c>
+      <c r="B76" s="67" t="s">
+        <v>159</v>
+      </c>
+      <c r="C76" s="67" t="s">
+        <v>160</v>
+      </c>
+      <c r="D76" s="67" t="s">
+        <v>147</v>
+      </c>
+      <c r="E76" s="67" t="s">
+        <v>64</v>
+      </c>
+      <c r="F76" s="68">
+        <v>50327</v>
+      </c>
+      <c r="G76" s="67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" s="68">
+        <v>4</v>
+      </c>
+      <c r="I76" s="69">
+        <v>46203</v>
+      </c>
+      <c r="J76" s="69">
+        <v>46296</v>
+      </c>
+      <c r="K76" s="67" t="s">
+        <v>45</v>
+      </c>
+      <c r="L76" s="67" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="14.25" customHeight="1">
+      <c r="A77" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="B75" s="85" t="s">
+      <c r="B77" s="85" t="s">
         <v>139</v>
       </c>
-      <c r="C75" s="85" t="s">
+      <c r="C77" s="85" t="s">
         <v>25</v>
       </c>
-      <c r="D75" s="85" t="s">
+      <c r="D77" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="E75" s="85" t="s">
+      <c r="E77" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="F75" s="86">
+      <c r="F77" s="86">
         <v>50266</v>
       </c>
-      <c r="G75" s="85" t="s">
+      <c r="G77" s="85" t="s">
         <v>143</v>
       </c>
-      <c r="H75" s="86">
+      <c r="H77" s="86">
         <v>20</v>
       </c>
-      <c r="I75" s="87">
+      <c r="I77" s="87">
         <v>46210</v>
       </c>
-      <c r="J75" s="87">
+      <c r="J77" s="87">
         <v>46270</v>
       </c>
-      <c r="K75" s="85" t="s">
+      <c r="K77" s="85" t="s">
         <v>28</v>
       </c>
-      <c r="L75" s="85" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A76" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F76" s="5">
-        <v>52211</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H76" s="5">
-        <v>5</v>
-      </c>
-      <c r="I76" s="22">
-        <v>46203</v>
-      </c>
-      <c r="J76" s="22">
-        <v>46296</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L76" s="63" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="14.25" customHeight="1">
-      <c r="A77" s="66" t="s">
-        <v>156</v>
-      </c>
-      <c r="B77" s="67" t="s">
-        <v>159</v>
-      </c>
-      <c r="C77" s="67" t="s">
-        <v>160</v>
-      </c>
-      <c r="D77" s="67" t="s">
-        <v>147</v>
-      </c>
-      <c r="E77" s="67" t="s">
-        <v>64</v>
-      </c>
-      <c r="F77" s="68">
-        <v>50327</v>
-      </c>
-      <c r="G77" s="67" t="s">
-        <v>19</v>
-      </c>
-      <c r="H77" s="68">
-        <v>4</v>
-      </c>
-      <c r="I77" s="69">
-        <v>46203</v>
-      </c>
-      <c r="J77" s="69">
-        <v>46296</v>
-      </c>
-      <c r="K77" s="67" t="s">
-        <v>45</v>
-      </c>
-      <c r="L77" s="67" t="s">
+      <c r="L77" s="85" t="s">
         <v>29</v>
       </c>
     </row>
@@ -8829,7 +8835,7 @@
         <v>27</v>
       </c>
       <c r="H78" s="5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I78" s="22">
         <v>46213</v>
@@ -8918,6 +8924,44 @@
       </c>
       <c r="L80" s="2" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="15" customHeight="1">
+      <c r="A81" s="84" t="s">
+        <v>23</v>
+      </c>
+      <c r="B81" s="85" t="s">
+        <v>139</v>
+      </c>
+      <c r="C81" s="85" t="s">
+        <v>25</v>
+      </c>
+      <c r="D81" s="85" t="s">
+        <v>26</v>
+      </c>
+      <c r="E81" s="85" t="s">
+        <v>18</v>
+      </c>
+      <c r="F81" s="86">
+        <v>50266</v>
+      </c>
+      <c r="G81" s="85" t="s">
+        <v>143</v>
+      </c>
+      <c r="H81" s="86">
+        <v>20</v>
+      </c>
+      <c r="I81" s="87">
+        <v>46225</v>
+      </c>
+      <c r="J81" s="87">
+        <v>46284</v>
+      </c>
+      <c r="K81" s="85" t="s">
+        <v>28</v>
+      </c>
+      <c r="L81" s="85" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -35998,34 +36042,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="465031c5-3d91-457d-a71b-eb9b5941244d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="bb079858-90af-4c1d-b6f1-55332f11d181" xsi:nil="true"/>
-    <SharedWithUsers xmlns="bb079858-90af-4c1d-b6f1-55332f11d181">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <MediaLengthInSeconds xmlns="465031c5-3d91-457d-a71b-eb9b5941244d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008FFDA55EC64F6340997887DF003F4858" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="610c4182e7e7902e7aea694cdd9432aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb079858-90af-4c1d-b6f1-55332f11d181" xmlns:ns3="465031c5-3d91-457d-a71b-eb9b5941244d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="92492927522a77c15d270bbe3d3d4b37" ns2:_="" ns3:_="">
     <xsd:import namespace="bb079858-90af-4c1d-b6f1-55332f11d181"/>
@@ -36260,8 +36276,36 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="465031c5-3d91-457d-a71b-eb9b5941244d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="bb079858-90af-4c1d-b6f1-55332f11d181" xsi:nil="true"/>
+    <SharedWithUsers xmlns="bb079858-90af-4c1d-b6f1-55332f11d181">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <MediaLengthInSeconds xmlns="465031c5-3d91-457d-a71b-eb9b5941244d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F40177C-67A3-4DD8-A168-9BC85606FD5C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6492E40-AF0B-480F-B23D-6DA53B2EBE0E}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -36269,5 +36313,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6492E40-AF0B-480F-B23D-6DA53B2EBE0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F40177C-67A3-4DD8-A168-9BC85606FD5C}"/>
 </file>
--- a/data/warn-scraper/cache/ia/source.xlsx
+++ b/data/warn-scraper/cache/ia/source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowamac.sharepoint.com/sites/IWDWorkforceServices/Shared Documents/Rapid Response/WARN/WARN Log/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{12B5FB6E-7F4A-4633-AC98-BD3E97F00845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CDD03BB-6C80-4ADD-B00E-8E06FEE4A680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -46,12 +46,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6789" uniqueCount="1199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6797" uniqueCount="1199">
   <si>
     <t>Iowa WARN Log</t>
   </si>
   <si>
-    <t>Updated: 08-4-2026</t>
+    <t>Updated: 08-5-2026</t>
   </si>
   <si>
     <t>Company</t>
@@ -3830,7 +3830,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4024,6 +4024,19 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5537,8 +5550,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L85" totalsRowShown="0" headerRowDxfId="77">
-  <autoFilter ref="A2:L85" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L86" totalsRowShown="0" headerRowDxfId="77">
+  <autoFilter ref="A2:L86" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{624CA823-360D-451E-81B4-66E6AEBB7049}" name="Company" dataDxfId="76"/>
     <tableColumn id="2" xr3:uid="{2CB99E09-68C4-4CD3-8D8C-07722FD0C438}" name="Address Line 1" dataDxfId="75"/>
@@ -5860,7 +5873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L85"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="38.5" style="13" customWidth="1"/>
@@ -9087,6 +9100,44 @@
       </c>
       <c r="L85" s="2" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" s="79" customFormat="1" ht="15" customHeight="1">
+      <c r="A86" s="75" t="s">
+        <v>23</v>
+      </c>
+      <c r="B86" s="76" t="s">
+        <v>139</v>
+      </c>
+      <c r="C86" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="D86" s="76" t="s">
+        <v>26</v>
+      </c>
+      <c r="E86" s="76" t="s">
+        <v>18</v>
+      </c>
+      <c r="F86" s="77">
+        <v>50266</v>
+      </c>
+      <c r="G86" s="76" t="s">
+        <v>143</v>
+      </c>
+      <c r="H86" s="77">
+        <v>7</v>
+      </c>
+      <c r="I86" s="78">
+        <v>46238</v>
+      </c>
+      <c r="J86" s="78">
+        <v>46298</v>
+      </c>
+      <c r="K86" s="76" t="s">
+        <v>28</v>
+      </c>
+      <c r="L86" s="76" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -36167,34 +36218,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="465031c5-3d91-457d-a71b-eb9b5941244d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="bb079858-90af-4c1d-b6f1-55332f11d181" xsi:nil="true"/>
-    <SharedWithUsers xmlns="bb079858-90af-4c1d-b6f1-55332f11d181">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <MediaLengthInSeconds xmlns="465031c5-3d91-457d-a71b-eb9b5941244d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008FFDA55EC64F6340997887DF003F4858" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="610c4182e7e7902e7aea694cdd9432aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb079858-90af-4c1d-b6f1-55332f11d181" xmlns:ns3="465031c5-3d91-457d-a71b-eb9b5941244d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="92492927522a77c15d270bbe3d3d4b37" ns2:_="" ns3:_="">
     <xsd:import namespace="bb079858-90af-4c1d-b6f1-55332f11d181"/>
@@ -36429,14 +36452,42 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="465031c5-3d91-457d-a71b-eb9b5941244d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="bb079858-90af-4c1d-b6f1-55332f11d181" xsi:nil="true"/>
+    <SharedWithUsers xmlns="bb079858-90af-4c1d-b6f1-55332f11d181">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <MediaLengthInSeconds xmlns="465031c5-3d91-457d-a71b-eb9b5941244d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6492E40-AF0B-480F-B23D-6DA53B2EBE0E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F40177C-67A3-4DD8-A168-9BC85606FD5C}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D66E9BA-12AB-4417-9A6A-6113397F4F5F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6492E40-AF0B-480F-B23D-6DA53B2EBE0E}"/>
 </file>
--- a/data/warn-scraper/cache/ia/source.xlsx
+++ b/data/warn-scraper/cache/ia/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowamac.sharepoint.com/sites/IWDWorkforceServices/Shared Documents/Rapid Response/WARN/WARN Log/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D69176E-BDED-411F-BD48-A71689494EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F85C923E-CD68-41EE-98C5-D6406E8C9E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -46,12 +46,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6848" uniqueCount="1200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6854" uniqueCount="1197">
   <si>
     <t>Iowa WARN Log</t>
   </si>
   <si>
-    <t>Updated: 08-28-2026</t>
+    <t>Updated: 09-01-2026</t>
   </si>
   <si>
     <t>Company</t>
@@ -3547,15 +3547,6 @@
   </si>
   <si>
     <t>12/20/2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collins Aerospace </t>
-  </si>
-  <si>
-    <t>400 Collins Road NE</t>
-  </si>
-  <si>
-    <t>9/1/2021</t>
   </si>
   <si>
     <t xml:space="preserve">Principal Life Insurance Company </t>
@@ -3758,7 +3749,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3781,6 +3772,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D9D9"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
       </patternFill>
     </fill>
   </fills>
@@ -3848,7 +3845,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4065,6 +4062,18 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -5580,8 +5589,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L92" totalsRowShown="0" headerRowDxfId="77">
-  <autoFilter ref="A2:L92" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L93" totalsRowShown="0" headerRowDxfId="77">
+  <autoFilter ref="A2:L93" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{624CA823-360D-451E-81B4-66E6AEBB7049}" name="Company" dataDxfId="76"/>
     <tableColumn id="2" xr3:uid="{2CB99E09-68C4-4CD3-8D8C-07722FD0C438}" name="Address Line 1" dataDxfId="75"/>
@@ -5685,8 +5694,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1BEA32C5-692B-4A99-ADCC-E13692B74419}" name="Table413" displayName="Table413" ref="A2:L10" totalsRowShown="0" headerRowDxfId="12">
-  <autoFilter ref="A2:L10" xr:uid="{7470B6DE-4503-4D23-8D41-AC272013CBFF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{1BEA32C5-692B-4A99-ADCC-E13692B74419}" name="Table413" displayName="Table413" ref="A2:L9" totalsRowShown="0" headerRowDxfId="12">
+  <autoFilter ref="A2:L9" xr:uid="{7470B6DE-4503-4D23-8D41-AC272013CBFF}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{5EC3C567-DD83-4D25-83FC-574F4BD72715}" name="Company" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{584A3774-9FF7-45FB-94BD-71E440D87D86}" name="Address Line 1" dataDxfId="10"/>
@@ -9398,6 +9407,44 @@
         <v>48</v>
       </c>
     </row>
+    <row r="93" spans="1:12" ht="15" customHeight="1">
+      <c r="A93" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F93" s="5">
+        <v>50644</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H93" s="5">
+        <v>5</v>
+      </c>
+      <c r="I93" s="22">
+        <v>46265</v>
+      </c>
+      <c r="J93" s="22">
+        <v>46265</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
     <row r="94" spans="1:12" ht="15" customHeight="1">
       <c r="A94" s="6"/>
       <c r="B94" s="2"/>
@@ -9433,7 +9480,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78E1DDF6-6CC3-48B9-A90E-CA11C6F8439A}">
-  <dimension ref="A1:L193"/>
+  <dimension ref="A1:L194"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="38.5" style="13" customWidth="1"/>
@@ -16686,7 +16733,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="15" hidden="1">
+    <row r="192" spans="1:12" ht="2.25" customHeight="1">
       <c r="A192" s="6"/>
       <c r="B192" s="2" t="s">
         <v>184</v>
@@ -16714,7 +16761,7 @@
       <c r="K192" s="2"/>
       <c r="L192" s="2"/>
     </row>
-    <row r="193" spans="1:12" ht="15" hidden="1">
+    <row r="193" spans="1:12" ht="15">
       <c r="A193" s="80" t="s">
         <v>180</v>
       </c>
@@ -16750,6 +16797,42 @@
       </c>
       <c r="L193" s="81" t="s">
         <v>182</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" ht="2.25" customHeight="1">
+      <c r="A194" s="84"/>
+      <c r="B194" s="85" t="s">
+        <v>161</v>
+      </c>
+      <c r="C194" s="85" t="s">
+        <v>88</v>
+      </c>
+      <c r="D194" s="85" t="s">
+        <v>89</v>
+      </c>
+      <c r="E194" s="85" t="s">
+        <v>63</v>
+      </c>
+      <c r="F194" s="86">
+        <v>50644</v>
+      </c>
+      <c r="G194" s="85" t="s">
+        <v>142</v>
+      </c>
+      <c r="H194" s="86">
+        <v>5</v>
+      </c>
+      <c r="I194" s="87">
+        <v>46265</v>
+      </c>
+      <c r="J194" s="87">
+        <v>46265</v>
+      </c>
+      <c r="K194" s="85" t="s">
+        <v>53</v>
+      </c>
+      <c r="L194" s="85" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -28987,7 +29070,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC2664FB-EEE5-4B9D-9CD3-D928A6EDFE7A}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="38.5" style="13" customWidth="1"/>
@@ -29066,186 +29149,186 @@
         <v>1168</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>137</v>
+        <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="F3" s="5">
-        <v>52498</v>
+        <v>50392</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H3" s="5">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>1169</v>
       </c>
       <c r="J3" s="8">
-        <v>44470</v>
+        <v>44480</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>233</v>
+        <v>27</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>179</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15">
       <c r="A4" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>1170</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>1171</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>17</v>
+        <v>269</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>25</v>
+        <v>270</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="5">
-        <v>50392</v>
+        <v>50010</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>26</v>
       </c>
       <c r="H4" s="5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="J4" s="8">
-        <v>44480</v>
+        <v>44491</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>27</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>28</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15">
       <c r="A5" s="6" t="s">
-        <v>241</v>
+        <v>1173</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>269</v>
+        <v>137</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>270</v>
+        <v>76</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="5">
-        <v>50010</v>
+        <v>52404</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H5" s="5">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="J5" s="8">
-        <v>44491</v>
+        <v>44535</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>27</v>
+        <v>233</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="15">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="30">
       <c r="A6" s="6" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>137</v>
+        <v>1179</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>76</v>
+        <v>1180</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="5">
-        <v>52404</v>
+        <v>51334</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H6" s="5">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>1178</v>
+        <v>1181</v>
       </c>
       <c r="J6" s="8">
-        <v>44535</v>
+        <v>44505</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>233</v>
+        <v>1003</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="30">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15">
       <c r="A7" s="6" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>1182</v>
+        <v>656</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>1183</v>
+        <v>657</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="5">
-        <v>51334</v>
+        <v>50208</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="H7" s="5">
-        <v>59</v>
+        <v>710</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>1184</v>
       </c>
       <c r="J7" s="8">
-        <v>44505</v>
+        <v>44561</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>1003</v>
+        <v>27</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>1175</v>
+        <v>984</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15">
@@ -29256,109 +29339,71 @@
         <v>1186</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>656</v>
+        <v>332</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>657</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="5">
-        <v>50208</v>
+        <v>52655</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>19</v>
+        <v>532</v>
       </c>
       <c r="H8" s="5">
-        <v>710</v>
+        <v>247</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>1187</v>
+        <v>1184</v>
       </c>
       <c r="J8" s="8">
-        <v>44561</v>
+        <v>44547</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>984</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15">
       <c r="A9" s="6" t="s">
-        <v>1188</v>
+        <v>1167</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>332</v>
+        <v>381</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
       <c r="F9" s="5">
-        <v>52655</v>
+        <v>50392</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>532</v>
       </c>
       <c r="H9" s="5">
-        <v>247</v>
+        <v>30</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="J9" s="8">
-        <v>44547</v>
+        <v>44519</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15">
-      <c r="A10" s="6" t="s">
-        <v>1170</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>1190</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" s="5">
-        <v>50392</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="H10" s="5">
-        <v>30</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>1191</v>
-      </c>
-      <c r="J10" s="8">
-        <v>44519</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L10" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -29855,7 +29900,7 @@
         <v>392</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>18</v>
@@ -30153,7 +30198,7 @@
         <v>515</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>712</v>
@@ -30191,7 +30236,7 @@
         <v>588</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>664</v>
@@ -31065,7 +31110,7 @@
         <v>209</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>211</v>
@@ -31103,7 +31148,7 @@
         <v>209</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>211</v>
@@ -31445,7 +31490,7 @@
         <v>430</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="C56" s="34" t="s">
         <v>56</v>
@@ -32164,7 +32209,7 @@
     </row>
     <row r="75" spans="1:12" ht="15">
       <c r="A75" s="11" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>663</v>
@@ -32395,7 +32440,7 @@
         <v>745</v>
       </c>
       <c r="B81" s="34" t="s">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="C81" s="34" t="s">
         <v>747</v>
@@ -36537,15 +36582,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008FFDA55EC64F6340997887DF003F4858" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="610c4182e7e7902e7aea694cdd9432aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb079858-90af-4c1d-b6f1-55332f11d181" xmlns:ns3="465031c5-3d91-457d-a71b-eb9b5941244d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="92492927522a77c15d270bbe3d3d4b37" ns2:_="" ns3:_="">
     <xsd:import namespace="bb079858-90af-4c1d-b6f1-55332f11d181"/>
@@ -36780,14 +36816,23 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D66E9BA-12AB-4417-9A6A-6113397F4F5F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F40177C-67A3-4DD8-A168-9BC85606FD5C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6492E40-AF0B-480F-B23D-6DA53B2EBE0E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6492E40-AF0B-480F-B23D-6DA53B2EBE0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F40177C-67A3-4DD8-A168-9BC85606FD5C}"/>
 </file>
--- a/data/warn-scraper/cache/ia/source.xlsx
+++ b/data/warn-scraper/cache/ia/source.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30413"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iowamac.sharepoint.com/sites/IWDWorkforceServices/Shared Documents/Rapid Response/WARN/WARN Log/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F85C923E-CD68-41EE-98C5-D6406E8C9E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{769AC9C2-A5FB-4545-850B-FDD2B89876A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -46,12 +46,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6854" uniqueCount="1197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6862" uniqueCount="1197">
   <si>
     <t>Iowa WARN Log</t>
   </si>
   <si>
-    <t>Updated: 09-01-2026</t>
+    <t>Updated: 09-02-2026</t>
   </si>
   <si>
     <t>Company</t>
@@ -5589,8 +5589,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L93" totalsRowShown="0" headerRowDxfId="77">
-  <autoFilter ref="A2:L93" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}" name="Table4" displayName="Table4" ref="A2:L94" totalsRowShown="0" headerRowDxfId="77">
+  <autoFilter ref="A2:L94" xr:uid="{82138FD0-8F80-44C1-A2D4-3DBE3F5E46DA}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{624CA823-360D-451E-81B4-66E6AEBB7049}" name="Company" dataDxfId="76"/>
     <tableColumn id="2" xr3:uid="{2CB99E09-68C4-4CD3-8D8C-07722FD0C438}" name="Address Line 1" dataDxfId="75"/>
@@ -9446,18 +9446,42 @@
       </c>
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1">
-      <c r="A94" s="6"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="5"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="5"/>
-      <c r="I94" s="22"/>
-      <c r="J94" s="22"/>
-      <c r="K94" s="2"/>
-      <c r="L94" s="2"/>
+      <c r="A94" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="B94" s="76" t="s">
+        <v>138</v>
+      </c>
+      <c r="C94" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="D94" s="76" t="s">
+        <v>25</v>
+      </c>
+      <c r="E94" s="76" t="s">
+        <v>18</v>
+      </c>
+      <c r="F94" s="77">
+        <v>50266</v>
+      </c>
+      <c r="G94" s="76" t="s">
+        <v>142</v>
+      </c>
+      <c r="H94" s="77">
+        <v>5</v>
+      </c>
+      <c r="I94" s="78">
+        <v>46266</v>
+      </c>
+      <c r="J94" s="78">
+        <v>46326</v>
+      </c>
+      <c r="K94" s="76" t="s">
+        <v>27</v>
+      </c>
+      <c r="L94" s="76" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:XFD2">
@@ -36582,6 +36606,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008FFDA55EC64F6340997887DF003F4858" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="610c4182e7e7902e7aea694cdd9432aa">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bb079858-90af-4c1d-b6f1-55332f11d181" xmlns:ns3="465031c5-3d91-457d-a71b-eb9b5941244d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="92492927522a77c15d270bbe3d3d4b37" ns2:_="" ns3:_="">
     <xsd:import namespace="bb079858-90af-4c1d-b6f1-55332f11d181"/>
@@ -36816,23 +36849,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4D66E9BA-12AB-4417-9A6A-6113397F4F5F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6492E40-AF0B-480F-B23D-6DA53B2EBE0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F40177C-67A3-4DD8-A168-9BC85606FD5C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F40177C-67A3-4DD8-A168-9BC85606FD5C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6492E40-AF0B-480F-B23D-6DA53B2EBE0E}"/>
 </file>